--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B2" t="n">
         <v>79018</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R2" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127554096</v>
+        <v>127511371</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R3" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127511371</v>
+        <v>127503574</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127503663</v>
+        <v>127505584</v>
       </c>
       <c r="B5" t="n">
         <v>79018</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464847</v>
+        <v>464920</v>
       </c>
       <c r="R5" t="n">
-        <v>6784531</v>
+        <v>6784591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127601236</v>
+        <v>127566254</v>
       </c>
       <c r="B6" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464862</v>
+        <v>464782</v>
       </c>
       <c r="R6" t="n">
-        <v>6784534</v>
+        <v>6784529</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,14 +1171,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,29 +1192,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127505584</v>
+        <v>127602494</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,37 +1221,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464920</v>
+        <v>464821</v>
       </c>
       <c r="R7" t="n">
-        <v>6784591</v>
+        <v>6784490</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,19 +1281,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,18 +1297,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127602494</v>
+        <v>127503663</v>
       </c>
       <c r="B10" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,40 +1546,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464821</v>
+        <v>464847</v>
       </c>
       <c r="R10" t="n">
-        <v>6784490</v>
+        <v>6784531</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,14 +1603,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,29 +1624,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127566254</v>
+        <v>127601236</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,37 +1653,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464782</v>
+        <v>464862</v>
       </c>
       <c r="R11" t="n">
-        <v>6784529</v>
+        <v>6784534</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,19 +1713,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,18 +1729,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
         <v>127502947</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127503996</v>
+        <v>127518186</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464844</v>
+        <v>464838</v>
       </c>
       <c r="R13" t="n">
-        <v>6784533</v>
+        <v>6784648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127518186</v>
+        <v>127503996</v>
       </c>
       <c r="B14" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464838</v>
+        <v>464844</v>
       </c>
       <c r="R14" t="n">
-        <v>6784648</v>
+        <v>6784533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127504284</v>
+        <v>127581092</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2210,13 +2210,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464840</v>
+        <v>464794</v>
       </c>
       <c r="R16" t="n">
-        <v>6784571</v>
+        <v>6784479</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2256,11 +2256,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,53 +2282,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127503447</v>
+        <v>127585141</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464865</v>
+        <v>464827</v>
       </c>
       <c r="R17" t="n">
-        <v>6784539</v>
+        <v>6784453</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2399,48 +2389,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127581242</v>
+        <v>127503447</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464794</v>
+        <v>464865</v>
       </c>
       <c r="R18" t="n">
-        <v>6784479</v>
+        <v>6784539</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2506,7 +2501,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127585141</v>
+        <v>127504284</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2541,13 +2536,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464827</v>
+        <v>464840</v>
       </c>
       <c r="R19" t="n">
-        <v>6784453</v>
+        <v>6784571</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,6 +2582,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127505687</v>
+        <v>127602544</v>
       </c>
       <c r="B20" t="n">
-        <v>57658</v>
+        <v>79607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,42 +2624,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464919</v>
+        <v>464858</v>
       </c>
       <c r="R20" t="n">
-        <v>6784599</v>
+        <v>6784447</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,24 +2684,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bild på skalad torraka</t>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,55 +2700,62 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127602544</v>
+        <v>127602573</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2768,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464858</v>
+        <v>464867</v>
       </c>
       <c r="R21" t="n">
-        <v>6784447</v>
+        <v>6784461</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en tallstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,57 +2831,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127602573</v>
+        <v>127580771</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464867</v>
+        <v>464785</v>
       </c>
       <c r="R22" t="n">
-        <v>6784461</v>
+        <v>6784477</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,14 +2899,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,29 +2920,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127503116</v>
+        <v>127505687</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,37 +2949,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464870</v>
+        <v>464919</v>
       </c>
       <c r="R23" t="n">
-        <v>6784516</v>
+        <v>6784599</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3029,6 +3024,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bild på skalad torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B24" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R24" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127580771</v>
+        <v>127524724</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464785</v>
+        <v>464825</v>
       </c>
       <c r="R25" t="n">
-        <v>6784477</v>
+        <v>6784652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,32 +3269,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127547132</v>
+        <v>127502954</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464846</v>
+        <v>464884</v>
       </c>
       <c r="R26" t="n">
-        <v>6784631</v>
+        <v>6784499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127538313</v>
+        <v>127547132</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,21 +3387,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464830</v>
+        <v>464846</v>
       </c>
       <c r="R27" t="n">
-        <v>6784627</v>
+        <v>6784631</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127502954</v>
+        <v>127537979</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464884</v>
+        <v>464830</v>
       </c>
       <c r="R28" t="n">
-        <v>6784499</v>
+        <v>6784627</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127550588</v>
+        <v>127545206</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464800</v>
+        <v>464836</v>
       </c>
       <c r="R29" t="n">
         <v>6784606</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3671,11 +3671,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3702,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127545206</v>
+        <v>127550588</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3737,13 +3732,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464836</v>
+        <v>464800</v>
       </c>
       <c r="R30" t="n">
         <v>6784606</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3783,6 +3778,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3932,21 +3932,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R32" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R34" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127503208</v>
+        <v>127503065</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464880</v>
+        <v>464885</v>
       </c>
       <c r="R36" t="n">
-        <v>6784522</v>
+        <v>6784500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,6 +4430,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4456,10 +4461,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127503065</v>
+        <v>127503208</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464885</v>
+        <v>464880</v>
       </c>
       <c r="R37" t="n">
-        <v>6784500</v>
+        <v>6784522</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,11 +4542,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4674,10 +4674,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127567350</v>
+        <v>127602770</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,37 +4685,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464790</v>
+        <v>464833</v>
       </c>
       <c r="R39" t="n">
-        <v>6784508</v>
+        <v>6784487</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4742,19 +4745,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,25 +4761,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B40" t="n">
         <v>79050</v>
@@ -4819,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R40" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4887,10 +4886,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127602073</v>
+        <v>127567350</v>
       </c>
       <c r="B41" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,40 +4897,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464813</v>
+        <v>464790</v>
       </c>
       <c r="R41" t="n">
-        <v>6784586</v>
+        <v>6784508</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4958,14 +4954,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,26 +4975,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R42" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127601649</v>
+        <v>127585927</v>
       </c>
       <c r="B43" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5111,40 +5111,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464890</v>
+        <v>464839</v>
       </c>
       <c r="R43" t="n">
-        <v>6784589</v>
+        <v>6784435</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5171,14 +5168,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5187,29 +5189,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127559415</v>
+        <v>127601649</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,37 +5218,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464894</v>
+        <v>464890</v>
       </c>
       <c r="R44" t="n">
-        <v>6784597</v>
+        <v>6784589</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,19 +5278,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,18 +5294,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127582753</v>
+        <v>127602118</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5436,37 +5436,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464803</v>
+        <v>464840</v>
       </c>
       <c r="R46" t="n">
-        <v>6784481</v>
+        <v>6784632</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5493,24 +5496,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter Fem bilder</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5519,28 +5512,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127602118</v>
+        <v>127582753</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5548,40 +5542,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464840</v>
+        <v>464803</v>
       </c>
       <c r="R47" t="n">
-        <v>6784632</v>
+        <v>6784481</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5608,14 +5599,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Rikligt i en radie av 50 meter Fem bilder</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5624,19 +5625,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127579179</v>
+        <v>127580584</v>
       </c>
       <c r="B53" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464790</v>
+        <v>464783</v>
       </c>
       <c r="R53" t="n">
-        <v>6784508</v>
+        <v>6784477</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,11 +6278,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Liten och stor, 2 ex bilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6309,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127580584</v>
+        <v>127579179</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6320,21 +6315,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464783</v>
+        <v>464790</v>
       </c>
       <c r="R54" t="n">
-        <v>6784477</v>
+        <v>6784508</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6390,6 +6385,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Liten och stor, 2 ex bilder</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6522,10 +6522,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B56" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R56" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6741,10 +6741,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6752,21 +6752,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,13 +6776,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R58" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,10 +6853,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127507819</v>
+        <v>127602418</v>
       </c>
       <c r="B59" t="n">
-        <v>75142</v>
+        <v>79050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6864,37 +6864,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464858</v>
+        <v>464873</v>
       </c>
       <c r="R59" t="n">
-        <v>6784650</v>
+        <v>6784704</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6921,19 +6924,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6942,28 +6940,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127602418</v>
+        <v>127507819</v>
       </c>
       <c r="B60" t="n">
-        <v>79050</v>
+        <v>75142</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6971,40 +6970,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464873</v>
+        <v>464858</v>
       </c>
       <c r="R60" t="n">
-        <v>6784704</v>
+        <v>6784650</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7031,14 +7027,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7047,19 +7048,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127504835</v>
+        <v>127538460</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464893</v>
+        <v>464830</v>
       </c>
       <c r="R62" t="n">
-        <v>6784570</v>
+        <v>6784627</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7259,11 +7259,6 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter Bilder på garn vid slutet av rullstensåsen mot väg, 3 bilder</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,10 +7285,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127538460</v>
+        <v>127504835</v>
       </c>
       <c r="B63" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7301,21 +7296,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7325,13 +7320,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464830</v>
+        <v>464893</v>
       </c>
       <c r="R63" t="n">
-        <v>6784627</v>
+        <v>6784570</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7371,6 +7366,11 @@
       <c r="AB63" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter Bilder på garn vid slutet av rullstensåsen mot väg, 3 bilder</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7397,7 +7397,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B64" t="n">
         <v>79018</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R64" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,11 +7478,6 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,7 +7504,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B65" t="n">
         <v>79018</v>
@@ -7544,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R65" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7592,6 +7587,11 @@
           <t>09:17</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Bild 3 på tall rikligt</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7613,6 +7613,3541 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127627233</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>464804</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6784620</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127627267</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>464839</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6784616</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127627395</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>464815</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6784485</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127627347</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>464841</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6784551</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127627464</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>464880</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6784448</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127626980</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>464883</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6784583</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127627244</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>185</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>464822</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6784620</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127627419</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>464828</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6784480</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127627476</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>464889</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6784444</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127626973</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>185</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>464856</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6784585</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127627165</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>464808</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6784637</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127626997</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>464848</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6784592</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På 1 tallstam och 1 gran</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127627349</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>464825</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6784560</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127627375</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>464790</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6784488</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127627343</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>464836</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6784540</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127627035</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>464881</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6784597</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127627017</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>464871</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6784599</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127626939</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>464858</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6784586</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127626956</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>185</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>464858</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6784586</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127626911</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>464868</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6784563</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127627429</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>464849</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6784448</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127627287</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>464842</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6784599</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På raka</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127627174</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>464796</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6784631</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127627007</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>464841</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6784612</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127627101</v>
+      </c>
+      <c r="B90" t="n">
+        <v>75142</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>464854</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6784664</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127627329</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>185</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>464867</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6784590</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127627383</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>464805</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6784486</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127627129</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>185</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>464866</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6784700</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127627242</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>464822</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6784620</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127627358</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>464792</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6784524</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127626927</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>464868</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6784557</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127627454</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>464860</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6784458</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På 3 granar</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127627351</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>464813</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6784554</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127626967</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>464854</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6784570</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127554096</v>
+        <v>127511371</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R2" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127511371</v>
+        <v>127503574</v>
       </c>
       <c r="B3" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R4" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127505584</v>
+        <v>127601236</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464920</v>
+        <v>464862</v>
       </c>
       <c r="R5" t="n">
-        <v>6784591</v>
+        <v>6784534</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,19 +1067,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,28 +1083,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127566254</v>
+        <v>127602494</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1113,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464782</v>
+        <v>464821</v>
       </c>
       <c r="R6" t="n">
-        <v>6784529</v>
+        <v>6784490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1173,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,28 +1189,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127602494</v>
+        <v>127566254</v>
       </c>
       <c r="B7" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,40 +1219,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464821</v>
+        <v>464782</v>
       </c>
       <c r="R7" t="n">
-        <v>6784490</v>
+        <v>6784529</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,14 +1276,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,51 +1297,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127540024</v>
+        <v>127505584</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464840</v>
+        <v>464920</v>
       </c>
       <c r="R8" t="n">
-        <v>6784637</v>
+        <v>6784591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1396,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild torraka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127536063</v>
+        <v>127503663</v>
       </c>
       <c r="B9" t="n">
         <v>79018</v>
@@ -1463,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464819</v>
+        <v>464847</v>
       </c>
       <c r="R9" t="n">
-        <v>6784639</v>
+        <v>6784531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127503663</v>
+        <v>127536063</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1570,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464847</v>
+        <v>464819</v>
       </c>
       <c r="R10" t="n">
-        <v>6784531</v>
+        <v>6784639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,51 +1636,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127601236</v>
+        <v>127540024</v>
       </c>
       <c r="B11" t="n">
-        <v>79050</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464862</v>
+        <v>464840</v>
       </c>
       <c r="R11" t="n">
-        <v>6784534</v>
+        <v>6784637</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,14 +1704,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Bild torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,29 +1730,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127502947</v>
+        <v>127518186</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464884</v>
+        <v>464838</v>
       </c>
       <c r="R12" t="n">
-        <v>6784499</v>
+        <v>6784648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127518186</v>
+        <v>127503996</v>
       </c>
       <c r="B13" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464838</v>
+        <v>464844</v>
       </c>
       <c r="R13" t="n">
-        <v>6784648</v>
+        <v>6784533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127503996</v>
+        <v>127502947</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464844</v>
+        <v>464884</v>
       </c>
       <c r="R14" t="n">
-        <v>6784533</v>
+        <v>6784499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2613,37 +2613,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127602544</v>
+        <v>127602573</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2651,10 +2657,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464858</v>
+        <v>464867</v>
       </c>
       <c r="R20" t="n">
-        <v>6784447</v>
+        <v>6784461</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2691,7 +2697,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På en tallstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,43 +2725,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127602573</v>
+        <v>127602544</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464867</v>
+        <v>464858</v>
       </c>
       <c r="R21" t="n">
-        <v>6784461</v>
+        <v>6784447</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127503116</v>
+        <v>127524724</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,21 +3066,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464870</v>
+        <v>464825</v>
       </c>
       <c r="R24" t="n">
-        <v>6784516</v>
+        <v>6784652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B25" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R25" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,32 +3269,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127502954</v>
+        <v>127547132</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464884</v>
+        <v>464846</v>
       </c>
       <c r="R26" t="n">
-        <v>6784499</v>
+        <v>6784631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127547132</v>
+        <v>127537979</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,21 +3387,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464846</v>
+        <v>464830</v>
       </c>
       <c r="R27" t="n">
-        <v>6784631</v>
+        <v>6784627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127537979</v>
+        <v>127502954</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464830</v>
+        <v>464884</v>
       </c>
       <c r="R28" t="n">
-        <v>6784627</v>
+        <v>6784499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127545206</v>
+        <v>127530350</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79019</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464836</v>
+        <v>464867</v>
       </c>
       <c r="R29" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3671,6 +3671,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,32 +3814,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127530350</v>
+        <v>127545206</v>
       </c>
       <c r="B31" t="n">
-        <v>79019</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3844,13 +3849,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464867</v>
+        <v>464836</v>
       </c>
       <c r="R31" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3890,11 +3895,6 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4674,10 +4674,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127602770</v>
+        <v>127567350</v>
       </c>
       <c r="B39" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,40 +4685,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464833</v>
+        <v>464790</v>
       </c>
       <c r="R39" t="n">
-        <v>6784487</v>
+        <v>6784508</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4745,14 +4742,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4761,26 +4763,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B40" t="n">
         <v>79050</v>
@@ -4818,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R40" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4886,10 +4887,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127567350</v>
+        <v>127602073</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,37 +4898,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464790</v>
+        <v>464813</v>
       </c>
       <c r="R41" t="n">
-        <v>6784508</v>
+        <v>6784586</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4954,19 +4958,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,25 +4974,26 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R42" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R43" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127601608</v>
+        <v>127506640</v>
       </c>
       <c r="B48" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,40 +5654,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464891</v>
+        <v>464876</v>
       </c>
       <c r="R48" t="n">
-        <v>6784591</v>
+        <v>6784663</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5714,14 +5711,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Bild med tall i bakgrund</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5730,76 +5737,66 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127601723</v>
+        <v>127505537</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464899</v>
+        <v>464924</v>
       </c>
       <c r="R49" t="n">
-        <v>6784610</v>
+        <v>6784563</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5826,14 +5823,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>Bild på stam mot topp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5842,29 +5849,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127506640</v>
+        <v>127601608</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5872,37 +5878,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464876</v>
+        <v>464891</v>
       </c>
       <c r="R50" t="n">
-        <v>6784663</v>
+        <v>6784591</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5929,24 +5938,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Bild med tall i bakgrund</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5955,66 +5954,76 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127505537</v>
+        <v>127601723</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464924</v>
+        <v>464899</v>
       </c>
       <c r="R51" t="n">
-        <v>6784563</v>
+        <v>6784610</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6041,24 +6050,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Bild på stam mot topp</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6067,18 +6066,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R56" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6634,7 +6634,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127539258</v>
+        <v>127544415</v>
       </c>
       <c r="B57" t="n">
         <v>79018</v>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464840</v>
+        <v>464836</v>
       </c>
       <c r="R57" t="n">
-        <v>6784645</v>
+        <v>6784606</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6715,6 +6715,11 @@
       <c r="AB57" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6741,10 +6746,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127562945</v>
+        <v>127507819</v>
       </c>
       <c r="B58" t="n">
-        <v>91350</v>
+        <v>75142</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6752,21 +6757,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6776,10 +6781,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464814</v>
+        <v>464858</v>
       </c>
       <c r="R58" t="n">
-        <v>6784582</v>
+        <v>6784650</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6822,11 +6827,6 @@
       <c r="AB58" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,10 +6853,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127602418</v>
+        <v>127539258</v>
       </c>
       <c r="B59" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6864,40 +6864,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464873</v>
+        <v>464840</v>
       </c>
       <c r="R59" t="n">
-        <v>6784704</v>
+        <v>6784645</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6924,14 +6921,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6940,29 +6942,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127507819</v>
+        <v>127602418</v>
       </c>
       <c r="B60" t="n">
-        <v>75142</v>
+        <v>79050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6970,37 +6971,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464858</v>
+        <v>464873</v>
       </c>
       <c r="R60" t="n">
-        <v>6784650</v>
+        <v>6784704</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7027,19 +7031,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7048,18 +7047,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127627347</v>
+        <v>127627464</v>
       </c>
       <c r="B69" t="n">
         <v>79018</v>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464841</v>
+        <v>464880</v>
       </c>
       <c r="R69" t="n">
-        <v>6784551</v>
+        <v>6784448</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På 4 tallstammar</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8030,7 +8030,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127627464</v>
+        <v>127627347</v>
       </c>
       <c r="B70" t="n">
         <v>79018</v>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464880</v>
+        <v>464841</v>
       </c>
       <c r="R70" t="n">
-        <v>6784448</v>
+        <v>6784551</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8237,10 +8237,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627244</v>
+        <v>127627419</v>
       </c>
       <c r="B72" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8248,21 +8248,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464822</v>
+        <v>464828</v>
       </c>
       <c r="R72" t="n">
-        <v>6784620</v>
+        <v>6784480</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8311,6 +8311,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8338,7 +8343,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627419</v>
+        <v>127627476</v>
       </c>
       <c r="B73" t="n">
         <v>79018</v>
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464828</v>
+        <v>464889</v>
       </c>
       <c r="R73" t="n">
-        <v>6784480</v>
+        <v>6784444</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8416,7 +8421,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8444,10 +8449,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627476</v>
+        <v>127627244</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8455,21 +8460,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8482,10 +8487,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464889</v>
+        <v>464822</v>
       </c>
       <c r="R74" t="n">
-        <v>6784444</v>
+        <v>6784620</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8518,11 +8523,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9797,43 +9797,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127627287</v>
+        <v>127627174</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9841,10 +9835,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464842</v>
+        <v>464796</v>
       </c>
       <c r="R87" t="n">
-        <v>6784599</v>
+        <v>6784631</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9877,11 +9871,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På raka</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9909,7 +9898,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127627174</v>
+        <v>127627007</v>
       </c>
       <c r="B88" t="n">
         <v>79018</v>
@@ -9947,10 +9936,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464796</v>
+        <v>464841</v>
       </c>
       <c r="R88" t="n">
-        <v>6784631</v>
+        <v>6784612</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9983,6 +9972,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10010,37 +10004,43 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127627007</v>
+        <v>127627287</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464841</v>
+        <v>464842</v>
       </c>
       <c r="R89" t="n">
-        <v>6784612</v>
+        <v>6784599</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På 10 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10217,7 +10217,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127627329</v>
+        <v>127627129</v>
       </c>
       <c r="B91" t="n">
         <v>79050</v>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464867</v>
+        <v>464866</v>
       </c>
       <c r="R91" t="n">
-        <v>6784590</v>
+        <v>6784700</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10318,10 +10318,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127627383</v>
+        <v>127627329</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10329,21 +10329,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464805</v>
+        <v>464867</v>
       </c>
       <c r="R92" t="n">
-        <v>6784486</v>
+        <v>6784590</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127627129</v>
+        <v>127627383</v>
       </c>
       <c r="B93" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10430,21 +10430,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464866</v>
+        <v>464805</v>
       </c>
       <c r="R93" t="n">
-        <v>6784700</v>
+        <v>6784486</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10838,7 +10838,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127627454</v>
+        <v>127627351</v>
       </c>
       <c r="B97" t="n">
         <v>79018</v>
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464860</v>
+        <v>464813</v>
       </c>
       <c r="R97" t="n">
-        <v>6784458</v>
+        <v>6784554</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På 3 granar</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10944,7 +10944,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127627351</v>
+        <v>127627454</v>
       </c>
       <c r="B98" t="n">
         <v>79018</v>
@@ -10982,10 +10982,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464813</v>
+        <v>464860</v>
       </c>
       <c r="R98" t="n">
-        <v>6784554</v>
+        <v>6784458</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -3590,32 +3590,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127530350</v>
+        <v>127545206</v>
       </c>
       <c r="B29" t="n">
-        <v>79019</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464867</v>
+        <v>464836</v>
       </c>
       <c r="R29" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3671,11 +3671,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,32 +3809,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127545206</v>
+        <v>127530350</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79019</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3849,13 +3844,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464836</v>
+        <v>464867</v>
       </c>
       <c r="R31" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3895,6 +3890,11 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3921,32 +3921,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127584626</v>
+        <v>127554923</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464815</v>
+        <v>464854</v>
       </c>
       <c r="R32" t="n">
-        <v>6784461</v>
+        <v>6784587</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4028,32 +4028,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127554923</v>
+        <v>127584626</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464854</v>
+        <v>464815</v>
       </c>
       <c r="R33" t="n">
-        <v>6784587</v>
+        <v>6784461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127585927</v>
+        <v>127601649</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5004,37 +5004,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464839</v>
+        <v>464890</v>
       </c>
       <c r="R42" t="n">
-        <v>6784435</v>
+        <v>6784589</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5061,19 +5064,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,25 +5080,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -5135,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R43" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5207,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127601649</v>
+        <v>127559415</v>
       </c>
       <c r="B44" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5218,40 +5217,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464890</v>
+        <v>464894</v>
       </c>
       <c r="R44" t="n">
-        <v>6784589</v>
+        <v>6784597</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5278,14 +5274,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,29 +5295,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127504671</v>
+        <v>127582753</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5324,21 +5324,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464871</v>
+        <v>464803</v>
       </c>
       <c r="R45" t="n">
-        <v>6784572</v>
+        <v>6784481</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Miljöbilder på rullstensås vid stubben</t>
+          <t>Rikligt i en radie av 50 meter Fem bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5425,7 +5425,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127602118</v>
+        <v>127504671</v>
       </c>
       <c r="B46" t="n">
         <v>79636</v>
@@ -5454,22 +5454,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464840</v>
+        <v>464871</v>
       </c>
       <c r="R46" t="n">
-        <v>6784632</v>
+        <v>6784572</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,14 +5493,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Miljöbilder på rullstensås vid stubben</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,29 +5519,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127582753</v>
+        <v>127602118</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5542,37 +5548,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464803</v>
+        <v>464840</v>
       </c>
       <c r="R47" t="n">
-        <v>6784481</v>
+        <v>6784632</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5599,24 +5608,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter Fem bilder</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5625,18 +5624,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B64" t="n">
         <v>79018</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R64" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,6 +7478,11 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7504,7 +7509,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B65" t="n">
         <v>79018</v>
@@ -7539,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R65" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7585,11 +7590,6 @@
       <c r="AB65" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9378,10 +9378,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9389,21 +9389,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9454,11 +9454,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9484,10 +9479,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B84" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9495,21 +9490,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9558,6 +9553,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127511371</v>
+        <v>127554096</v>
       </c>
       <c r="B2" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R2" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127503574</v>
+        <v>127511371</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127554096</v>
+        <v>127503574</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R4" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1636,32 +1636,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127540024</v>
+        <v>127518186</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>75142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464840</v>
+        <v>464838</v>
       </c>
       <c r="R11" t="n">
-        <v>6784637</v>
+        <v>6784648</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,11 +1717,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bild torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127518186</v>
+        <v>127503996</v>
       </c>
       <c r="B12" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464838</v>
+        <v>464844</v>
       </c>
       <c r="R12" t="n">
-        <v>6784648</v>
+        <v>6784533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127503996</v>
+        <v>127601675</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,37 +1861,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464844</v>
+        <v>464886</v>
       </c>
       <c r="R13" t="n">
-        <v>6784533</v>
+        <v>6784594</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,19 +1921,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,25 +1937,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127502947</v>
+        <v>127581092</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -1997,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464884</v>
+        <v>464794</v>
       </c>
       <c r="R14" t="n">
-        <v>6784499</v>
+        <v>6784479</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127601675</v>
+        <v>127585141</v>
       </c>
       <c r="B15" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,40 +2074,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464886</v>
+        <v>464827</v>
       </c>
       <c r="R15" t="n">
-        <v>6784594</v>
+        <v>6784453</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,14 +2131,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,67 +2152,71 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127581092</v>
+        <v>127503447</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464794</v>
+        <v>464865</v>
       </c>
       <c r="R16" t="n">
-        <v>6784479</v>
+        <v>6784539</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127585141</v>
+        <v>127504284</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464827</v>
+        <v>464840</v>
       </c>
       <c r="R17" t="n">
-        <v>6784453</v>
+        <v>6784571</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,6 +2363,11 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127503447</v>
+        <v>127602573</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,42 +2405,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464865</v>
+        <v>464867</v>
       </c>
       <c r="R18" t="n">
-        <v>6784539</v>
+        <v>6784461</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2462,19 +2471,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,28 +2487,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127504284</v>
+        <v>127602544</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,37 +2517,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464840</v>
+        <v>464858</v>
       </c>
       <c r="R19" t="n">
-        <v>6784571</v>
+        <v>6784447</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,24 +2577,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2595,75 +2593,67 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127602573</v>
+        <v>127580771</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464867</v>
+        <v>464785</v>
       </c>
       <c r="R20" t="n">
-        <v>6784461</v>
+        <v>6784477</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,14 +2680,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,29 +2701,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127602544</v>
+        <v>127524724</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>75142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,40 +2730,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464858</v>
+        <v>464825</v>
       </c>
       <c r="R21" t="n">
-        <v>6784447</v>
+        <v>6784652</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,14 +2787,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,26 +2808,25 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127580771</v>
+        <v>127503116</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2866,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464785</v>
+        <v>464870</v>
       </c>
       <c r="R22" t="n">
-        <v>6784477</v>
+        <v>6784516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127505687</v>
+        <v>127547132</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2949,42 +2944,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464919</v>
+        <v>464846</v>
       </c>
       <c r="R23" t="n">
-        <v>6784599</v>
+        <v>6784631</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,11 +3014,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bild på skalad torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127524724</v>
+        <v>127537979</v>
       </c>
       <c r="B24" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464825</v>
+        <v>464830</v>
       </c>
       <c r="R24" t="n">
-        <v>6784652</v>
+        <v>6784627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127503116</v>
+        <v>127502954</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464870</v>
+        <v>464884</v>
       </c>
       <c r="R25" t="n">
-        <v>6784516</v>
+        <v>6784499</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,32 +3254,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127547132</v>
+        <v>127545206</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,13 +3289,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464846</v>
+        <v>464836</v>
       </c>
       <c r="R26" t="n">
-        <v>6784631</v>
+        <v>6784606</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3376,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127537979</v>
+        <v>127584626</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464830</v>
+        <v>464815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784627</v>
+        <v>6784461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,32 +3468,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127502954</v>
+        <v>127505499</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79607</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3518,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464884</v>
+        <v>464908</v>
       </c>
       <c r="R28" t="n">
-        <v>6784499</v>
+        <v>6784550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3590,32 +3575,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127545206</v>
+        <v>127580438</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3625,13 +3610,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464836</v>
+        <v>464780</v>
       </c>
       <c r="R29" t="n">
-        <v>6784606</v>
+        <v>6784485</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3697,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127550588</v>
+        <v>127503065</v>
       </c>
       <c r="B30" t="n">
         <v>79018</v>
@@ -3732,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464800</v>
+        <v>464885</v>
       </c>
       <c r="R30" t="n">
-        <v>6784606</v>
+        <v>6784500</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3767,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127530350</v>
+        <v>127503208</v>
       </c>
       <c r="B31" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,16 +3805,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464867</v>
+        <v>464880</v>
       </c>
       <c r="R31" t="n">
-        <v>6784698</v>
+        <v>6784522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,11 +3875,6 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3921,48 +3901,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127554923</v>
+        <v>127601782</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464854</v>
+        <v>464822</v>
       </c>
       <c r="R32" t="n">
-        <v>6784587</v>
+        <v>6784579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,19 +3972,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4010,25 +3988,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127584626</v>
+        <v>127567350</v>
       </c>
       <c r="B33" t="n">
         <v>79018</v>
@@ -4063,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464815</v>
+        <v>464790</v>
       </c>
       <c r="R33" t="n">
-        <v>6784461</v>
+        <v>6784508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127505499</v>
+        <v>127602770</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>79050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,37 +4125,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464908</v>
+        <v>464833</v>
       </c>
       <c r="R34" t="n">
-        <v>6784550</v>
+        <v>6784487</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,19 +4185,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4224,28 +4201,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127580438</v>
+        <v>127602073</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4253,37 +4231,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464780</v>
+        <v>464813</v>
       </c>
       <c r="R35" t="n">
-        <v>6784485</v>
+        <v>6784586</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4310,19 +4291,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4331,28 +4307,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127503065</v>
+        <v>127601649</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4360,37 +4337,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464885</v>
+        <v>464890</v>
       </c>
       <c r="R36" t="n">
-        <v>6784500</v>
+        <v>6784589</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4417,24 +4397,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bild 1</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,25 +4413,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127503208</v>
+        <v>127585927</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4496,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464880</v>
+        <v>464839</v>
       </c>
       <c r="R37" t="n">
-        <v>6784522</v>
+        <v>6784435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4568,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127601782</v>
+        <v>127559415</v>
       </c>
       <c r="B38" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4579,40 +4550,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464822</v>
+        <v>464894</v>
       </c>
       <c r="R38" t="n">
-        <v>6784579</v>
+        <v>6784597</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4639,14 +4607,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4655,29 +4628,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127567350</v>
+        <v>127602118</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,37 +4657,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464790</v>
+        <v>464840</v>
       </c>
       <c r="R39" t="n">
-        <v>6784508</v>
+        <v>6784632</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4742,19 +4717,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,28 +4733,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127602770</v>
+        <v>127601608</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>79636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4792,21 +4763,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4790,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464833</v>
+        <v>464891</v>
       </c>
       <c r="R40" t="n">
-        <v>6784487</v>
+        <v>6784591</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4859,7 +4830,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4887,37 +4858,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127602073</v>
+        <v>127601723</v>
       </c>
       <c r="B41" t="n">
-        <v>79050</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4925,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464813</v>
+        <v>464899</v>
       </c>
       <c r="R41" t="n">
-        <v>6784586</v>
+        <v>6784610</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,7 +4942,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4993,10 +4970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127601649</v>
+        <v>127582358</v>
       </c>
       <c r="B42" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5004,40 +4981,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464890</v>
+        <v>464803</v>
       </c>
       <c r="R42" t="n">
-        <v>6784589</v>
+        <v>6784481</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5064,14 +5038,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,26 +5059,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127585927</v>
+        <v>127580584</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -5134,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464839</v>
+        <v>464783</v>
       </c>
       <c r="R43" t="n">
-        <v>6784435</v>
+        <v>6784477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,10 +5184,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127559415</v>
+        <v>127601312</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,37 +5195,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464894</v>
+        <v>464864</v>
       </c>
       <c r="R44" t="n">
-        <v>6784597</v>
+        <v>6784567</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,19 +5255,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,28 +5271,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127582753</v>
+        <v>127507819</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5324,21 +5301,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5348,10 +5325,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464803</v>
+        <v>464858</v>
       </c>
       <c r="R45" t="n">
-        <v>6784481</v>
+        <v>6784650</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,11 +5371,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter Fem bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5425,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127504671</v>
+        <v>127539258</v>
       </c>
       <c r="B46" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5436,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5460,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464871</v>
+        <v>464840</v>
       </c>
       <c r="R46" t="n">
-        <v>6784572</v>
+        <v>6784645</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5506,11 +5478,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Miljöbilder på rullstensås vid stubben</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5537,10 +5504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127602118</v>
+        <v>127602418</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>79050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5548,21 +5515,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5575,10 +5542,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464840</v>
+        <v>464873</v>
       </c>
       <c r="R47" t="n">
-        <v>6784632</v>
+        <v>6784704</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5615,7 +5582,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5643,10 +5610,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127506640</v>
+        <v>127538460</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5654,21 +5621,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5678,10 +5645,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464876</v>
+        <v>464830</v>
       </c>
       <c r="R48" t="n">
-        <v>6784663</v>
+        <v>6784627</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5724,11 +5691,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Bild med tall i bakgrund</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5755,7 +5717,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127505537</v>
+        <v>127503078</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5790,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464924</v>
+        <v>464884</v>
       </c>
       <c r="R49" t="n">
-        <v>6784563</v>
+        <v>6784499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,11 +5798,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Bild på stam mot topp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5867,10 +5824,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127601608</v>
+        <v>127528615</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,40 +5835,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464891</v>
+        <v>464875</v>
       </c>
       <c r="R50" t="n">
-        <v>6784591</v>
+        <v>6784695</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5938,14 +5892,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,62 +5913,55 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127601723</v>
+        <v>127627233</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6017,13 +5969,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464899</v>
+        <v>464804</v>
       </c>
       <c r="R51" t="n">
-        <v>6784610</v>
+        <v>6784620</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6057,7 +6009,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6073,22 +6025,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127529581</v>
+        <v>127627267</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6096,34 +6048,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464875</v>
+        <v>464839</v>
       </c>
       <c r="R52" t="n">
-        <v>6784695</v>
+        <v>6784616</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6153,51 +6108,37 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2 bild vid lilla delen</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127580584</v>
+        <v>127627395</v>
       </c>
       <c r="B53" t="n">
         <v>79018</v>
@@ -6226,16 +6167,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464783</v>
+        <v>464815</v>
       </c>
       <c r="R53" t="n">
-        <v>6784477</v>
+        <v>6784485</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6265,49 +6209,40 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127579179</v>
+        <v>127627464</v>
       </c>
       <c r="B54" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6315,34 +6250,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464790</v>
+        <v>464880</v>
       </c>
       <c r="R54" t="n">
-        <v>6784508</v>
+        <v>6784448</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6372,24 +6310,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Liten och stor, 2 ex bilder</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6398,28 +6326,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127601312</v>
+        <v>127627347</v>
       </c>
       <c r="B55" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6427,21 +6356,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6454,13 +6383,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464864</v>
+        <v>464841</v>
       </c>
       <c r="R55" t="n">
-        <v>6784567</v>
+        <v>6784551</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6494,7 +6423,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6510,22 +6439,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127562945</v>
+        <v>127626980</v>
       </c>
       <c r="B56" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6533,34 +6462,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464814</v>
+        <v>464883</v>
       </c>
       <c r="R56" t="n">
-        <v>6784582</v>
+        <v>6784583</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6590,54 +6522,40 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Bilder, 2 exemplar</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127544415</v>
+        <v>127627244</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6645,37 +6563,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464836</v>
+        <v>464822</v>
       </c>
       <c r="R57" t="n">
-        <v>6784606</v>
+        <v>6784620</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6702,54 +6623,40 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127507819</v>
+        <v>127627419</v>
       </c>
       <c r="B58" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6757,34 +6664,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464858</v>
+        <v>464828</v>
       </c>
       <c r="R58" t="n">
-        <v>6784650</v>
+        <v>6784480</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,19 +6724,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6835,25 +6740,26 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127539258</v>
+        <v>127627476</v>
       </c>
       <c r="B59" t="n">
         <v>79018</v>
@@ -6882,16 +6788,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464840</v>
+        <v>464889</v>
       </c>
       <c r="R59" t="n">
-        <v>6784645</v>
+        <v>6784444</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6921,19 +6830,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6942,25 +6846,26 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127602418</v>
+        <v>127626973</v>
       </c>
       <c r="B60" t="n">
         <v>79050</v>
@@ -6998,13 +6903,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464873</v>
+        <v>464856</v>
       </c>
       <c r="R60" t="n">
-        <v>6784704</v>
+        <v>6784585</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7034,11 +6939,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7054,22 +6954,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127554764</v>
+        <v>127627165</v>
       </c>
       <c r="B61" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7077,34 +6977,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464854</v>
+        <v>464808</v>
       </c>
       <c r="R61" t="n">
-        <v>6784587</v>
+        <v>6784637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7134,54 +7037,40 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bild på hakspår samt Mindre m...</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127538460</v>
+        <v>127626997</v>
       </c>
       <c r="B62" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,34 +7078,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464830</v>
+        <v>464848</v>
       </c>
       <c r="R62" t="n">
-        <v>6784627</v>
+        <v>6784592</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,19 +7138,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På 1 tallstam och 1 gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7267,25 +7154,26 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127504835</v>
+        <v>127627349</v>
       </c>
       <c r="B63" t="n">
         <v>79018</v>
@@ -7314,19 +7202,22 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464893</v>
+        <v>464825</v>
       </c>
       <c r="R63" t="n">
-        <v>6784570</v>
+        <v>6784560</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7353,24 +7244,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Bilder på garn vid slutet av rullstensåsen mot väg, 3 bilder</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7379,25 +7260,26 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127504014</v>
+        <v>127627375</v>
       </c>
       <c r="B64" t="n">
         <v>79018</v>
@@ -7426,16 +7308,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464846</v>
+        <v>464790</v>
       </c>
       <c r="R64" t="n">
-        <v>6784532</v>
+        <v>6784488</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,24 +7350,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7491,25 +7366,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127565174</v>
+        <v>127627343</v>
       </c>
       <c r="B65" t="n">
         <v>79018</v>
@@ -7538,16 +7414,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R65" t="n">
-        <v>6784582</v>
+        <v>6784540</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,19 +7456,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7598,25 +7472,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627233</v>
+        <v>127627035</v>
       </c>
       <c r="B66" t="n">
         <v>79018</v>
@@ -7654,10 +7529,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464804</v>
+        <v>464881</v>
       </c>
       <c r="R66" t="n">
-        <v>6784620</v>
+        <v>6784597</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7690,11 +7565,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7722,10 +7592,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627267</v>
+        <v>127627017</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7733,21 +7603,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7760,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464839</v>
+        <v>464871</v>
       </c>
       <c r="R67" t="n">
-        <v>6784616</v>
+        <v>6784599</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7823,7 +7693,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127627395</v>
+        <v>127626939</v>
       </c>
       <c r="B68" t="n">
         <v>79018</v>
@@ -7861,10 +7731,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464815</v>
+        <v>464858</v>
       </c>
       <c r="R68" t="n">
-        <v>6784485</v>
+        <v>6784586</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,6 +7767,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7924,10 +7799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127627464</v>
+        <v>127626956</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7935,21 +7810,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7962,10 +7837,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464880</v>
+        <v>464858</v>
       </c>
       <c r="R69" t="n">
-        <v>6784448</v>
+        <v>6784586</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7998,11 +7873,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8030,7 +7900,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127627347</v>
+        <v>127626911</v>
       </c>
       <c r="B70" t="n">
         <v>79018</v>
@@ -8068,10 +7938,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464841</v>
+        <v>464868</v>
       </c>
       <c r="R70" t="n">
-        <v>6784551</v>
+        <v>6784563</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,7 +7978,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På 4 tallstammar</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8136,7 +8006,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626980</v>
+        <v>127627429</v>
       </c>
       <c r="B71" t="n">
         <v>79018</v>
@@ -8174,10 +8044,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464883</v>
+        <v>464849</v>
       </c>
       <c r="R71" t="n">
-        <v>6784583</v>
+        <v>6784448</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,6 +8080,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8237,7 +8112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627419</v>
+        <v>127627174</v>
       </c>
       <c r="B72" t="n">
         <v>79018</v>
@@ -8275,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464828</v>
+        <v>464796</v>
       </c>
       <c r="R72" t="n">
-        <v>6784480</v>
+        <v>6784631</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8311,11 +8186,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8343,7 +8213,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627476</v>
+        <v>127627007</v>
       </c>
       <c r="B73" t="n">
         <v>79018</v>
@@ -8381,10 +8251,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464889</v>
+        <v>464841</v>
       </c>
       <c r="R73" t="n">
-        <v>6784444</v>
+        <v>6784612</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8421,7 +8291,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,37 +8319,43 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627244</v>
+        <v>127627287</v>
       </c>
       <c r="B74" t="n">
-        <v>79050</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8487,10 +8363,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464822</v>
+        <v>464842</v>
       </c>
       <c r="R74" t="n">
-        <v>6784620</v>
+        <v>6784599</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8523,6 +8399,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8550,10 +8431,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626973</v>
+        <v>127627101</v>
       </c>
       <c r="B75" t="n">
-        <v>79050</v>
+        <v>75142</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8561,21 +8442,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8588,10 +8469,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464856</v>
+        <v>464854</v>
       </c>
       <c r="R75" t="n">
-        <v>6784585</v>
+        <v>6784664</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8651,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627165</v>
+        <v>127627129</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8662,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8689,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464808</v>
+        <v>464866</v>
       </c>
       <c r="R76" t="n">
-        <v>6784637</v>
+        <v>6784700</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8752,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127626997</v>
+        <v>127627329</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8763,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8790,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464848</v>
+        <v>464867</v>
       </c>
       <c r="R77" t="n">
-        <v>6784592</v>
+        <v>6784590</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8826,11 +8707,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På 1 tallstam och 1 gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8858,7 +8734,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627349</v>
+        <v>127627383</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8896,10 +8772,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464825</v>
+        <v>464805</v>
       </c>
       <c r="R78" t="n">
-        <v>6784560</v>
+        <v>6784486</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8932,11 +8808,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,7 +8835,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627375</v>
+        <v>127627242</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -9002,10 +8873,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464790</v>
+        <v>464822</v>
       </c>
       <c r="R79" t="n">
-        <v>6784488</v>
+        <v>6784620</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9042,7 +8913,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9070,7 +8941,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127627343</v>
+        <v>127627358</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -9108,10 +8979,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464836</v>
+        <v>464792</v>
       </c>
       <c r="R80" t="n">
-        <v>6784540</v>
+        <v>6784524</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9148,7 +9019,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På 5 tallstammar</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9176,7 +9047,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127627035</v>
+        <v>127626927</v>
       </c>
       <c r="B81" t="n">
         <v>79018</v>
@@ -9214,10 +9085,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464881</v>
+        <v>464868</v>
       </c>
       <c r="R81" t="n">
-        <v>6784597</v>
+        <v>6784557</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9250,6 +9121,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9277,7 +9153,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127627017</v>
+        <v>127627351</v>
       </c>
       <c r="B82" t="n">
         <v>79018</v>
@@ -9315,10 +9191,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464871</v>
+        <v>464813</v>
       </c>
       <c r="R82" t="n">
-        <v>6784599</v>
+        <v>6784554</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,6 +9227,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9378,10 +9259,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127626956</v>
+        <v>127627454</v>
       </c>
       <c r="B83" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9389,21 +9270,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9416,10 +9297,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464858</v>
+        <v>464860</v>
       </c>
       <c r="R83" t="n">
-        <v>6784586</v>
+        <v>6784458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9452,6 +9333,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9479,10 +9365,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127626939</v>
+        <v>127626967</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9490,21 +9376,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9517,10 +9403,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464858</v>
+        <v>464854</v>
       </c>
       <c r="R84" t="n">
-        <v>6784586</v>
+        <v>6784570</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9553,11 +9439,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9585,48 +9466,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127626911</v>
+        <v>127540024</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464868</v>
+        <v>464840</v>
       </c>
       <c r="R85" t="n">
-        <v>6784563</v>
+        <v>6784637</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9656,14 +9534,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>Bild torraka</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,56 +9560,56 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127627429</v>
+        <v>127681891</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9729,13 +9617,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464849</v>
+        <v>464897</v>
       </c>
       <c r="R86" t="n">
-        <v>6784448</v>
+        <v>6784620</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9765,11 +9653,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9785,22 +9668,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127627174</v>
+        <v>127505687</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,26 +9691,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9835,13 +9723,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464796</v>
+        <v>464919</v>
       </c>
       <c r="R87" t="n">
-        <v>6784631</v>
+        <v>6784599</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9868,37 +9756,46 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127627007</v>
+        <v>127550588</v>
       </c>
       <c r="B88" t="n">
         <v>79018</v>
@@ -9927,19 +9824,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464841</v>
+        <v>464800</v>
       </c>
       <c r="R88" t="n">
-        <v>6784612</v>
+        <v>6784606</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9969,14 +9863,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På 10 tallstammar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9985,73 +9889,63 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127627287</v>
+        <v>127530350</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79019</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464842</v>
+        <v>464867</v>
       </c>
       <c r="R89" t="n">
-        <v>6784599</v>
+        <v>6784698</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10081,14 +9975,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10097,57 +10001,53 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127627101</v>
+        <v>127554923</v>
       </c>
       <c r="B90" t="n">
-        <v>75142</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -10157,7 +10057,7 @@
         <v>464854</v>
       </c>
       <c r="R90" t="n">
-        <v>6784664</v>
+        <v>6784587</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10187,40 +10087,49 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127627129</v>
+        <v>127504671</v>
       </c>
       <c r="B91" t="n">
-        <v>79050</v>
+        <v>79636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10228,37 +10137,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464866</v>
+        <v>464871</v>
       </c>
       <c r="R91" t="n">
-        <v>6784700</v>
+        <v>6784572</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10288,40 +10194,54 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Miljöbilder på rullstensås vid stubben</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127627329</v>
+        <v>127506640</v>
       </c>
       <c r="B92" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10329,37 +10249,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464867</v>
+        <v>464876</v>
       </c>
       <c r="R92" t="n">
-        <v>6784590</v>
+        <v>6784663</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,37 +10306,51 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Bild med tall i bakgrund</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127627383</v>
+        <v>127505537</v>
       </c>
       <c r="B93" t="n">
         <v>79018</v>
@@ -10448,19 +10379,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464805</v>
+        <v>464924</v>
       </c>
       <c r="R93" t="n">
-        <v>6784486</v>
+        <v>6784563</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10490,40 +10418,54 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Bild på stam mot topp</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127627242</v>
+        <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10531,21 +10473,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10558,10 +10500,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464822</v>
+        <v>464790</v>
       </c>
       <c r="R94" t="n">
-        <v>6784620</v>
+        <v>6784508</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10591,14 +10533,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>3 ex på samma tall, bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10614,19 +10566,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127627358</v>
+        <v>127544415</v>
       </c>
       <c r="B95" t="n">
         <v>79018</v>
@@ -10655,22 +10607,19 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464792</v>
+        <v>464836</v>
       </c>
       <c r="R95" t="n">
-        <v>6784524</v>
+        <v>6784606</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10697,14 +10646,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10713,29 +10672,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127626927</v>
+        <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10743,37 +10701,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464868</v>
+        <v>464814</v>
       </c>
       <c r="R96" t="n">
-        <v>6784557</v>
+        <v>6784582</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10803,14 +10758,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10819,29 +10784,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127627351</v>
+        <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10849,26 +10813,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10876,10 +10841,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464813</v>
+        <v>464854</v>
       </c>
       <c r="R97" t="n">
-        <v>6784554</v>
+        <v>6784587</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10909,14 +10874,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10925,26 +10900,25 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127627454</v>
+        <v>127504835</v>
       </c>
       <c r="B98" t="n">
         <v>79018</v>
@@ -10982,13 +10956,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464860</v>
+        <v>464893</v>
       </c>
       <c r="R98" t="n">
-        <v>6784458</v>
+        <v>6784570</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11015,14 +10989,24 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På 3 granar</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11038,22 +11022,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127626967</v>
+        <v>127504014</v>
       </c>
       <c r="B99" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11061,37 +11045,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464854</v>
+        <v>464846</v>
       </c>
       <c r="R99" t="n">
-        <v>6784570</v>
+        <v>6784532</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11121,33 +11102,163 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Bild 3 på tall rikligt</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127565174</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>464814</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6784582</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127554096</v>
+        <v>127511371</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R2" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127511371</v>
+        <v>127503574</v>
       </c>
       <c r="B3" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R4" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127601236</v>
+        <v>127505584</v>
       </c>
       <c r="B5" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,40 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464862</v>
+        <v>464920</v>
       </c>
       <c r="R5" t="n">
-        <v>6784534</v>
+        <v>6784591</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,14 +1064,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,29 +1085,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127602494</v>
+        <v>127503663</v>
       </c>
       <c r="B6" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464821</v>
+        <v>464847</v>
       </c>
       <c r="R6" t="n">
-        <v>6784490</v>
+        <v>6784531</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,14 +1171,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,26 +1192,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127566254</v>
+        <v>127536063</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1243,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464782</v>
+        <v>464819</v>
       </c>
       <c r="R7" t="n">
-        <v>6784529</v>
+        <v>6784639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127505584</v>
+        <v>127566254</v>
       </c>
       <c r="B8" t="n">
         <v>79018</v>
@@ -1350,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464920</v>
+        <v>464782</v>
       </c>
       <c r="R8" t="n">
-        <v>6784591</v>
+        <v>6784529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127503663</v>
+        <v>127601236</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,37 +1435,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464847</v>
+        <v>464862</v>
       </c>
       <c r="R9" t="n">
-        <v>6784531</v>
+        <v>6784534</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,19 +1495,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,28 +1511,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127536063</v>
+        <v>127602494</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,37 +1541,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464819</v>
+        <v>464821</v>
       </c>
       <c r="R10" t="n">
-        <v>6784639</v>
+        <v>6784490</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,19 +1601,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,18 +1617,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2170,50 +2170,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127503447</v>
+        <v>127504284</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464865</v>
+        <v>464840</v>
       </c>
       <c r="R16" t="n">
-        <v>6784539</v>
+        <v>6784571</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2256,6 +2251,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,45 +2282,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127504284</v>
+        <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464840</v>
+        <v>464865</v>
       </c>
       <c r="R17" t="n">
-        <v>6784571</v>
+        <v>6784539</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2363,11 +2368,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,57 +2394,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127602573</v>
+        <v>127524724</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>75142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464867</v>
+        <v>464825</v>
       </c>
       <c r="R18" t="n">
-        <v>6784461</v>
+        <v>6784652</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2471,14 +2462,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,29 +2483,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127602544</v>
+        <v>127503116</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,40 +2512,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464858</v>
+        <v>464870</v>
       </c>
       <c r="R19" t="n">
-        <v>6784447</v>
+        <v>6784516</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2577,14 +2569,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,67 +2590,75 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127580771</v>
+        <v>127602573</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464785</v>
+        <v>464867</v>
       </c>
       <c r="R20" t="n">
-        <v>6784477</v>
+        <v>6784461</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2680,19 +2685,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,28 +2701,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127524724</v>
+        <v>127602544</v>
       </c>
       <c r="B21" t="n">
-        <v>75142</v>
+        <v>79607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,37 +2731,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464825</v>
+        <v>464858</v>
       </c>
       <c r="R21" t="n">
-        <v>6784652</v>
+        <v>6784447</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,19 +2791,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,25 +2807,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127503116</v>
+        <v>127580771</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464870</v>
+        <v>464785</v>
       </c>
       <c r="R22" t="n">
-        <v>6784516</v>
+        <v>6784477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R27" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B34" t="n">
         <v>79050</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R34" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B35" t="n">
         <v>79050</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R35" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127601649</v>
+        <v>127585927</v>
       </c>
       <c r="B36" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,40 +4337,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464890</v>
+        <v>464839</v>
       </c>
       <c r="R36" t="n">
-        <v>6784589</v>
+        <v>6784435</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,14 +4394,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4413,26 +4415,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4467,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R37" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,10 +4540,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127559415</v>
+        <v>127601649</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,37 +4551,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464894</v>
+        <v>464890</v>
       </c>
       <c r="R38" t="n">
-        <v>6784597</v>
+        <v>6784589</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4607,19 +4611,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,18 +4627,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4752,37 +4752,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127601608</v>
+        <v>127601723</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4790,10 +4796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464891</v>
+        <v>464899</v>
       </c>
       <c r="R40" t="n">
-        <v>6784591</v>
+        <v>6784610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4836,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,43 +4864,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127601723</v>
+        <v>127601608</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464899</v>
+        <v>464891</v>
       </c>
       <c r="R41" t="n">
-        <v>6784610</v>
+        <v>6784591</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5290,10 +5290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127507819</v>
+        <v>127602418</v>
       </c>
       <c r="B45" t="n">
-        <v>75142</v>
+        <v>79050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,37 +5301,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464858</v>
+        <v>464873</v>
       </c>
       <c r="R45" t="n">
-        <v>6784650</v>
+        <v>6784704</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5358,19 +5361,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5379,28 +5377,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127539258</v>
+        <v>127507819</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5407,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464840</v>
+        <v>464858</v>
       </c>
       <c r="R46" t="n">
-        <v>6784645</v>
+        <v>6784650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127602418</v>
+        <v>127539258</v>
       </c>
       <c r="B47" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,40 +5514,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464873</v>
+        <v>464840</v>
       </c>
       <c r="R47" t="n">
-        <v>6784704</v>
+        <v>6784645</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5575,14 +5571,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5591,19 +5592,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6552,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127627244</v>
+        <v>127627419</v>
       </c>
       <c r="B57" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464822</v>
+        <v>464828</v>
       </c>
       <c r="R57" t="n">
-        <v>6784620</v>
+        <v>6784480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,6 +6626,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6653,7 +6658,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127627419</v>
+        <v>127627476</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464828</v>
+        <v>464889</v>
       </c>
       <c r="R58" t="n">
-        <v>6784480</v>
+        <v>6784444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6759,10 +6764,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127627476</v>
+        <v>127627244</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6770,21 +6775,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6797,10 +6802,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464889</v>
+        <v>464822</v>
       </c>
       <c r="R59" t="n">
-        <v>6784444</v>
+        <v>6784620</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6833,11 +6838,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B60" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R60" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R61" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127627343</v>
+        <v>127627017</v>
       </c>
       <c r="B65" t="n">
         <v>79018</v>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464836</v>
+        <v>464871</v>
       </c>
       <c r="R65" t="n">
-        <v>6784540</v>
+        <v>6784599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7459,11 +7459,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7486,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627035</v>
+        <v>127627343</v>
       </c>
       <c r="B66" t="n">
         <v>79018</v>
@@ -7529,10 +7524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464881</v>
+        <v>464836</v>
       </c>
       <c r="R66" t="n">
-        <v>6784597</v>
+        <v>6784540</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7565,6 +7560,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7592,7 +7592,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627017</v>
+        <v>127627035</v>
       </c>
       <c r="B67" t="n">
         <v>79018</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464871</v>
+        <v>464881</v>
       </c>
       <c r="R67" t="n">
-        <v>6784599</v>
+        <v>6784597</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8112,37 +8112,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627174</v>
+        <v>127627287</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8150,10 +8156,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464796</v>
+        <v>464842</v>
       </c>
       <c r="R72" t="n">
-        <v>6784631</v>
+        <v>6784599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,6 +8192,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,7 +8224,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B73" t="n">
         <v>79018</v>
@@ -8251,10 +8262,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R73" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,11 +8298,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,43 +8325,37 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627287</v>
+        <v>127627007</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464842</v>
+        <v>464841</v>
       </c>
       <c r="R74" t="n">
-        <v>6784599</v>
+        <v>6784612</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627129</v>
+        <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464866</v>
+        <v>464805</v>
       </c>
       <c r="R76" t="n">
-        <v>6784700</v>
+        <v>6784486</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627329</v>
+        <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464867</v>
+        <v>464822</v>
       </c>
       <c r="R77" t="n">
-        <v>6784590</v>
+        <v>6784620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,6 +8707,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8734,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627383</v>
+        <v>127627329</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8745,21 +8750,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8772,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464805</v>
+        <v>464867</v>
       </c>
       <c r="R78" t="n">
-        <v>6784486</v>
+        <v>6784590</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8835,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627242</v>
+        <v>127627129</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8846,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464822</v>
+        <v>464866</v>
       </c>
       <c r="R79" t="n">
-        <v>6784620</v>
+        <v>6784700</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8909,11 +8914,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9578,38 +9578,42 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127681891</v>
+        <v>127505687</v>
       </c>
       <c r="B86" t="n">
-        <v>97325</v>
+        <v>57658</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9617,13 +9621,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464897</v>
+        <v>464919</v>
       </c>
       <c r="R86" t="n">
-        <v>6784620</v>
+        <v>6784599</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9650,18 +9654,27 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9680,42 +9693,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127505687</v>
+        <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>57658</v>
+        <v>97325</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9723,13 +9732,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464919</v>
+        <v>464897</v>
       </c>
       <c r="R87" t="n">
-        <v>6784599</v>
+        <v>6784620</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9756,27 +9765,18 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R88" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B89" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R89" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R95" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B96" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R96" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10802,10 +10802,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127554764</v>
+        <v>127504835</v>
       </c>
       <c r="B97" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10813,27 +10813,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10841,13 +10840,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464854</v>
+        <v>464893</v>
       </c>
       <c r="R97" t="n">
-        <v>6784587</v>
+        <v>6784570</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10891,7 +10890,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Bild på hackspår samt Mindre m...</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10900,6 +10899,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10918,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127504835</v>
+        <v>127554764</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10929,26 +10929,27 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10956,13 +10957,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464893</v>
+        <v>464854</v>
       </c>
       <c r="R98" t="n">
-        <v>6784570</v>
+        <v>6784587</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11006,7 +11007,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11015,7 +11016,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11260,6 +11260,4824 @@
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127706126</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>464701</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6784425</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127706550</v>
+      </c>
+      <c r="B102" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>464683</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6784461</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>3 bilder på vedsvamp, tallåga</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127706377</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>464687</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6784448</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127708066</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>464699</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6784396</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>2 bilder, rikligt på tall</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127705341</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>464871</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6784452</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127705741</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>464863</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6784423</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Vedsvamp på tallåga, 4 bilder</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127707668</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>464689</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6784378</v>
+      </c>
+      <c r="S107" t="n">
+        <v>50</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127707616</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>464701</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6784412</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127707829</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>464707</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6784355</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127706778</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>464678</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6784479</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127706080</v>
+      </c>
+      <c r="B111" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>464701</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6784425</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127706856</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>464680</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6784495</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127705423</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>464849</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6784443</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127707057</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>464666</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6784496</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 bild på stam mot krona</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127705998</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>464708</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6784437</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127704413</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>464906</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6784432</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127704473</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>464897</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6784413</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127706997</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78777</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>464666</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6784496</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127706968</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>464673</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6784503</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>5 bilder på vedsvampar på tallåga</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127707041</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79607</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>464666</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6784496</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127706073</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>464701</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6784425</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127705869</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>464736</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6784473</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127706768</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>464683</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6784461</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127707243</v>
+      </c>
+      <c r="B124" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>464652</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6784464</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1 bild på låga med garnlav</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127705109</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>464872</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6784441</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127707809</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79607</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>464707</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6784355</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>1 bild på kraftig stubbe</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127705654</v>
+      </c>
+      <c r="B127" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>464863</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6784423</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127704405</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>464901</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6784434</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127704457</v>
+      </c>
+      <c r="B129" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>464901</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6784434</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>127707455</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>464669</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6784449</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>127707530</v>
+      </c>
+      <c r="B131" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>464686</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6784430</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127705327</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>464871</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6784452</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>1 bild, även Mindre mä..</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127707956</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>464719</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6784403</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127705478</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>464863</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6784423</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127707246</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>464652</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6784464</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>127707282</v>
+      </c>
+      <c r="B136" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>464658</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6784455</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127705832</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>464736</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6784473</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127705062</v>
+      </c>
+      <c r="B138" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>464888</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6784446</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127707368</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>464658</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6784455</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127707123</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>464660</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6784477</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127705893</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>464718</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6784460</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>127707100</v>
+      </c>
+      <c r="B142" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>464660</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6784477</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>2 bilder, hål ca 3 meter upp</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>127706848</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>464680</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6784495</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>127706356</v>
+      </c>
+      <c r="B144" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>464687</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6784448</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127511371</v>
       </c>
       <c r="B2" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127503574</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127554096</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127505584</v>
+        <v>127601236</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464920</v>
+        <v>464862</v>
       </c>
       <c r="R5" t="n">
-        <v>6784591</v>
+        <v>6784534</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,19 +1067,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,28 +1083,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127503663</v>
+        <v>127602494</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1113,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464847</v>
+        <v>464821</v>
       </c>
       <c r="R6" t="n">
-        <v>6784531</v>
+        <v>6784490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1173,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,28 +1189,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127536063</v>
+        <v>127566254</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464819</v>
+        <v>464782</v>
       </c>
       <c r="R7" t="n">
-        <v>6784639</v>
+        <v>6784529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127566254</v>
+        <v>127505584</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464782</v>
+        <v>464920</v>
       </c>
       <c r="R8" t="n">
-        <v>6784529</v>
+        <v>6784591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B9" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,40 +1433,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R9" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,14 +1490,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,29 +1511,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B10" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,40 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R10" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,14 +1597,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,29 +1618,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127601675</v>
+        <v>127518186</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>75144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,40 +1647,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464886</v>
+        <v>464838</v>
       </c>
       <c r="R11" t="n">
-        <v>6784594</v>
+        <v>6784648</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,14 +1704,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,29 +1725,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127518186</v>
+        <v>127503996</v>
       </c>
       <c r="B12" t="n">
-        <v>75142</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464838</v>
+        <v>464844</v>
       </c>
       <c r="R12" t="n">
-        <v>6784648</v>
+        <v>6784533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127503996</v>
+        <v>127601675</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,37 +1861,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464844</v>
+        <v>464886</v>
       </c>
       <c r="R13" t="n">
-        <v>6784533</v>
+        <v>6784594</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,19 +1921,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,28 +1937,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127581092</v>
+        <v>127504284</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464794</v>
+        <v>464840</v>
       </c>
       <c r="R14" t="n">
-        <v>6784479</v>
+        <v>6784571</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,6 +2037,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127585141</v>
+        <v>127581092</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464827</v>
+        <v>464794</v>
       </c>
       <c r="R15" t="n">
-        <v>6784453</v>
+        <v>6784479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127504284</v>
+        <v>127585141</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,13 +2210,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464840</v>
+        <v>464827</v>
       </c>
       <c r="R16" t="n">
-        <v>6784571</v>
+        <v>6784453</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,11 +2256,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,7 +2285,7 @@
         <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127524724</v>
       </c>
       <c r="B18" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>127503116</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,57 +2608,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127602573</v>
+        <v>127580771</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464867</v>
+        <v>464785</v>
       </c>
       <c r="R20" t="n">
-        <v>6784461</v>
+        <v>6784477</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,14 +2676,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,56 +2697,61 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127602544</v>
+        <v>127602573</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2758,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464858</v>
+        <v>464867</v>
       </c>
       <c r="R21" t="n">
-        <v>6784447</v>
+        <v>6784461</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2798,7 +2799,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en tallstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127580771</v>
+        <v>127602544</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,37 +2838,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464785</v>
+        <v>464858</v>
       </c>
       <c r="R22" t="n">
-        <v>6784477</v>
+        <v>6784447</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2894,19 +2898,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,18 +2914,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2936,7 +2936,7 @@
         <v>127547132</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>127537979</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R27" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127580438</v>
+        <v>127503065</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464780</v>
+        <v>464885</v>
       </c>
       <c r="R29" t="n">
-        <v>6784485</v>
+        <v>6784500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,6 +3656,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,10 +3687,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127503065</v>
+        <v>127503208</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464885</v>
+        <v>464880</v>
       </c>
       <c r="R30" t="n">
-        <v>6784500</v>
+        <v>6784522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127503208</v>
+        <v>127580438</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464880</v>
+        <v>464780</v>
       </c>
       <c r="R31" t="n">
-        <v>6784522</v>
+        <v>6784485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
         <v>127601782</v>
       </c>
       <c r="B32" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127567350</v>
+        <v>127602770</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,37 +4018,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464790</v>
+        <v>464833</v>
       </c>
       <c r="R33" t="n">
-        <v>6784508</v>
+        <v>6784487</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4075,19 +4078,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4096,18 +4094,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4117,7 +4116,7 @@
         <v>127602073</v>
       </c>
       <c r="B34" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4220,10 +4219,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602770</v>
+        <v>127567350</v>
       </c>
       <c r="B35" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,40 +4230,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464833</v>
+        <v>464790</v>
       </c>
       <c r="R35" t="n">
-        <v>6784487</v>
+        <v>6784508</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4291,14 +4287,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,19 +4308,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
         <v>127585927</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>127559415</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127601649</v>
       </c>
       <c r="B38" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>127602118</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>127601608</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>127582358</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127580584</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127601312</v>
       </c>
       <c r="B44" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>127602418</v>
       </c>
       <c r="B45" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>127507819</v>
       </c>
       <c r="B46" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>127539258</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>127538460</v>
       </c>
       <c r="B48" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127503078</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>127528615</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>127627233</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>127627267</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>127627395</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>127627464</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>127627347</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>127626980</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>127627419</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>127627476</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>127627244</v>
       </c>
       <c r="B59" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R60" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B61" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R61" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,7 +7070,7 @@
         <v>127626997</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>127627349</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>127627375</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>127627343</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>127627035</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>127627017</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,21 +7704,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,11 +7769,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7799,10 +7794,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B69" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,21 +7805,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7875,6 +7870,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>127626911</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>127627429</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8112,37 +8112,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627174</v>
+        <v>127627287</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8150,10 +8156,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464796</v>
+        <v>464842</v>
       </c>
       <c r="R72" t="n">
-        <v>6784631</v>
+        <v>6784599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,6 +8192,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,10 +8224,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8251,10 +8262,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R73" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,11 +8298,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,43 +8325,37 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627287</v>
+        <v>127627007</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464842</v>
+        <v>464841</v>
       </c>
       <c r="R74" t="n">
-        <v>6784599</v>
+        <v>6784612</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8434,7 +8434,7 @@
         <v>127627101</v>
       </c>
       <c r="B75" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8739,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627329</v>
+        <v>127627129</v>
       </c>
       <c r="B78" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464867</v>
+        <v>464866</v>
       </c>
       <c r="R78" t="n">
-        <v>6784590</v>
+        <v>6784700</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8840,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627129</v>
+        <v>127627329</v>
       </c>
       <c r="B79" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464866</v>
+        <v>464867</v>
       </c>
       <c r="R79" t="n">
-        <v>6784700</v>
+        <v>6784590</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
         <v>127627358</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>127626927</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>127627351</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>127627454</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>127626967</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>127505687</v>
       </c>
       <c r="B86" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R88" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B89" t="n">
-        <v>79019</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R89" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10129,7 +10129,7 @@
         <v>127504671</v>
       </c>
       <c r="B91" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>127506640</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>127505537</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B95" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R95" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R96" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10805,7 +10805,7 @@
         <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>127504835</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11034,10 +11034,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11063,16 +11063,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R99" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11119,7 +11122,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11128,6 +11131,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11146,10 +11150,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11175,19 +11179,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R100" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11234,7 +11235,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Miljöbilder för området, rikligt med garnlav</t>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11243,7 +11244,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>127706126</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127705341</v>
+        <v>127706550</v>
       </c>
       <c r="B102" t="n">
         <v>8450</v>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464871</v>
+        <v>464683</v>
       </c>
       <c r="R102" t="n">
-        <v>6784452</v>
+        <v>6784461</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11450,6 +11450,11 @@
       <c r="AB102" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>3 bilder på vedsvamp, tallåga</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11476,32 +11481,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127705741</v>
+        <v>127705341</v>
       </c>
       <c r="B103" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11511,10 +11516,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464863</v>
+        <v>464871</v>
       </c>
       <c r="R103" t="n">
-        <v>6784423</v>
+        <v>6784452</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11557,11 +11562,6 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Vedsvamp på tallåga, 4 bilder</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11591,7 +11591,7 @@
         <v>127707668</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11700,10 +11700,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127707616</v>
+        <v>127706377</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464701</v>
+        <v>464687</v>
       </c>
       <c r="R105" t="n">
-        <v>6784412</v>
+        <v>6784448</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11807,32 +11807,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127706550</v>
+        <v>127708066</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464683</v>
+        <v>464699</v>
       </c>
       <c r="R106" t="n">
-        <v>6784461</v>
+        <v>6784396</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11919,10 +11919,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127706377</v>
+        <v>127705741</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464687</v>
+        <v>464863</v>
       </c>
       <c r="R107" t="n">
-        <v>6784448</v>
+        <v>6784423</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12000,6 +12000,11 @@
       <c r="AB107" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Vedsvamp på tallåga, 4 bilder</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12026,10 +12031,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127708066</v>
+        <v>127707616</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12061,10 +12066,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464699</v>
+        <v>464701</v>
       </c>
       <c r="R108" t="n">
-        <v>6784396</v>
+        <v>6784412</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12107,11 +12112,6 @@
       <c r="AB108" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12141,7 +12141,7 @@
         <v>127707829</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>127706778</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127705423</v>
+        <v>127707057</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464849</v>
+        <v>464666</v>
       </c>
       <c r="R113" t="n">
-        <v>6784443</v>
+        <v>6784496</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,6 +12647,11 @@
       <c r="AB113" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>1 bild på stam mot krona</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12673,10 +12678,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127707057</v>
+        <v>127705423</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12708,10 +12713,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464666</v>
+        <v>464849</v>
       </c>
       <c r="R114" t="n">
-        <v>6784496</v>
+        <v>6784443</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12754,11 +12759,6 @@
       <c r="AB114" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>1 bild på stam mot krona</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12788,7 +12788,7 @@
         <v>127705998</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12892,10 +12892,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127704413</v>
+        <v>127706968</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464906</v>
+        <v>464673</v>
       </c>
       <c r="R116" t="n">
-        <v>6784432</v>
+        <v>6784503</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12973,6 +12973,11 @@
       <c r="AB116" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>5 bilder på vedsvampar på tallåga</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12999,10 +13004,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127704473</v>
+        <v>127704413</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13034,10 +13039,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464897</v>
+        <v>464906</v>
       </c>
       <c r="R117" t="n">
-        <v>6784413</v>
+        <v>6784432</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13106,10 +13111,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127706997</v>
+        <v>127704473</v>
       </c>
       <c r="B118" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13117,21 +13122,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13141,10 +13146,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464666</v>
+        <v>464897</v>
       </c>
       <c r="R118" t="n">
-        <v>6784496</v>
+        <v>6784413</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13213,10 +13218,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127706968</v>
+        <v>127706997</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13224,21 +13229,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13248,10 +13253,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464673</v>
+        <v>464666</v>
       </c>
       <c r="R119" t="n">
-        <v>6784503</v>
+        <v>6784496</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13294,11 +13299,6 @@
       <c r="AB119" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>5 bilder på vedsvampar på tallåga</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13328,7 +13328,7 @@
         <v>127707041</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>127706073</v>
       </c>
       <c r="B121" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>127705869</v>
       </c>
       <c r="B122" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13661,32 +13661,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127707243</v>
+        <v>127706768</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464652</v>
+        <v>464683</v>
       </c>
       <c r="R123" t="n">
-        <v>6784464</v>
+        <v>6784461</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13742,11 +13742,6 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>1 bild på låga med garnlav</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13773,32 +13768,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127706768</v>
+        <v>127707243</v>
       </c>
       <c r="B124" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13808,10 +13803,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464683</v>
+        <v>464652</v>
       </c>
       <c r="R124" t="n">
-        <v>6784461</v>
+        <v>6784464</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13854,6 +13849,11 @@
       <c r="AB124" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1 bild på låga med garnlav</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13883,7 +13883,7 @@
         <v>127705109</v>
       </c>
       <c r="B125" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13987,50 +13987,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127705654</v>
+        <v>127707809</v>
       </c>
       <c r="B126" t="n">
-        <v>58031</v>
+        <v>79609</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464863</v>
+        <v>464707</v>
       </c>
       <c r="R126" t="n">
-        <v>6784423</v>
+        <v>6784355</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14073,6 +14068,11 @@
       <c r="AB126" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>1 bild på kraftig stubbe</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14102,7 +14102,7 @@
         <v>127704405</v>
       </c>
       <c r="B127" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14206,45 +14206,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127707809</v>
+        <v>127705654</v>
       </c>
       <c r="B128" t="n">
-        <v>79607</v>
+        <v>58033</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464707</v>
+        <v>464863</v>
       </c>
       <c r="R128" t="n">
-        <v>6784355</v>
+        <v>6784423</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14287,11 +14292,6 @@
       <c r="AB128" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>1 bild på kraftig stubbe</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14318,27 +14318,27 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127704457</v>
+        <v>127707455</v>
       </c>
       <c r="B129" t="n">
-        <v>58031</v>
+        <v>57663</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -14347,16 +14347,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464901</v>
+        <v>464669</v>
       </c>
       <c r="R129" t="n">
-        <v>6784434</v>
+        <v>6784449</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14399,6 +14404,11 @@
       <c r="AB129" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14425,38 +14435,38 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127707455</v>
+        <v>127707530</v>
       </c>
       <c r="B130" t="n">
-        <v>57661</v>
+        <v>56855</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14465,10 +14475,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464669</v>
+        <v>464686</v>
       </c>
       <c r="R130" t="n">
-        <v>6784449</v>
+        <v>6784430</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14515,7 +14525,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14542,10 +14552,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127707530</v>
+        <v>127704457</v>
       </c>
       <c r="B131" t="n">
-        <v>56853</v>
+        <v>58033</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14553,39 +14563,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>464686</v>
+        <v>464901</v>
       </c>
       <c r="R131" t="n">
-        <v>6784430</v>
+        <v>6784434</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14628,11 +14633,6 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14662,7 +14662,7 @@
         <v>127705327</v>
       </c>
       <c r="B132" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>127707956</v>
       </c>
       <c r="B133" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14883,32 +14883,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127707246</v>
+        <v>127707282</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14918,10 +14918,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464652</v>
+        <v>464658</v>
       </c>
       <c r="R134" t="n">
-        <v>6784464</v>
+        <v>6784455</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14990,32 +14990,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127707282</v>
+        <v>127707246</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15025,10 +15025,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464658</v>
+        <v>464652</v>
       </c>
       <c r="R135" t="n">
-        <v>6784455</v>
+        <v>6784464</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15100,7 +15100,7 @@
         <v>127705478</v>
       </c>
       <c r="B136" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15214,10 +15214,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127705832</v>
+        <v>127707368</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464736</v>
+        <v>464658</v>
       </c>
       <c r="R137" t="n">
-        <v>6784473</v>
+        <v>6784455</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15321,10 +15321,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127705062</v>
+        <v>127705832</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15356,10 +15356,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464888</v>
+        <v>464736</v>
       </c>
       <c r="R138" t="n">
-        <v>6784446</v>
+        <v>6784473</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15428,10 +15428,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127707368</v>
+        <v>127707123</v>
       </c>
       <c r="B139" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15463,10 +15463,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464658</v>
+        <v>464660</v>
       </c>
       <c r="R139" t="n">
-        <v>6784455</v>
+        <v>6784477</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15535,10 +15535,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127707123</v>
+        <v>127705062</v>
       </c>
       <c r="B140" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464660</v>
+        <v>464888</v>
       </c>
       <c r="R140" t="n">
-        <v>6784477</v>
+        <v>6784446</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15645,7 +15645,7 @@
         <v>127705893</v>
       </c>
       <c r="B141" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>127707100</v>
       </c>
       <c r="B142" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>127706848</v>
       </c>
       <c r="B143" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127714234</v>
+        <v>127721029</v>
       </c>
       <c r="B145" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16115,13 +16115,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464936</v>
+        <v>464816</v>
       </c>
       <c r="R145" t="n">
-        <v>6784248</v>
+        <v>6784317</v>
       </c>
       <c r="S145" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16187,32 +16187,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127718498</v>
+        <v>127715439</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16222,13 +16222,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>464686</v>
+        <v>464832</v>
       </c>
       <c r="R146" t="n">
-        <v>6784147</v>
+        <v>6784214</v>
       </c>
       <c r="S146" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16294,10 +16294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127720285</v>
+        <v>127714234</v>
       </c>
       <c r="B147" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16329,13 +16329,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464564</v>
+        <v>464936</v>
       </c>
       <c r="R147" t="n">
-        <v>6784324</v>
+        <v>6784248</v>
       </c>
       <c r="S147" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16374,12 +16374,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16406,10 +16401,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127715198</v>
+        <v>127720285</v>
       </c>
       <c r="B148" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16441,13 +16436,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464836</v>
+        <v>464564</v>
       </c>
       <c r="R148" t="n">
-        <v>6784199</v>
+        <v>6784324</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16487,6 +16482,11 @@
       <c r="AB148" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16513,10 +16513,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127715439</v>
+        <v>127715198</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16548,10 +16548,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464832</v>
+        <v>464836</v>
       </c>
       <c r="R149" t="n">
-        <v>6784214</v>
+        <v>6784199</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16620,10 +16620,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127718180</v>
+        <v>127719564</v>
       </c>
       <c r="B150" t="n">
-        <v>57658</v>
+        <v>79609</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16631,42 +16631,40 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464678</v>
+        <v>464859</v>
       </c>
       <c r="R150" t="n">
-        <v>6784123</v>
+        <v>6784218</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16693,24 +16691,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>2 bilder även på garn</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16719,28 +16707,29 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127719564</v>
+        <v>127718180</v>
       </c>
       <c r="B151" t="n">
-        <v>79607</v>
+        <v>57660</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16748,40 +16737,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464859</v>
+        <v>464678</v>
       </c>
       <c r="R151" t="n">
-        <v>6784218</v>
+        <v>6784123</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16808,14 +16799,24 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>2 bilder även på garn</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16824,51 +16825,50 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127721029</v>
+        <v>127718498</v>
       </c>
       <c r="B152" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16878,13 +16878,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464816</v>
+        <v>464686</v>
       </c>
       <c r="R152" t="n">
-        <v>6784317</v>
+        <v>6784147</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16950,10 +16950,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127719996</v>
+        <v>127719621</v>
       </c>
       <c r="B153" t="n">
-        <v>57821</v>
+        <v>78779</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16961,46 +16961,40 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464615</v>
+        <v>464775</v>
       </c>
       <c r="R153" t="n">
-        <v>6784345</v>
+        <v>6784302</v>
       </c>
       <c r="S153" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17027,19 +17021,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17048,28 +17037,29 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127719621</v>
+        <v>127715717</v>
       </c>
       <c r="B154" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17077,40 +17067,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464775</v>
+        <v>464788</v>
       </c>
       <c r="R154" t="n">
-        <v>6784302</v>
+        <v>6784220</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17137,14 +17124,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17153,29 +17145,28 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127718980</v>
+        <v>127718502</v>
       </c>
       <c r="B155" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17207,13 +17198,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464628</v>
+        <v>464686</v>
       </c>
       <c r="R155" t="n">
-        <v>6784279</v>
+        <v>6784147</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17279,10 +17270,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127718502</v>
+        <v>127718980</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17314,13 +17305,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464686</v>
+        <v>464628</v>
       </c>
       <c r="R156" t="n">
-        <v>6784147</v>
+        <v>6784279</v>
       </c>
       <c r="S156" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17389,7 +17380,7 @@
         <v>127718813</v>
       </c>
       <c r="B157" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17498,10 +17489,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127715717</v>
+        <v>127719996</v>
       </c>
       <c r="B158" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17509,37 +17500,46 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464788</v>
+        <v>464615</v>
       </c>
       <c r="R158" t="n">
-        <v>6784220</v>
+        <v>6784345</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17605,10 +17605,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127714269</v>
+        <v>127714347</v>
       </c>
       <c r="B159" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17640,10 +17640,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>464939</v>
+        <v>464931</v>
       </c>
       <c r="R159" t="n">
-        <v>6784225</v>
+        <v>6784233</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17686,6 +17686,11 @@
       <c r="AB159" t="inlineStr">
         <is>
           <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Flera bilder på vedsvampar, tallåga</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17712,10 +17717,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127714347</v>
+        <v>127715912</v>
       </c>
       <c r="B160" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17747,10 +17752,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464931</v>
+        <v>464770</v>
       </c>
       <c r="R160" t="n">
-        <v>6784233</v>
+        <v>6784253</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17782,7 +17787,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17792,12 +17797,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Flera bilder på vedsvampar, tallåga</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17824,10 +17824,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127715912</v>
+        <v>127714269</v>
       </c>
       <c r="B161" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17859,10 +17859,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464770</v>
+        <v>464939</v>
       </c>
       <c r="R161" t="n">
-        <v>6784253</v>
+        <v>6784225</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17934,7 +17934,7 @@
         <v>127718380</v>
       </c>
       <c r="B162" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>127719855</v>
       </c>
       <c r="B163" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18145,10 +18145,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127715006</v>
+        <v>127717251</v>
       </c>
       <c r="B164" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18156,42 +18156,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>464844</v>
+        <v>464650</v>
       </c>
       <c r="R164" t="n">
-        <v>6784281</v>
+        <v>6784215</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18231,6 +18226,11 @@
       <c r="AB164" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18257,10 +18257,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127717251</v>
+        <v>127718006</v>
       </c>
       <c r="B165" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18268,21 +18268,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18292,13 +18292,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464650</v>
+        <v>464701</v>
       </c>
       <c r="R165" t="n">
-        <v>6784215</v>
+        <v>6784168</v>
       </c>
       <c r="S165" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>1 bild stubbe med tallar I bakgrund fulla av garn</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18369,10 +18369,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127718006</v>
+        <v>127715006</v>
       </c>
       <c r="B166" t="n">
-        <v>79636</v>
+        <v>57660</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18380,34 +18380,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464701</v>
+        <v>464844</v>
       </c>
       <c r="R166" t="n">
-        <v>6784168</v>
+        <v>6784281</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18450,11 +18455,6 @@
       <c r="AB166" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>1 bild stubbe med tallar I bakgrund fulla av garn</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18481,37 +18481,43 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127719463</v>
+        <v>127719421</v>
       </c>
       <c r="B167" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -18519,10 +18525,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464867</v>
+        <v>464871</v>
       </c>
       <c r="R167" t="n">
-        <v>6784270</v>
+        <v>6784277</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -18559,7 +18565,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På 2 torrtallar, en tallåga</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18587,57 +18593,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127719421</v>
+        <v>127718021</v>
       </c>
       <c r="B168" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>464871</v>
+        <v>464701</v>
       </c>
       <c r="R168" t="n">
-        <v>6784277</v>
+        <v>6784168</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18664,14 +18661,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>På 2 torrtallar, en tallåga</t>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18680,29 +18682,28 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127718352</v>
+        <v>127719463</v>
       </c>
       <c r="B169" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18728,19 +18729,22 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464664</v>
+        <v>464867</v>
       </c>
       <c r="R169" t="n">
-        <v>6784142</v>
+        <v>6784270</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18767,24 +18771,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>2 bilder på kolad stubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18793,28 +18787,29 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127718190</v>
+        <v>127718352</v>
       </c>
       <c r="B170" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18822,21 +18817,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18846,10 +18841,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464678</v>
+        <v>464664</v>
       </c>
       <c r="R170" t="n">
-        <v>6784123</v>
+        <v>6784142</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18892,6 +18887,11 @@
       <c r="AB170" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>2 bilder på kolad stubbe</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18918,10 +18918,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127718021</v>
+        <v>127715519</v>
       </c>
       <c r="B171" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18929,21 +18929,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18953,10 +18953,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464701</v>
+        <v>464800</v>
       </c>
       <c r="R171" t="n">
-        <v>6784168</v>
+        <v>6784210</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19025,10 +19025,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127715684</v>
+        <v>127718190</v>
       </c>
       <c r="B172" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19060,10 +19060,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464800</v>
+        <v>464678</v>
       </c>
       <c r="R172" t="n">
-        <v>6784210</v>
+        <v>6784123</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19132,10 +19132,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127717666</v>
+        <v>127719674</v>
       </c>
       <c r="B173" t="n">
-        <v>79636</v>
+        <v>79052</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,37 +19143,40 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464682</v>
+        <v>464745</v>
       </c>
       <c r="R173" t="n">
-        <v>6784195</v>
+        <v>6784305</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19200,19 +19203,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19221,28 +19219,29 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127719674</v>
+        <v>127719947</v>
       </c>
       <c r="B174" t="n">
-        <v>79050</v>
+        <v>79638</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19250,40 +19249,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>464745</v>
+        <v>464623</v>
       </c>
       <c r="R174" t="n">
-        <v>6784305</v>
+        <v>6784354</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19310,14 +19306,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19326,29 +19327,28 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127719947</v>
+        <v>127717666</v>
       </c>
       <c r="B175" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464623</v>
+        <v>464682</v>
       </c>
       <c r="R175" t="n">
-        <v>6784354</v>
+        <v>6784195</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19452,10 +19452,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127714657</v>
+        <v>127719762</v>
       </c>
       <c r="B176" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19463,37 +19463,40 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464858</v>
+        <v>464798</v>
       </c>
       <c r="R176" t="n">
-        <v>6784259</v>
+        <v>6784237</v>
       </c>
       <c r="S176" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19520,19 +19523,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19541,28 +19539,29 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127719525</v>
+        <v>127714657</v>
       </c>
       <c r="B177" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19570,40 +19569,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464859</v>
+        <v>464858</v>
       </c>
       <c r="R177" t="n">
-        <v>6784218</v>
+        <v>6784259</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19630,14 +19626,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19646,29 +19647,28 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127719762</v>
+        <v>127716564</v>
       </c>
       <c r="B178" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19676,40 +19676,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>464798</v>
+        <v>464727</v>
       </c>
       <c r="R178" t="n">
-        <v>6784237</v>
+        <v>6784316</v>
       </c>
       <c r="S178" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19736,14 +19733,24 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19752,29 +19759,28 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127716564</v>
+        <v>127719525</v>
       </c>
       <c r="B179" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19782,37 +19788,40 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>464727</v>
+        <v>464859</v>
       </c>
       <c r="R179" t="n">
-        <v>6784316</v>
+        <v>6784218</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19839,24 +19848,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19865,18 +19864,19 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -19990,10 +19990,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127718357</v>
+        <v>127718964</v>
       </c>
       <c r="B181" t="n">
-        <v>79607</v>
+        <v>57660</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20001,34 +20001,39 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>464664</v>
+        <v>464628</v>
       </c>
       <c r="R181" t="n">
-        <v>6784142</v>
+        <v>6784279</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20071,6 +20076,11 @@
       <c r="AB181" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>1 bild på stubbe med hål ca 10 cm</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20097,10 +20107,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127718964</v>
+        <v>127719588</v>
       </c>
       <c r="B182" t="n">
-        <v>57658</v>
+        <v>78779</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20108,42 +20118,40 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464628</v>
+        <v>464844</v>
       </c>
       <c r="R182" t="n">
-        <v>6784279</v>
+        <v>6784242</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20170,24 +20178,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>1 bild på stubbe med hål ca 10 cm</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20196,28 +20194,29 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127719588</v>
+        <v>127718357</v>
       </c>
       <c r="B183" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20225,40 +20224,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>464844</v>
+        <v>464664</v>
       </c>
       <c r="R183" t="n">
-        <v>6784242</v>
+        <v>6784142</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20285,14 +20281,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20301,29 +20302,28 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127714380</v>
+        <v>127714909</v>
       </c>
       <c r="B184" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20355,10 +20355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>464913</v>
+        <v>464844</v>
       </c>
       <c r="R184" t="n">
-        <v>6784254</v>
+        <v>6784281</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20400,12 +20400,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>1 bild, myrstack</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20432,10 +20427,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127714909</v>
+        <v>127718026</v>
       </c>
       <c r="B185" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20467,10 +20462,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>464844</v>
+        <v>464701</v>
       </c>
       <c r="R185" t="n">
-        <v>6784281</v>
+        <v>6784168</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20539,10 +20534,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127718026</v>
+        <v>127714380</v>
       </c>
       <c r="B186" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20574,10 +20569,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>464701</v>
+        <v>464913</v>
       </c>
       <c r="R186" t="n">
-        <v>6784168</v>
+        <v>6784254</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20609,7 +20604,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20619,7 +20614,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>1 bild, myrstack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20649,7 +20649,7 @@
         <v>127720039</v>
       </c>
       <c r="B187" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20758,10 +20758,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127714955</v>
+        <v>127716661</v>
       </c>
       <c r="B188" t="n">
-        <v>78777</v>
+        <v>57660</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20769,34 +20769,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R188" t="n">
-        <v>6784281</v>
+        <v>6784275</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20865,10 +20870,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127715185</v>
+        <v>127720341</v>
       </c>
       <c r="B189" t="n">
-        <v>79607</v>
+        <v>79020</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20876,21 +20881,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20900,13 +20905,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>464836</v>
+        <v>464568</v>
       </c>
       <c r="R189" t="n">
-        <v>6784199</v>
+        <v>6784376</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20946,6 +20951,11 @@
       <c r="AB189" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20972,10 +20982,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127716661</v>
+        <v>127719613</v>
       </c>
       <c r="B190" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20983,42 +20993,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464710</v>
+        <v>464669</v>
       </c>
       <c r="R190" t="n">
-        <v>6784275</v>
+        <v>6784345</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21058,6 +21063,11 @@
       <c r="AB190" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder, första med lutande tall</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21084,10 +21094,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719613</v>
+        <v>127714955</v>
       </c>
       <c r="B191" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21095,21 +21105,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21119,13 +21129,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464669</v>
+        <v>464844</v>
       </c>
       <c r="R191" t="n">
-        <v>6784345</v>
+        <v>6784281</v>
       </c>
       <c r="S191" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21165,11 +21175,6 @@
       <c r="AB191" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder, första med lutande tall</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21196,10 +21201,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127720341</v>
+        <v>127715185</v>
       </c>
       <c r="B192" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21207,21 +21212,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21231,13 +21236,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464568</v>
+        <v>464836</v>
       </c>
       <c r="R192" t="n">
-        <v>6784376</v>
+        <v>6784199</v>
       </c>
       <c r="S192" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21277,11 +21282,6 @@
       <c r="AB192" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21311,7 +21311,7 @@
         <v>127719544</v>
       </c>
       <c r="B193" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21420,10 +21420,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127718375</v>
+        <v>127719315</v>
       </c>
       <c r="B194" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21431,21 +21431,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21455,13 +21455,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464664</v>
+        <v>464650</v>
       </c>
       <c r="R194" t="n">
-        <v>6784142</v>
+        <v>6784317</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21501,6 +21501,11 @@
       <c r="AB194" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21527,10 +21532,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127717659</v>
+        <v>127718375</v>
       </c>
       <c r="B195" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21538,21 +21543,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21562,10 +21567,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464682</v>
+        <v>464664</v>
       </c>
       <c r="R195" t="n">
-        <v>6784195</v>
+        <v>6784142</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21608,11 +21613,6 @@
       <c r="AB195" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 bilder på 2 stubbar</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21639,10 +21639,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127718015</v>
+        <v>127719813</v>
       </c>
       <c r="B196" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21650,21 +21650,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21674,10 +21674,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464701</v>
+        <v>464647</v>
       </c>
       <c r="R196" t="n">
-        <v>6784168</v>
+        <v>6784377</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21746,51 +21746,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127719816</v>
+        <v>127720766</v>
       </c>
       <c r="B197" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>464752</v>
+        <v>464581</v>
       </c>
       <c r="R197" t="n">
-        <v>6784264</v>
+        <v>6784393</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21817,14 +21814,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21833,29 +21835,28 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127719813</v>
+        <v>127718015</v>
       </c>
       <c r="B198" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21863,21 +21864,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21887,10 +21888,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>464647</v>
+        <v>464701</v>
       </c>
       <c r="R198" t="n">
-        <v>6784377</v>
+        <v>6784168</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21959,10 +21960,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127719315</v>
+        <v>127717659</v>
       </c>
       <c r="B199" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21970,21 +21971,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21994,13 +21995,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>464650</v>
+        <v>464682</v>
       </c>
       <c r="R199" t="n">
-        <v>6784317</v>
+        <v>6784195</v>
       </c>
       <c r="S199" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22044,7 +22045,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
+          <t>2 bilder på 2 stubbar</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22071,10 +22072,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127719841</v>
+        <v>127719816</v>
       </c>
       <c r="B200" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22100,19 +22101,22 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464647</v>
+        <v>464752</v>
       </c>
       <c r="R200" t="n">
-        <v>6784377</v>
+        <v>6784264</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22139,19 +22143,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22160,50 +22159,51 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127720766</v>
+        <v>127719841</v>
       </c>
       <c r="B201" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22213,10 +22213,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464581</v>
+        <v>464647</v>
       </c>
       <c r="R201" t="n">
-        <v>6784393</v>
+        <v>6784377</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22285,10 +22285,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127718840</v>
+        <v>127717010</v>
       </c>
       <c r="B202" t="n">
-        <v>57821</v>
+        <v>78779</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22296,42 +22296,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464588</v>
+        <v>464680</v>
       </c>
       <c r="R202" t="n">
-        <v>6784281</v>
+        <v>6784254</v>
       </c>
       <c r="S202" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22371,6 +22366,11 @@
       <c r="AB202" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>1 Bild på stubbe med garn i bakgrund på tall</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22397,10 +22397,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127714169</v>
+        <v>127718616</v>
       </c>
       <c r="B203" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464951</v>
+        <v>464618</v>
       </c>
       <c r="R203" t="n">
         <v>6784236</v>
@@ -22467,7 +22467,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22477,7 +22477,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22504,10 +22509,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127718616</v>
+        <v>127714169</v>
       </c>
       <c r="B204" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22539,7 +22544,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>464618</v>
+        <v>464951</v>
       </c>
       <c r="R204" t="n">
         <v>6784236</v>
@@ -22574,7 +22579,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22584,12 +22589,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22616,10 +22616,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127717010</v>
+        <v>127716791</v>
       </c>
       <c r="B205" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22627,21 +22627,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22651,13 +22651,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>464680</v>
+        <v>464667</v>
       </c>
       <c r="R205" t="n">
-        <v>6784254</v>
+        <v>6784294</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>1 Bild på stubbe med garn i bakgrund på tall</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22728,10 +22728,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127716791</v>
+        <v>127718840</v>
       </c>
       <c r="B206" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22739,34 +22739,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>464667</v>
+        <v>464588</v>
       </c>
       <c r="R206" t="n">
-        <v>6784294</v>
+        <v>6784281</v>
       </c>
       <c r="S206" t="n">
         <v>50</v>
@@ -22809,11 +22814,6 @@
       <c r="AB206" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22840,57 +22840,48 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127719338</v>
+        <v>127716476</v>
       </c>
       <c r="B207" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>464893</v>
+        <v>464774</v>
       </c>
       <c r="R207" t="n">
-        <v>6784258</v>
+        <v>6784282</v>
       </c>
       <c r="S207" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22917,40 +22908,54 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+        </is>
+      </c>
       <c r="AD207" t="b">
         <v>0</v>
       </c>
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127719298</v>
+        <v>127719838</v>
       </c>
       <c r="B208" t="n">
-        <v>57658</v>
+        <v>78779</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22958,45 +22963,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>464943</v>
+        <v>464647</v>
       </c>
       <c r="R208" t="n">
-        <v>6784241</v>
+        <v>6784377</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23023,9 +23020,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23040,22 +23047,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127716476</v>
+        <v>127719298</v>
       </c>
       <c r="B209" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23063,37 +23070,45 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>464774</v>
+        <v>464943</v>
       </c>
       <c r="R209" t="n">
-        <v>6784282</v>
+        <v>6784241</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23120,24 +23135,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23152,12 +23152,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
         <v>127718884</v>
       </c>
       <c r="B210" t="n">
-        <v>57788</v>
+        <v>57790</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23276,48 +23276,57 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127719838</v>
+        <v>127719338</v>
       </c>
       <c r="B211" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>464647</v>
+        <v>464893</v>
       </c>
       <c r="R211" t="n">
-        <v>6784377</v>
+        <v>6784258</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23344,39 +23353,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
@@ -23386,7 +23386,7 @@
         <v>127715270</v>
       </c>
       <c r="B212" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23603,10 +23603,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127715332</v>
+        <v>127719810</v>
       </c>
       <c r="B214" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23614,21 +23614,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23638,10 +23638,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>464836</v>
+        <v>464647</v>
       </c>
       <c r="R214" t="n">
-        <v>6784193</v>
+        <v>6784377</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23684,6 +23684,11 @@
       <c r="AB214" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23710,10 +23715,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127714858</v>
+        <v>127718968</v>
       </c>
       <c r="B215" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23721,21 +23726,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23745,10 +23750,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>464856</v>
+        <v>464628</v>
       </c>
       <c r="R215" t="n">
-        <v>6784268</v>
+        <v>6784279</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23791,11 +23796,6 @@
       <c r="AB215" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23822,10 +23822,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127716937</v>
+        <v>127719747</v>
       </c>
       <c r="B216" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23833,37 +23833,40 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>464680</v>
+        <v>464834</v>
       </c>
       <c r="R216" t="n">
-        <v>6784254</v>
+        <v>6784187</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23890,24 +23893,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23916,18 +23909,19 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
@@ -23937,7 +23931,7 @@
         <v>127716097</v>
       </c>
       <c r="B217" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24041,10 +24035,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127718968</v>
+        <v>127714858</v>
       </c>
       <c r="B218" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24052,21 +24046,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24076,10 +24070,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>464628</v>
+        <v>464856</v>
       </c>
       <c r="R218" t="n">
-        <v>6784279</v>
+        <v>6784268</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24122,6 +24116,11 @@
       <c r="AB218" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24148,10 +24147,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127719810</v>
+        <v>127716937</v>
       </c>
       <c r="B219" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24159,21 +24158,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24183,10 +24182,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>464647</v>
+        <v>464680</v>
       </c>
       <c r="R219" t="n">
-        <v>6784377</v>
+        <v>6784254</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24233,7 +24232,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24260,10 +24259,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127719747</v>
+        <v>127715332</v>
       </c>
       <c r="B220" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24271,40 +24270,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>464834</v>
+        <v>464836</v>
       </c>
       <c r="R220" t="n">
-        <v>6784187</v>
+        <v>6784193</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24331,14 +24327,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24347,19 +24348,18 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -24369,7 +24369,7 @@
         <v>127719877</v>
       </c>
       <c r="B221" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>127719836</v>
       </c>
       <c r="B222" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24573,32 +24573,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127721018</v>
+        <v>127717066</v>
       </c>
       <c r="B223" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24608,10 +24608,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>464816</v>
+        <v>464671</v>
       </c>
       <c r="R223" t="n">
-        <v>6784317</v>
+        <v>6784233</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24654,6 +24654,11 @@
       <c r="AB223" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>2 bilder på vedsvamp, tall</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24680,32 +24685,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127717066</v>
+        <v>127721018</v>
       </c>
       <c r="B224" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24715,10 +24720,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464671</v>
+        <v>464816</v>
       </c>
       <c r="R224" t="n">
-        <v>6784233</v>
+        <v>6784317</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24761,11 +24766,6 @@
       <c r="AB224" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>2 bilder på vedsvamp, tall</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24795,7 +24795,7 @@
         <v>127719210</v>
       </c>
       <c r="B225" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24898,10 +24898,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127717016</v>
+        <v>127717085</v>
       </c>
       <c r="B226" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24909,34 +24909,39 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464672</v>
+        <v>464671</v>
       </c>
       <c r="R226" t="n">
-        <v>6784257</v>
+        <v>6784233</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25005,10 +25010,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127717085</v>
+        <v>127719863</v>
       </c>
       <c r="B227" t="n">
-        <v>57821</v>
+        <v>91352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25016,42 +25021,40 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464671</v>
+        <v>464688</v>
       </c>
       <c r="R227" t="n">
-        <v>6784233</v>
+        <v>6784295</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25078,49 +25081,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD227" t="b">
         <v>0</v>
       </c>
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127719942</v>
+        <v>127717016</v>
       </c>
       <c r="B228" t="n">
-        <v>79607</v>
+        <v>79020</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25128,21 +25122,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25152,10 +25146,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>464623</v>
+        <v>464672</v>
       </c>
       <c r="R228" t="n">
-        <v>6784354</v>
+        <v>6784257</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25198,11 +25192,6 @@
       <c r="AB228" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>1 Bild på kolad stubbe</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25229,10 +25218,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127719863</v>
+        <v>127719942</v>
       </c>
       <c r="B229" t="n">
-        <v>91350</v>
+        <v>79609</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25240,40 +25229,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>464688</v>
+        <v>464623</v>
       </c>
       <c r="R229" t="n">
-        <v>6784295</v>
+        <v>6784354</v>
       </c>
       <c r="S229" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25300,30 +25286,44 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>1 Bild på kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD229" t="b">
         <v>0</v>
       </c>
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
         <v>127714717</v>
       </c>
       <c r="B230" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127505584</v>
+        <v>127601236</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464920</v>
+        <v>464862</v>
       </c>
       <c r="R5" t="n">
-        <v>6784591</v>
+        <v>6784534</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,19 +1067,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,28 +1083,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127503663</v>
+        <v>127602494</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1113,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464847</v>
+        <v>464821</v>
       </c>
       <c r="R6" t="n">
-        <v>6784531</v>
+        <v>6784490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1173,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,25 +1189,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127536063</v>
+        <v>127566254</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1245,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464819</v>
+        <v>464782</v>
       </c>
       <c r="R7" t="n">
-        <v>6784639</v>
+        <v>6784529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127566254</v>
+        <v>127505584</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1352,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464782</v>
+        <v>464920</v>
       </c>
       <c r="R8" t="n">
-        <v>6784529</v>
+        <v>6784591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,40 +1433,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R9" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,14 +1490,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,29 +1511,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,40 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R10" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,14 +1597,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,19 +1618,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127524724</v>
+        <v>127580771</v>
       </c>
       <c r="B18" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464825</v>
+        <v>464785</v>
       </c>
       <c r="R18" t="n">
-        <v>6784652</v>
+        <v>6784477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127503116</v>
+        <v>127524724</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464870</v>
+        <v>464825</v>
       </c>
       <c r="R19" t="n">
-        <v>6784516</v>
+        <v>6784652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127602544</v>
+        <v>127503116</v>
       </c>
       <c r="B20" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,40 +2619,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464858</v>
+        <v>464870</v>
       </c>
       <c r="R20" t="n">
-        <v>6784447</v>
+        <v>6784516</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2679,14 +2676,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,67 +2697,75 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127580771</v>
+        <v>127602573</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464785</v>
+        <v>464867</v>
       </c>
       <c r="R21" t="n">
-        <v>6784477</v>
+        <v>6784461</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2782,19 +2792,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,61 +2808,56 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127602573</v>
+        <v>127602544</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464867</v>
+        <v>464858</v>
       </c>
       <c r="R22" t="n">
-        <v>6784461</v>
+        <v>6784447</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127502954</v>
+        <v>127547132</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464884</v>
+        <v>464846</v>
       </c>
       <c r="R23" t="n">
-        <v>6784499</v>
+        <v>6784631</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127547132</v>
+        <v>127537979</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464846</v>
+        <v>464830</v>
       </c>
       <c r="R24" t="n">
-        <v>6784631</v>
+        <v>6784627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127537979</v>
+        <v>127502954</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464830</v>
+        <v>464884</v>
       </c>
       <c r="R25" t="n">
-        <v>6784627</v>
+        <v>6784499</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127602770</v>
+        <v>127567350</v>
       </c>
       <c r="B33" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,40 +4018,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464833</v>
+        <v>464790</v>
       </c>
       <c r="R33" t="n">
-        <v>6784487</v>
+        <v>6784508</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4078,14 +4075,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,26 +4096,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B34" t="n">
         <v>79052</v>
@@ -4151,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R34" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4219,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127567350</v>
+        <v>127602073</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4230,37 +4231,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464790</v>
+        <v>464813</v>
       </c>
       <c r="R35" t="n">
-        <v>6784508</v>
+        <v>6784586</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4287,19 +4291,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4308,18 +4307,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4752,37 +4752,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127601608</v>
+        <v>127601723</v>
       </c>
       <c r="B40" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4790,10 +4796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464891</v>
+        <v>464899</v>
       </c>
       <c r="R40" t="n">
-        <v>6784591</v>
+        <v>6784610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4836,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,43 +4864,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127601723</v>
+        <v>127601608</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464899</v>
+        <v>464891</v>
       </c>
       <c r="R41" t="n">
-        <v>6784610</v>
+        <v>6784591</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -14920,7 +14920,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127714234</v>
+        <v>127721029</v>
       </c>
       <c r="B135" t="n">
         <v>79020</v>
@@ -14955,13 +14955,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464936</v>
+        <v>464816</v>
       </c>
       <c r="R135" t="n">
-        <v>6784248</v>
+        <v>6784317</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15027,7 +15027,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127715198</v>
+        <v>127714234</v>
       </c>
       <c r="B136" t="n">
         <v>79020</v>
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464836</v>
+        <v>464936</v>
       </c>
       <c r="R136" t="n">
-        <v>6784199</v>
+        <v>6784248</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15134,7 +15134,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127721029</v>
+        <v>127715198</v>
       </c>
       <c r="B137" t="n">
         <v>79020</v>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464816</v>
+        <v>464836</v>
       </c>
       <c r="R137" t="n">
-        <v>6784317</v>
+        <v>6784199</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15241,32 +15241,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127718498</v>
+        <v>127720285</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15276,13 +15276,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464686</v>
+        <v>464564</v>
       </c>
       <c r="R138" t="n">
-        <v>6784147</v>
+        <v>6784324</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15322,6 +15322,11 @@
       <c r="AB138" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15348,10 +15353,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127720285</v>
+        <v>127719564</v>
       </c>
       <c r="B139" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15359,37 +15364,40 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464564</v>
+        <v>464859</v>
       </c>
       <c r="R139" t="n">
-        <v>6784324</v>
+        <v>6784218</v>
       </c>
       <c r="S139" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15416,24 +15424,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15442,69 +15440,67 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127719564</v>
+        <v>127718498</v>
       </c>
       <c r="B140" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464859</v>
+        <v>464686</v>
       </c>
       <c r="R140" t="n">
-        <v>6784218</v>
+        <v>6784147</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15531,14 +15527,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15547,19 +15548,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -17294,7 +17294,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127719947</v>
+        <v>127717666</v>
       </c>
       <c r="B157" t="n">
         <v>79638</v>
@@ -17329,10 +17329,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464623</v>
+        <v>464682</v>
       </c>
       <c r="R157" t="n">
-        <v>6784354</v>
+        <v>6784195</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17401,7 +17401,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127717666</v>
+        <v>127719947</v>
       </c>
       <c r="B158" t="n">
         <v>79638</v>
@@ -17436,10 +17436,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464682</v>
+        <v>464623</v>
       </c>
       <c r="R158" t="n">
-        <v>6784195</v>
+        <v>6784354</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19547,10 +19547,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127718840</v>
+        <v>127714169</v>
       </c>
       <c r="B178" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19558,42 +19558,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>464588</v>
+        <v>464951</v>
       </c>
       <c r="R178" t="n">
-        <v>6784281</v>
+        <v>6784236</v>
       </c>
       <c r="S178" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19622,7 +19617,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19632,7 +19627,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19659,10 +19654,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127714169</v>
+        <v>127718840</v>
       </c>
       <c r="B179" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19670,37 +19665,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>464951</v>
+        <v>464588</v>
       </c>
       <c r="R179" t="n">
-        <v>6784236</v>
+        <v>6784281</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19766,48 +19766,57 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127719838</v>
+        <v>127719338</v>
       </c>
       <c r="B180" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>464647</v>
+        <v>464893</v>
       </c>
       <c r="R180" t="n">
-        <v>6784377</v>
+        <v>6784258</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19834,96 +19843,83 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127719338</v>
+        <v>127718884</v>
       </c>
       <c r="B181" t="n">
-        <v>8450</v>
+        <v>57790</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>106545</v>
+        <v>103035</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>464893</v>
+        <v>464607</v>
       </c>
       <c r="R181" t="n">
-        <v>6784258</v>
+        <v>6784297</v>
       </c>
       <c r="S181" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19950,40 +19946,49 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127718884</v>
+        <v>127719838</v>
       </c>
       <c r="B182" t="n">
-        <v>57790</v>
+        <v>78779</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19991,42 +19996,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>103035</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464607</v>
+        <v>464647</v>
       </c>
       <c r="R182" t="n">
-        <v>6784297</v>
+        <v>6784377</v>
       </c>
       <c r="S182" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20844,10 +20844,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127719877</v>
+        <v>127719836</v>
       </c>
       <c r="B190" t="n">
-        <v>91352</v>
+        <v>79609</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20855,21 +20855,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464667</v>
+        <v>464715</v>
       </c>
       <c r="R190" t="n">
-        <v>6784226</v>
+        <v>6784291</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -20918,6 +20918,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20945,10 +20950,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719836</v>
+        <v>127719877</v>
       </c>
       <c r="B191" t="n">
-        <v>79609</v>
+        <v>91352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20956,21 +20961,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20983,10 +20988,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464715</v>
+        <v>464667</v>
       </c>
       <c r="R191" t="n">
-        <v>6784291</v>
+        <v>6784226</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21019,11 +21024,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21051,32 +21051,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127714444</v>
+        <v>127721018</v>
       </c>
       <c r="B192" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464913</v>
+        <v>464816</v>
       </c>
       <c r="R192" t="n">
-        <v>6784254</v>
+        <v>6784317</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21158,10 +21158,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127717898</v>
+        <v>127714444</v>
       </c>
       <c r="B193" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21169,21 +21169,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21193,10 +21193,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464701</v>
+        <v>464913</v>
       </c>
       <c r="R193" t="n">
-        <v>6784168</v>
+        <v>6784254</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21265,10 +21265,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127719210</v>
+        <v>127717898</v>
       </c>
       <c r="B194" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21276,40 +21276,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464941</v>
+        <v>464701</v>
       </c>
       <c r="R194" t="n">
-        <v>6784243</v>
+        <v>6784168</v>
       </c>
       <c r="S194" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21336,14 +21333,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21352,67 +21354,69 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127721018</v>
+        <v>127719210</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464816</v>
+        <v>464941</v>
       </c>
       <c r="R195" t="n">
-        <v>6784317</v>
+        <v>6784243</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21439,19 +21443,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21460,18 +21459,19 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -24172,10 +24172,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127716476</v>
+        <v>127707455</v>
       </c>
       <c r="B220" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24183,37 +24183,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>464774</v>
+        <v>464669</v>
       </c>
       <c r="R220" t="n">
-        <v>6784282</v>
+        <v>6784449</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24240,27 +24242,27 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24269,7 +24271,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24288,50 +24289,53 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127707455</v>
+        <v>127707530</v>
       </c>
       <c r="B221" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>464669</v>
+        <v>464686</v>
       </c>
       <c r="R221" t="n">
-        <v>6784449</v>
+        <v>6784430</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24378,7 +24382,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Spillning under tall med en vit påläggning på stammen</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24405,42 +24409,37 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127707530</v>
+        <v>127716476</v>
       </c>
       <c r="B222" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
@@ -24448,10 +24447,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464686</v>
+        <v>464774</v>
       </c>
       <c r="R222" t="n">
-        <v>6784430</v>
+        <v>6784282</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24478,27 +24477,27 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Spillning under tall med en vit påläggning på stammen</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24507,6 +24506,7 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY231"/>
+  <dimension ref="A1:AY232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127601236</v>
+        <v>127505584</v>
       </c>
       <c r="B5" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,40 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464862</v>
+        <v>464920</v>
       </c>
       <c r="R5" t="n">
-        <v>6784534</v>
+        <v>6784591</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,14 +1064,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,29 +1085,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127602494</v>
+        <v>127503663</v>
       </c>
       <c r="B6" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464821</v>
+        <v>464847</v>
       </c>
       <c r="R6" t="n">
-        <v>6784490</v>
+        <v>6784531</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,14 +1171,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,26 +1192,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127566254</v>
+        <v>127536063</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1243,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464782</v>
+        <v>464819</v>
       </c>
       <c r="R7" t="n">
-        <v>6784529</v>
+        <v>6784639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127505584</v>
+        <v>127601236</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,37 +1328,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464920</v>
+        <v>464862</v>
       </c>
       <c r="R8" t="n">
-        <v>6784591</v>
+        <v>6784534</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,19 +1388,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,28 +1404,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127503663</v>
+        <v>127602494</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,37 +1434,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464847</v>
+        <v>464821</v>
       </c>
       <c r="R9" t="n">
-        <v>6784531</v>
+        <v>6784490</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,19 +1494,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,25 +1510,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127536063</v>
+        <v>127566254</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464819</v>
+        <v>464782</v>
       </c>
       <c r="R10" t="n">
-        <v>6784639</v>
+        <v>6784529</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127504284</v>
+        <v>127581242</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464840</v>
+        <v>464794</v>
       </c>
       <c r="R14" t="n">
-        <v>6784571</v>
+        <v>6784479</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,11 +2037,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,53 +2063,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127503447</v>
+        <v>127585141</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464865</v>
+        <v>464827</v>
       </c>
       <c r="R15" t="n">
-        <v>6784539</v>
+        <v>6784453</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,7 +2170,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127581092</v>
+        <v>127504284</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2215,13 +2205,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464794</v>
+        <v>464840</v>
       </c>
       <c r="R16" t="n">
-        <v>6784479</v>
+        <v>6784571</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2261,6 +2251,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,48 +2282,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127585141</v>
+        <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464827</v>
+        <v>464865</v>
       </c>
       <c r="R17" t="n">
-        <v>6784453</v>
+        <v>6784539</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127547132</v>
+        <v>127502954</v>
       </c>
       <c r="B23" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464846</v>
+        <v>464884</v>
       </c>
       <c r="R23" t="n">
-        <v>6784631</v>
+        <v>6784499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127537979</v>
+        <v>127547132</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464830</v>
+        <v>464846</v>
       </c>
       <c r="R24" t="n">
-        <v>6784627</v>
+        <v>6784631</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127502954</v>
+        <v>127537979</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464884</v>
+        <v>464830</v>
       </c>
       <c r="R25" t="n">
-        <v>6784499</v>
+        <v>6784627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B27" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R28" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127503065</v>
+        <v>127580438</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464885</v>
+        <v>464780</v>
       </c>
       <c r="R29" t="n">
-        <v>6784500</v>
+        <v>6784485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,11 +3656,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3687,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127503208</v>
+        <v>127503065</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464880</v>
+        <v>464885</v>
       </c>
       <c r="R30" t="n">
-        <v>6784522</v>
+        <v>6784500</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,6 +3763,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,7 +3794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127580438</v>
+        <v>127503208</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464780</v>
+        <v>464880</v>
       </c>
       <c r="R31" t="n">
-        <v>6784485</v>
+        <v>6784522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R36" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R37" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4752,43 +4752,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127601723</v>
+        <v>127601608</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4796,10 +4790,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464899</v>
+        <v>464891</v>
       </c>
       <c r="R40" t="n">
-        <v>6784610</v>
+        <v>6784591</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4836,7 +4830,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På en torrtall</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4864,37 +4858,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127601608</v>
+        <v>127601723</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464891</v>
+        <v>464899</v>
       </c>
       <c r="R41" t="n">
-        <v>6784591</v>
+        <v>6784610</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4970,7 +4970,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127582358</v>
+        <v>127580584</v>
       </c>
       <c r="B42" t="n">
         <v>79020</v>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464803</v>
+        <v>464783</v>
       </c>
       <c r="R42" t="n">
-        <v>6784481</v>
+        <v>6784477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127580584</v>
+        <v>127582358</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464783</v>
+        <v>464803</v>
       </c>
       <c r="R43" t="n">
-        <v>6784477</v>
+        <v>6784481</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127507819</v>
+        <v>127602418</v>
       </c>
       <c r="B45" t="n">
-        <v>75144</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,37 +5301,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464858</v>
+        <v>464873</v>
       </c>
       <c r="R45" t="n">
-        <v>6784650</v>
+        <v>6784704</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5358,19 +5361,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5379,28 +5377,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127539258</v>
+        <v>127507819</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5407,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464840</v>
+        <v>464858</v>
       </c>
       <c r="R46" t="n">
-        <v>6784645</v>
+        <v>6784650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127602418</v>
+        <v>127539258</v>
       </c>
       <c r="B47" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,40 +5514,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464873</v>
+        <v>464840</v>
       </c>
       <c r="R47" t="n">
-        <v>6784704</v>
+        <v>6784645</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5575,14 +5571,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5591,19 +5592,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627035</v>
+        <v>127627017</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464881</v>
+        <v>464871</v>
       </c>
       <c r="R66" t="n">
-        <v>6784597</v>
+        <v>6784599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7592,7 +7592,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627017</v>
+        <v>127627035</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464871</v>
+        <v>464881</v>
       </c>
       <c r="R67" t="n">
-        <v>6784599</v>
+        <v>6784597</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B68" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,21 +7704,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,6 +7769,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7794,10 +7799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7805,21 +7810,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7870,11 +7875,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8112,7 +8112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627174</v>
+        <v>127627007</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464796</v>
+        <v>464841</v>
       </c>
       <c r="R72" t="n">
-        <v>6784631</v>
+        <v>6784612</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,6 +8186,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,7 +8218,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B73" t="n">
         <v>79020</v>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R73" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,11 +8292,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -11034,7 +11034,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B99" t="n">
         <v>79020</v>
@@ -11063,16 +11063,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R99" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11119,7 +11122,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11128,6 +11131,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11146,7 +11150,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B100" t="n">
         <v>79020</v>
@@ -11175,19 +11179,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R100" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11234,7 +11235,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Miljöbilder för området, rikligt med garnlav</t>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11243,7 +11244,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11369,7 +11369,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127707616</v>
+        <v>127706377</v>
       </c>
       <c r="B102" t="n">
         <v>79020</v>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464701</v>
+        <v>464687</v>
       </c>
       <c r="R102" t="n">
-        <v>6784412</v>
+        <v>6784448</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706377</v>
+        <v>127707616</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464687</v>
+        <v>464701</v>
       </c>
       <c r="R104" t="n">
-        <v>6784448</v>
+        <v>6784412</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11797,7 +11797,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127707823</v>
+        <v>127707829</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127706073</v>
+        <v>127707041</v>
       </c>
       <c r="B115" t="n">
-        <v>57660</v>
+        <v>79609</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12771,39 +12771,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464701</v>
+        <v>464666</v>
       </c>
       <c r="R115" t="n">
-        <v>6784425</v>
+        <v>6784496</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12846,11 +12841,6 @@
       <c r="AB115" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12877,10 +12867,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127707041</v>
+        <v>127706073</v>
       </c>
       <c r="B116" t="n">
-        <v>79609</v>
+        <v>57660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12888,34 +12878,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464666</v>
+        <v>464701</v>
       </c>
       <c r="R116" t="n">
-        <v>6784496</v>
+        <v>6784425</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12958,6 +12953,11 @@
       <c r="AB116" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12984,10 +12984,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127705869</v>
+        <v>127706768</v>
       </c>
       <c r="B117" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12995,39 +12995,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464736</v>
+        <v>464683</v>
       </c>
       <c r="R117" t="n">
-        <v>6784473</v>
+        <v>6784461</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13096,10 +13091,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127706768</v>
+        <v>127705869</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13107,34 +13102,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464683</v>
+        <v>464736</v>
       </c>
       <c r="R118" t="n">
-        <v>6784461</v>
+        <v>6784473</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13957,7 +13957,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127707123</v>
+        <v>127707368</v>
       </c>
       <c r="B126" t="n">
         <v>79020</v>
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464660</v>
+        <v>464658</v>
       </c>
       <c r="R126" t="n">
-        <v>6784477</v>
+        <v>6784455</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127705062</v>
+        <v>127707123</v>
       </c>
       <c r="B127" t="n">
         <v>79020</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464888</v>
+        <v>464660</v>
       </c>
       <c r="R127" t="n">
-        <v>6784446</v>
+        <v>6784477</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14171,7 +14171,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127707368</v>
+        <v>127705062</v>
       </c>
       <c r="B128" t="n">
         <v>79020</v>
@@ -14206,10 +14206,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464658</v>
+        <v>464888</v>
       </c>
       <c r="R128" t="n">
-        <v>6784455</v>
+        <v>6784446</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14599,32 +14599,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127706356</v>
+        <v>127707939</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14634,10 +14634,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464687</v>
+        <v>464707</v>
       </c>
       <c r="R132" t="n">
-        <v>6784448</v>
+        <v>6784355</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14706,32 +14706,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127707939</v>
+        <v>127706356</v>
       </c>
       <c r="B133" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14741,10 +14741,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464707</v>
+        <v>464687</v>
       </c>
       <c r="R133" t="n">
-        <v>6784355</v>
+        <v>6784448</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14813,7 +14813,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127715439</v>
+        <v>127715198</v>
       </c>
       <c r="B134" t="n">
         <v>79020</v>
@@ -14848,10 +14848,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464832</v>
+        <v>464836</v>
       </c>
       <c r="R134" t="n">
-        <v>6784214</v>
+        <v>6784199</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14920,32 +14920,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127721029</v>
+        <v>127718498</v>
       </c>
       <c r="B135" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14955,13 +14955,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464816</v>
+        <v>464686</v>
       </c>
       <c r="R135" t="n">
-        <v>6784317</v>
+        <v>6784147</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15027,10 +15027,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127714234</v>
+        <v>127719564</v>
       </c>
       <c r="B136" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15038,37 +15038,40 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464936</v>
+        <v>464859</v>
       </c>
       <c r="R136" t="n">
-        <v>6784248</v>
+        <v>6784218</v>
       </c>
       <c r="S136" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15095,19 +15098,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15116,25 +15114,26 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127715198</v>
+        <v>127721029</v>
       </c>
       <c r="B137" t="n">
         <v>79020</v>
@@ -15169,10 +15168,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464836</v>
+        <v>464816</v>
       </c>
       <c r="R137" t="n">
-        <v>6784199</v>
+        <v>6784317</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15241,7 +15240,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127720285</v>
+        <v>127715439</v>
       </c>
       <c r="B138" t="n">
         <v>79020</v>
@@ -15276,13 +15275,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464564</v>
+        <v>464832</v>
       </c>
       <c r="R138" t="n">
-        <v>6784324</v>
+        <v>6784214</v>
       </c>
       <c r="S138" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15322,11 +15321,6 @@
       <c r="AB138" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15353,10 +15347,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127719564</v>
+        <v>127714234</v>
       </c>
       <c r="B139" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15364,40 +15358,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464859</v>
+        <v>464936</v>
       </c>
       <c r="R139" t="n">
-        <v>6784218</v>
+        <v>6784248</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15424,14 +15415,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15440,51 +15436,50 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127718498</v>
+        <v>127720285</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15494,13 +15489,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464686</v>
+        <v>464564</v>
       </c>
       <c r="R140" t="n">
-        <v>6784147</v>
+        <v>6784324</v>
       </c>
       <c r="S140" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15540,6 +15535,11 @@
       <c r="AB140" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15673,7 +15673,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127718502</v>
+        <v>127715717</v>
       </c>
       <c r="B142" t="n">
         <v>79020</v>
@@ -15708,13 +15708,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464686</v>
+        <v>464788</v>
       </c>
       <c r="R142" t="n">
-        <v>6784147</v>
+        <v>6784220</v>
       </c>
       <c r="S142" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127715717</v>
+        <v>127718502</v>
       </c>
       <c r="B143" t="n">
         <v>79020</v>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464788</v>
+        <v>464686</v>
       </c>
       <c r="R143" t="n">
-        <v>6784220</v>
+        <v>6784147</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15887,10 +15887,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127719621</v>
+        <v>127719996</v>
       </c>
       <c r="B144" t="n">
-        <v>78779</v>
+        <v>57823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15898,40 +15898,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464775</v>
+        <v>464615</v>
       </c>
       <c r="R144" t="n">
-        <v>6784302</v>
+        <v>6784345</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15958,14 +15964,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15974,29 +15985,28 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127719996</v>
+        <v>127719621</v>
       </c>
       <c r="B145" t="n">
-        <v>57823</v>
+        <v>78779</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16004,46 +16014,40 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464615</v>
+        <v>464775</v>
       </c>
       <c r="R145" t="n">
-        <v>6784345</v>
+        <v>6784302</v>
       </c>
       <c r="S145" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16070,19 +16074,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16091,18 +16090,19 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127718380</v>
+        <v>127714269</v>
       </c>
       <c r="B147" t="n">
         <v>79020</v>
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464664</v>
+        <v>464939</v>
       </c>
       <c r="R147" t="n">
-        <v>6784142</v>
+        <v>6784225</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16323,7 +16323,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127714269</v>
+        <v>127718380</v>
       </c>
       <c r="B148" t="n">
         <v>79020</v>
@@ -16358,10 +16358,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464939</v>
+        <v>464664</v>
       </c>
       <c r="R148" t="n">
-        <v>6784225</v>
+        <v>6784142</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16975,7 +16975,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127718021</v>
+        <v>127719463</v>
       </c>
       <c r="B154" t="n">
         <v>78779</v>
@@ -17004,19 +17004,22 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464701</v>
+        <v>464867</v>
       </c>
       <c r="R154" t="n">
-        <v>6784168</v>
+        <v>6784270</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17043,19 +17046,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17064,25 +17062,26 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127719463</v>
+        <v>127718021</v>
       </c>
       <c r="B155" t="n">
         <v>78779</v>
@@ -17111,22 +17110,19 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464867</v>
+        <v>464701</v>
       </c>
       <c r="R155" t="n">
-        <v>6784270</v>
+        <v>6784168</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17153,14 +17149,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17169,29 +17170,28 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719674</v>
+        <v>127719947</v>
       </c>
       <c r="B156" t="n">
-        <v>79052</v>
+        <v>79638</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,40 +17199,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464745</v>
+        <v>464623</v>
       </c>
       <c r="R156" t="n">
-        <v>6784305</v>
+        <v>6784354</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17259,14 +17256,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17275,19 +17277,18 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17401,10 +17402,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127719947</v>
+        <v>127719674</v>
       </c>
       <c r="B158" t="n">
-        <v>79638</v>
+        <v>79052</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17412,37 +17413,40 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464623</v>
+        <v>464745</v>
       </c>
       <c r="R158" t="n">
-        <v>6784354</v>
+        <v>6784305</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17469,19 +17473,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17490,18 +17489,19 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17614,7 +17614,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127714369</v>
+        <v>127714657</v>
       </c>
       <c r="B160" t="n">
         <v>79020</v>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464931</v>
+        <v>464858</v>
       </c>
       <c r="R160" t="n">
-        <v>6784233</v>
+        <v>6784259</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127714657</v>
+        <v>127714369</v>
       </c>
       <c r="B161" t="n">
         <v>79020</v>
@@ -17756,13 +17756,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464858</v>
+        <v>464931</v>
       </c>
       <c r="R161" t="n">
-        <v>6784259</v>
+        <v>6784233</v>
       </c>
       <c r="S161" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17934,48 +17934,51 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127716709</v>
+        <v>127719588</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R163" t="n">
-        <v>6784275</v>
+        <v>6784242</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18002,19 +18005,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18023,28 +18021,29 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127719588</v>
+        <v>127718357</v>
       </c>
       <c r="B164" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18052,40 +18051,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>464844</v>
+        <v>464664</v>
       </c>
       <c r="R164" t="n">
-        <v>6784242</v>
+        <v>6784142</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18112,14 +18108,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18128,51 +18129,50 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127718357</v>
+        <v>127716709</v>
       </c>
       <c r="B165" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18182,10 +18182,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464664</v>
+        <v>464710</v>
       </c>
       <c r="R165" t="n">
-        <v>6784142</v>
+        <v>6784275</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18254,7 +18254,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127714909</v>
+        <v>127718026</v>
       </c>
       <c r="B166" t="n">
         <v>79020</v>
@@ -18289,10 +18289,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464844</v>
+        <v>464701</v>
       </c>
       <c r="R166" t="n">
-        <v>6784281</v>
+        <v>6784168</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18361,7 +18361,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127718026</v>
+        <v>127714909</v>
       </c>
       <c r="B167" t="n">
         <v>79020</v>
@@ -18396,10 +18396,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464701</v>
+        <v>464844</v>
       </c>
       <c r="R167" t="n">
-        <v>6784168</v>
+        <v>6784281</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18692,10 +18692,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127714955</v>
+        <v>127715185</v>
       </c>
       <c r="B170" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18703,21 +18703,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18727,10 +18727,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464844</v>
+        <v>464836</v>
       </c>
       <c r="R170" t="n">
-        <v>6784281</v>
+        <v>6784199</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18799,10 +18799,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127715185</v>
+        <v>127714955</v>
       </c>
       <c r="B171" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18810,21 +18810,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18834,10 +18834,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464836</v>
+        <v>464844</v>
       </c>
       <c r="R171" t="n">
-        <v>6784199</v>
+        <v>6784281</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,48 +18906,51 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127720766</v>
+        <v>127719816</v>
       </c>
       <c r="B172" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464581</v>
+        <v>464752</v>
       </c>
       <c r="R172" t="n">
-        <v>6784393</v>
+        <v>6784264</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18974,19 +18977,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18995,28 +18993,29 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127718375</v>
+        <v>127718015</v>
       </c>
       <c r="B173" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,21 +19023,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19048,10 +19047,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464664</v>
+        <v>464701</v>
       </c>
       <c r="R173" t="n">
-        <v>6784142</v>
+        <v>6784168</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19120,10 +19119,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127719813</v>
+        <v>127719841</v>
       </c>
       <c r="B174" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19131,21 +19130,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19227,10 +19226,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127718015</v>
+        <v>127718375</v>
       </c>
       <c r="B175" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19238,21 +19237,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19262,10 +19261,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464701</v>
+        <v>464664</v>
       </c>
       <c r="R175" t="n">
-        <v>6784168</v>
+        <v>6784142</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19334,10 +19333,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127719816</v>
+        <v>127719813</v>
       </c>
       <c r="B176" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19345,40 +19344,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464752</v>
+        <v>464647</v>
       </c>
       <c r="R176" t="n">
-        <v>6784264</v>
+        <v>6784377</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19405,14 +19401,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19421,51 +19422,50 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127719841</v>
+        <v>127720766</v>
       </c>
       <c r="B177" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464647</v>
+        <v>464581</v>
       </c>
       <c r="R177" t="n">
-        <v>6784377</v>
+        <v>6784393</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19766,41 +19766,40 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127719338</v>
+        <v>127719298</v>
       </c>
       <c r="B180" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -19810,10 +19809,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>464893</v>
+        <v>464943</v>
       </c>
       <c r="R180" t="n">
-        <v>6784258</v>
+        <v>6784241</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -19854,7 +19853,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -19985,48 +19983,57 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127719838</v>
+        <v>127719338</v>
       </c>
       <c r="B182" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464647</v>
+        <v>464893</v>
       </c>
       <c r="R182" t="n">
-        <v>6784377</v>
+        <v>6784258</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20053,49 +20060,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127719298</v>
+        <v>127719838</v>
       </c>
       <c r="B183" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20103,45 +20101,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>464943</v>
+        <v>464647</v>
       </c>
       <c r="R183" t="n">
-        <v>6784241</v>
+        <v>6784377</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20168,9 +20158,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20185,12 +20185,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20523,7 +20523,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127715332</v>
+        <v>127716097</v>
       </c>
       <c r="B187" t="n">
         <v>79020</v>
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>464836</v>
+        <v>464774</v>
       </c>
       <c r="R187" t="n">
-        <v>6784193</v>
+        <v>6784280</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20630,7 +20630,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127716097</v>
+        <v>127715332</v>
       </c>
       <c r="B188" t="n">
         <v>79020</v>
@@ -20665,10 +20665,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464774</v>
+        <v>464836</v>
       </c>
       <c r="R188" t="n">
-        <v>6784280</v>
+        <v>6784193</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20844,10 +20844,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127719836</v>
+        <v>127719877</v>
       </c>
       <c r="B190" t="n">
-        <v>79609</v>
+        <v>91352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20855,21 +20855,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464715</v>
+        <v>464667</v>
       </c>
       <c r="R190" t="n">
-        <v>6784291</v>
+        <v>6784226</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -20918,11 +20918,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20950,10 +20945,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719877</v>
+        <v>127719836</v>
       </c>
       <c r="B191" t="n">
-        <v>91352</v>
+        <v>79609</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20961,21 +20956,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20988,10 +20983,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464667</v>
+        <v>464715</v>
       </c>
       <c r="R191" t="n">
-        <v>6784226</v>
+        <v>6784291</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21024,6 +21019,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21051,32 +21051,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127721018</v>
+        <v>127714444</v>
       </c>
       <c r="B192" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464816</v>
+        <v>464913</v>
       </c>
       <c r="R192" t="n">
-        <v>6784317</v>
+        <v>6784254</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21158,10 +21158,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127714444</v>
+        <v>127717898</v>
       </c>
       <c r="B193" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21169,21 +21169,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21193,10 +21193,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464913</v>
+        <v>464701</v>
       </c>
       <c r="R193" t="n">
-        <v>6784254</v>
+        <v>6784168</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21265,32 +21265,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127717898</v>
+        <v>127721018</v>
       </c>
       <c r="B194" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21300,10 +21300,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464701</v>
+        <v>464816</v>
       </c>
       <c r="R194" t="n">
-        <v>6784168</v>
+        <v>6784317</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21585,10 +21585,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127719863</v>
+        <v>127717085</v>
       </c>
       <c r="B197" t="n">
-        <v>91352</v>
+        <v>57823</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21596,40 +21596,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>464688</v>
+        <v>464671</v>
       </c>
       <c r="R197" t="n">
-        <v>6784295</v>
+        <v>6784233</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21656,40 +21658,49 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127717085</v>
+        <v>127719863</v>
       </c>
       <c r="B198" t="n">
-        <v>57823</v>
+        <v>91352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21697,42 +21708,40 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>464671</v>
+        <v>464688</v>
       </c>
       <c r="R198" t="n">
-        <v>6784233</v>
+        <v>6784295</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21759,39 +21768,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
@@ -21915,7 +21915,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127718813</v>
+        <v>127707668</v>
       </c>
       <c r="B200" t="n">
         <v>79020</v>
@@ -21950,10 +21950,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464588</v>
+        <v>464689</v>
       </c>
       <c r="R200" t="n">
-        <v>6784281</v>
+        <v>6784378</v>
       </c>
       <c r="S200" t="n">
         <v>50</v>
@@ -21980,27 +21980,27 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22027,50 +22027,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127706550</v>
+        <v>127708066</v>
       </c>
       <c r="B201" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464683</v>
+        <v>464699</v>
       </c>
       <c r="R201" t="n">
-        <v>6784461</v>
+        <v>6784396</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22117,7 +22112,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22126,7 +22121,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -22145,7 +22139,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127707668</v>
+        <v>127718813</v>
       </c>
       <c r="B202" t="n">
         <v>79020</v>
@@ -22180,10 +22174,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464689</v>
+        <v>464588</v>
       </c>
       <c r="R202" t="n">
-        <v>6784378</v>
+        <v>6784281</v>
       </c>
       <c r="S202" t="n">
         <v>50</v>
@@ -22210,27 +22204,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22257,45 +22251,50 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127708066</v>
+        <v>127706550</v>
       </c>
       <c r="B203" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464699</v>
+        <v>464683</v>
       </c>
       <c r="R203" t="n">
-        <v>6784396</v>
+        <v>6784461</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22342,7 +22341,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>2 bilder, rikligt på tall</t>
+          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22351,6 +22350,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -22705,7 +22705,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127706968</v>
+        <v>127716564</v>
       </c>
       <c r="B207" t="n">
         <v>79020</v>
@@ -22734,22 +22734,19 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>464673</v>
+        <v>464727</v>
       </c>
       <c r="R207" t="n">
-        <v>6784503</v>
+        <v>6784316</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22773,27 +22770,27 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22802,7 +22799,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -22821,7 +22817,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127716564</v>
+        <v>127706968</v>
       </c>
       <c r="B208" t="n">
         <v>79020</v>
@@ -22850,19 +22846,22 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>464727</v>
+        <v>464673</v>
       </c>
       <c r="R208" t="n">
-        <v>6784316</v>
+        <v>6784503</v>
       </c>
       <c r="S208" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22886,27 +22885,27 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
+          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22915,6 +22914,7 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -23268,7 +23268,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127720341</v>
+        <v>127719613</v>
       </c>
       <c r="B212" t="n">
         <v>79020</v>
@@ -23303,10 +23303,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>464568</v>
+        <v>464669</v>
       </c>
       <c r="R212" t="n">
-        <v>6784376</v>
+        <v>6784345</v>
       </c>
       <c r="S212" t="n">
         <v>50</v>
@@ -23353,7 +23353,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder, första med lutande tall</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23380,7 +23380,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127719613</v>
+        <v>127720341</v>
       </c>
       <c r="B213" t="n">
         <v>79020</v>
@@ -23415,10 +23415,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>464669</v>
+        <v>464568</v>
       </c>
       <c r="R213" t="n">
-        <v>6784345</v>
+        <v>6784376</v>
       </c>
       <c r="S213" t="n">
         <v>50</v>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder, första med lutande tall</t>
+          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23836,7 +23836,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127718616</v>
+        <v>127716791</v>
       </c>
       <c r="B217" t="n">
         <v>79020</v>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>464618</v>
+        <v>464667</v>
       </c>
       <c r="R217" t="n">
-        <v>6784236</v>
+        <v>6784294</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23948,10 +23948,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127717010</v>
+        <v>127718616</v>
       </c>
       <c r="B218" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23959,21 +23959,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>464680</v>
+        <v>464618</v>
       </c>
       <c r="R218" t="n">
-        <v>6784254</v>
+        <v>6784236</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24033,7 +24033,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>1 Bild på stubbe med garn i bakgrund på tall</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24060,10 +24060,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127716791</v>
+        <v>127717010</v>
       </c>
       <c r="B219" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24071,21 +24071,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>464667</v>
+        <v>464680</v>
       </c>
       <c r="R219" t="n">
-        <v>6784294</v>
+        <v>6784254</v>
       </c>
       <c r="S219" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>1 Bild på stubbe med garn i bakgrund på tall</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24289,42 +24289,37 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127707530</v>
+        <v>127716476</v>
       </c>
       <c r="B221" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
@@ -24332,10 +24327,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>464686</v>
+        <v>464774</v>
       </c>
       <c r="R221" t="n">
-        <v>6784430</v>
+        <v>6784282</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24362,27 +24357,27 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Spillning under tall med en vit påläggning på stammen</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24391,6 +24386,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24409,37 +24405,42 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127716476</v>
+        <v>127707530</v>
       </c>
       <c r="B222" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
@@ -24447,10 +24448,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464774</v>
+        <v>464686</v>
       </c>
       <c r="R222" t="n">
-        <v>6784282</v>
+        <v>6784430</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24477,27 +24478,27 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>Spillning under tall med en vit påläggning på stammen</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24506,7 +24507,6 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127705478</v>
+        <v>127716937</v>
       </c>
       <c r="B224" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,42 +24653,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464863</v>
+        <v>464680</v>
       </c>
       <c r="R224" t="n">
-        <v>6784423</v>
+        <v>6784254</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24715,27 +24707,27 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24762,7 +24754,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127716937</v>
+        <v>127714858</v>
       </c>
       <c r="B225" t="n">
         <v>79020</v>
@@ -24797,10 +24789,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464680</v>
+        <v>464856</v>
       </c>
       <c r="R225" t="n">
-        <v>6784254</v>
+        <v>6784268</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24847,7 +24839,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24874,10 +24866,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127719810</v>
+        <v>127705478</v>
       </c>
       <c r="B226" t="n">
-        <v>78778</v>
+        <v>57660</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24885,34 +24877,42 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464647</v>
+        <v>464863</v>
       </c>
       <c r="R226" t="n">
-        <v>6784377</v>
+        <v>6784423</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24939,27 +24939,27 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24986,10 +24986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127714858</v>
+        <v>127719810</v>
       </c>
       <c r="B227" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464856</v>
+        <v>464647</v>
       </c>
       <c r="R227" t="n">
-        <v>6784268</v>
+        <v>6784377</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25071,7 +25071,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>1 bild band i bakgrund</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25553,6 +25553,111 @@
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>127793591</v>
+      </c>
+      <c r="B232" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>464673</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6784214</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127505584</v>
+        <v>127566254</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464920</v>
+        <v>464782</v>
       </c>
       <c r="R5" t="n">
-        <v>6784591</v>
+        <v>6784529</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127503663</v>
+        <v>127505584</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464847</v>
+        <v>464920</v>
       </c>
       <c r="R6" t="n">
-        <v>6784531</v>
+        <v>6784591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127536063</v>
+        <v>127503663</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464819</v>
+        <v>464847</v>
       </c>
       <c r="R7" t="n">
-        <v>6784639</v>
+        <v>6784531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127601236</v>
+        <v>127536063</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,40 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464862</v>
+        <v>464819</v>
       </c>
       <c r="R8" t="n">
-        <v>6784534</v>
+        <v>6784639</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,14 +1385,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,26 +1406,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127602494</v>
+        <v>127601236</v>
       </c>
       <c r="B9" t="n">
         <v>79052</v>
@@ -1461,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464821</v>
+        <v>464862</v>
       </c>
       <c r="R9" t="n">
-        <v>6784490</v>
+        <v>6784534</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1529,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127566254</v>
+        <v>127602494</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,37 +1541,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464782</v>
+        <v>464821</v>
       </c>
       <c r="R10" t="n">
-        <v>6784529</v>
+        <v>6784490</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,19 +1601,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,18 +1617,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127581242</v>
+        <v>127581092</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B34" t="n">
         <v>79052</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R34" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B35" t="n">
         <v>79052</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R35" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R36" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R37" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127580584</v>
+        <v>127582358</v>
       </c>
       <c r="B42" t="n">
         <v>79020</v>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464783</v>
+        <v>464803</v>
       </c>
       <c r="R42" t="n">
-        <v>6784477</v>
+        <v>6784481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127582358</v>
+        <v>127580584</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464803</v>
+        <v>464783</v>
       </c>
       <c r="R43" t="n">
-        <v>6784481</v>
+        <v>6784477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6552,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127627244</v>
+        <v>127627419</v>
       </c>
       <c r="B57" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464822</v>
+        <v>464828</v>
       </c>
       <c r="R57" t="n">
-        <v>6784620</v>
+        <v>6784480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,6 +6626,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6653,7 +6658,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127627419</v>
+        <v>127627476</v>
       </c>
       <c r="B58" t="n">
         <v>79020</v>
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464828</v>
+        <v>464889</v>
       </c>
       <c r="R58" t="n">
-        <v>6784480</v>
+        <v>6784444</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6759,10 +6764,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127627476</v>
+        <v>127627244</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6770,21 +6775,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6797,10 +6802,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464889</v>
+        <v>464822</v>
       </c>
       <c r="R59" t="n">
-        <v>6784444</v>
+        <v>6784620</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6833,11 +6838,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B60" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R60" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R61" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627017</v>
+        <v>127627035</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464871</v>
+        <v>464881</v>
       </c>
       <c r="R66" t="n">
-        <v>6784599</v>
+        <v>6784597</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7592,7 +7592,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627035</v>
+        <v>127627017</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464881</v>
+        <v>464871</v>
       </c>
       <c r="R67" t="n">
-        <v>6784597</v>
+        <v>6784599</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8112,7 +8112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R72" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,11 +8186,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8218,7 +8213,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627174</v>
+        <v>127627007</v>
       </c>
       <c r="B73" t="n">
         <v>79020</v>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464796</v>
+        <v>464841</v>
       </c>
       <c r="R73" t="n">
-        <v>6784631</v>
+        <v>6784612</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8292,6 +8287,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627129</v>
+        <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464866</v>
+        <v>464805</v>
       </c>
       <c r="R76" t="n">
-        <v>6784700</v>
+        <v>6784486</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627329</v>
+        <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464867</v>
+        <v>464822</v>
       </c>
       <c r="R77" t="n">
-        <v>6784590</v>
+        <v>6784620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,6 +8707,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8734,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627383</v>
+        <v>127627329</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8745,21 +8750,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8772,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464805</v>
+        <v>464867</v>
       </c>
       <c r="R78" t="n">
-        <v>6784486</v>
+        <v>6784590</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8835,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627242</v>
+        <v>127627129</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8846,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464822</v>
+        <v>464866</v>
       </c>
       <c r="R79" t="n">
-        <v>6784620</v>
+        <v>6784700</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8909,11 +8914,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9696,7 +9696,7 @@
         <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>79021</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R88" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B89" t="n">
-        <v>79021</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R89" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>91358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R95" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B96" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R96" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10802,10 +10802,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127504835</v>
+        <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10813,26 +10813,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10840,13 +10841,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464893</v>
+        <v>464854</v>
       </c>
       <c r="R97" t="n">
-        <v>6784570</v>
+        <v>6784587</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10890,7 +10891,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10899,7 +10900,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10918,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127554764</v>
+        <v>127504835</v>
       </c>
       <c r="B98" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10929,27 +10929,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10957,13 +10956,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464854</v>
+        <v>464893</v>
       </c>
       <c r="R98" t="n">
-        <v>6784587</v>
+        <v>6784570</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11007,7 +11006,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Bild på hackspår samt Mindre m...</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11016,6 +11015,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11369,32 +11369,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127706377</v>
+        <v>127705341</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464687</v>
+        <v>464871</v>
       </c>
       <c r="R102" t="n">
-        <v>6784448</v>
+        <v>6784452</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127705454</v>
+        <v>127706377</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464863</v>
+        <v>464687</v>
       </c>
       <c r="R103" t="n">
-        <v>6784423</v>
+        <v>6784448</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127707616</v>
+        <v>127705454</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464701</v>
+        <v>464863</v>
       </c>
       <c r="R104" t="n">
-        <v>6784412</v>
+        <v>6784423</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11690,32 +11690,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127705341</v>
+        <v>127707616</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464871</v>
+        <v>464701</v>
       </c>
       <c r="R105" t="n">
-        <v>6784452</v>
+        <v>6784412</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12439,10 +12439,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127704413</v>
+        <v>127706997</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464906</v>
+        <v>464666</v>
       </c>
       <c r="R112" t="n">
-        <v>6784432</v>
+        <v>6784496</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127704473</v>
+        <v>127704413</v>
       </c>
       <c r="B113" t="n">
         <v>79020</v>
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464897</v>
+        <v>464906</v>
       </c>
       <c r="R113" t="n">
-        <v>6784413</v>
+        <v>6784432</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12653,10 +12653,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127706997</v>
+        <v>127704473</v>
       </c>
       <c r="B114" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12664,21 +12664,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464666</v>
+        <v>464897</v>
       </c>
       <c r="R114" t="n">
-        <v>6784496</v>
+        <v>6784413</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127707041</v>
+        <v>127706073</v>
       </c>
       <c r="B115" t="n">
-        <v>79609</v>
+        <v>57660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12771,34 +12771,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464666</v>
+        <v>464701</v>
       </c>
       <c r="R115" t="n">
-        <v>6784496</v>
+        <v>6784425</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,6 +12846,11 @@
       <c r="AB115" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12867,10 +12877,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127706073</v>
+        <v>127707041</v>
       </c>
       <c r="B116" t="n">
-        <v>57660</v>
+        <v>79609</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12878,39 +12888,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464701</v>
+        <v>464666</v>
       </c>
       <c r="R116" t="n">
-        <v>6784425</v>
+        <v>6784496</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12953,11 +12958,6 @@
       <c r="AB116" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13310,45 +13310,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127704405</v>
+        <v>127705654</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464901</v>
+        <v>464863</v>
       </c>
       <c r="R120" t="n">
-        <v>6784434</v>
+        <v>6784423</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13417,50 +13422,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127705654</v>
+        <v>127704405</v>
       </c>
       <c r="B121" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464863</v>
+        <v>464901</v>
       </c>
       <c r="R121" t="n">
-        <v>6784423</v>
+        <v>6784434</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127707123</v>
+        <v>127705832</v>
       </c>
       <c r="B127" t="n">
         <v>79020</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464660</v>
+        <v>464736</v>
       </c>
       <c r="R127" t="n">
-        <v>6784477</v>
+        <v>6784473</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14171,7 +14171,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127705062</v>
+        <v>127707123</v>
       </c>
       <c r="B128" t="n">
         <v>79020</v>
@@ -14206,10 +14206,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464888</v>
+        <v>464660</v>
       </c>
       <c r="R128" t="n">
-        <v>6784446</v>
+        <v>6784477</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14278,7 +14278,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127705832</v>
+        <v>127705062</v>
       </c>
       <c r="B129" t="n">
         <v>79020</v>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464736</v>
+        <v>464888</v>
       </c>
       <c r="R129" t="n">
-        <v>6784473</v>
+        <v>6784446</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14599,32 +14599,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127707939</v>
+        <v>127706356</v>
       </c>
       <c r="B132" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14634,10 +14634,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464707</v>
+        <v>464687</v>
       </c>
       <c r="R132" t="n">
-        <v>6784355</v>
+        <v>6784448</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14706,32 +14706,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127706356</v>
+        <v>127707939</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14741,10 +14741,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464687</v>
+        <v>464707</v>
       </c>
       <c r="R133" t="n">
-        <v>6784448</v>
+        <v>6784355</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14813,7 +14813,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127715198</v>
+        <v>127721029</v>
       </c>
       <c r="B134" t="n">
         <v>79020</v>
@@ -14848,10 +14848,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464836</v>
+        <v>464816</v>
       </c>
       <c r="R134" t="n">
-        <v>6784199</v>
+        <v>6784317</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14920,32 +14920,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127718498</v>
+        <v>127715439</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14955,13 +14955,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464686</v>
+        <v>464832</v>
       </c>
       <c r="R135" t="n">
-        <v>6784147</v>
+        <v>6784214</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15027,10 +15027,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127719564</v>
+        <v>127714234</v>
       </c>
       <c r="B136" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15038,40 +15038,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464859</v>
+        <v>464936</v>
       </c>
       <c r="R136" t="n">
-        <v>6784218</v>
+        <v>6784248</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15098,14 +15095,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15114,26 +15116,25 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127721029</v>
+        <v>127720285</v>
       </c>
       <c r="B137" t="n">
         <v>79020</v>
@@ -15168,13 +15169,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464816</v>
+        <v>464564</v>
       </c>
       <c r="R137" t="n">
-        <v>6784317</v>
+        <v>6784324</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15214,6 +15215,11 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15240,7 +15246,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127715439</v>
+        <v>127715198</v>
       </c>
       <c r="B138" t="n">
         <v>79020</v>
@@ -15275,10 +15281,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464832</v>
+        <v>464836</v>
       </c>
       <c r="R138" t="n">
-        <v>6784214</v>
+        <v>6784199</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15347,32 +15353,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127714234</v>
+        <v>127718498</v>
       </c>
       <c r="B139" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15382,10 +15388,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464936</v>
+        <v>464686</v>
       </c>
       <c r="R139" t="n">
-        <v>6784248</v>
+        <v>6784147</v>
       </c>
       <c r="S139" t="n">
         <v>50</v>
@@ -15417,7 +15423,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15427,7 +15433,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15454,10 +15460,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127720285</v>
+        <v>127719564</v>
       </c>
       <c r="B140" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15465,37 +15471,40 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464564</v>
+        <v>464859</v>
       </c>
       <c r="R140" t="n">
-        <v>6784324</v>
+        <v>6784218</v>
       </c>
       <c r="S140" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15522,24 +15531,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15548,25 +15547,26 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127718980</v>
+        <v>127715717</v>
       </c>
       <c r="B141" t="n">
         <v>79020</v>
@@ -15601,10 +15601,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464628</v>
+        <v>464788</v>
       </c>
       <c r="R141" t="n">
-        <v>6784279</v>
+        <v>6784220</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15673,7 +15673,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127715717</v>
+        <v>127718502</v>
       </c>
       <c r="B142" t="n">
         <v>79020</v>
@@ -15708,13 +15708,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464788</v>
+        <v>464686</v>
       </c>
       <c r="R142" t="n">
-        <v>6784220</v>
+        <v>6784147</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127718502</v>
+        <v>127718980</v>
       </c>
       <c r="B143" t="n">
         <v>79020</v>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464686</v>
+        <v>464628</v>
       </c>
       <c r="R143" t="n">
-        <v>6784147</v>
+        <v>6784279</v>
       </c>
       <c r="S143" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16430,10 +16430,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127715006</v>
+        <v>127719855</v>
       </c>
       <c r="B149" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16441,39 +16441,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464844</v>
+        <v>464647</v>
       </c>
       <c r="R149" t="n">
-        <v>6784281</v>
+        <v>6784377</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16542,10 +16537,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127719855</v>
+        <v>127715006</v>
       </c>
       <c r="B150" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16553,34 +16548,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464647</v>
+        <v>464844</v>
       </c>
       <c r="R150" t="n">
-        <v>6784377</v>
+        <v>6784281</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16863,57 +16863,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127719421</v>
+        <v>127718021</v>
       </c>
       <c r="B153" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464871</v>
+        <v>464701</v>
       </c>
       <c r="R153" t="n">
-        <v>6784277</v>
+        <v>6784168</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16940,14 +16931,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På 2 torrtallar, en tallåga</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16956,19 +16952,18 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17081,48 +17076,57 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127718021</v>
+        <v>127719421</v>
       </c>
       <c r="B155" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464701</v>
+        <v>464871</v>
       </c>
       <c r="R155" t="n">
-        <v>6784168</v>
+        <v>6784277</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17149,19 +17153,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På 2 torrtallar, en tallåga</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17170,28 +17169,29 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719947</v>
+        <v>127719674</v>
       </c>
       <c r="B156" t="n">
-        <v>79638</v>
+        <v>79052</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,37 +17199,40 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464623</v>
+        <v>464745</v>
       </c>
       <c r="R156" t="n">
-        <v>6784354</v>
+        <v>6784305</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17256,19 +17259,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17277,25 +17275,26 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127717666</v>
+        <v>127719947</v>
       </c>
       <c r="B157" t="n">
         <v>79638</v>
@@ -17330,10 +17329,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464682</v>
+        <v>464623</v>
       </c>
       <c r="R157" t="n">
-        <v>6784195</v>
+        <v>6784354</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17402,10 +17401,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127719674</v>
+        <v>127717666</v>
       </c>
       <c r="B158" t="n">
-        <v>79052</v>
+        <v>79638</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17413,40 +17412,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464745</v>
+        <v>464682</v>
       </c>
       <c r="R158" t="n">
-        <v>6784305</v>
+        <v>6784195</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17473,14 +17469,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17489,19 +17490,18 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17614,10 +17614,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127714657</v>
+        <v>127719525</v>
       </c>
       <c r="B160" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17625,37 +17625,40 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464858</v>
+        <v>464859</v>
       </c>
       <c r="R160" t="n">
-        <v>6784259</v>
+        <v>6784218</v>
       </c>
       <c r="S160" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17682,19 +17685,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17703,25 +17701,26 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127714369</v>
+        <v>127714657</v>
       </c>
       <c r="B161" t="n">
         <v>79020</v>
@@ -17756,13 +17755,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464931</v>
+        <v>464858</v>
       </c>
       <c r="R161" t="n">
-        <v>6784233</v>
+        <v>6784259</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17828,10 +17827,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127719525</v>
+        <v>127714369</v>
       </c>
       <c r="B162" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17839,40 +17838,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>464859</v>
+        <v>464931</v>
       </c>
       <c r="R162" t="n">
-        <v>6784218</v>
+        <v>6784233</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17899,14 +17895,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17915,70 +17916,66 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127719588</v>
+        <v>127716709</v>
       </c>
       <c r="B163" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R163" t="n">
-        <v>6784242</v>
+        <v>6784275</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18005,14 +18002,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18021,29 +18023,28 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127718357</v>
+        <v>127719588</v>
       </c>
       <c r="B164" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18051,37 +18052,40 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>464664</v>
+        <v>464844</v>
       </c>
       <c r="R164" t="n">
-        <v>6784142</v>
+        <v>6784242</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18108,19 +18112,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18129,50 +18128,51 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127716709</v>
+        <v>127718357</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18182,10 +18182,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464710</v>
+        <v>464664</v>
       </c>
       <c r="R165" t="n">
-        <v>6784275</v>
+        <v>6784142</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18254,7 +18254,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127718026</v>
+        <v>127714909</v>
       </c>
       <c r="B166" t="n">
         <v>79020</v>
@@ -18289,10 +18289,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464701</v>
+        <v>464844</v>
       </c>
       <c r="R166" t="n">
-        <v>6784168</v>
+        <v>6784281</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18361,7 +18361,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127714909</v>
+        <v>127718026</v>
       </c>
       <c r="B167" t="n">
         <v>79020</v>
@@ -18396,10 +18396,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464844</v>
+        <v>464701</v>
       </c>
       <c r="R167" t="n">
-        <v>6784281</v>
+        <v>6784168</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127716661</v>
+        <v>127714955</v>
       </c>
       <c r="B169" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18591,39 +18591,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R169" t="n">
-        <v>6784275</v>
+        <v>6784281</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18799,10 +18794,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127714955</v>
+        <v>127716661</v>
       </c>
       <c r="B171" t="n">
-        <v>78779</v>
+        <v>57660</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18810,34 +18805,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R171" t="n">
-        <v>6784281</v>
+        <v>6784275</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,10 +18906,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127719816</v>
+        <v>127718375</v>
       </c>
       <c r="B172" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18917,40 +18917,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464752</v>
+        <v>464664</v>
       </c>
       <c r="R172" t="n">
-        <v>6784264</v>
+        <v>6784142</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18977,14 +18974,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18993,29 +18995,28 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127718015</v>
+        <v>127719813</v>
       </c>
       <c r="B173" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19023,21 +19024,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19047,10 +19048,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464701</v>
+        <v>464647</v>
       </c>
       <c r="R173" t="n">
-        <v>6784168</v>
+        <v>6784377</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19119,32 +19120,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127719841</v>
+        <v>127720766</v>
       </c>
       <c r="B174" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19154,10 +19155,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>464647</v>
+        <v>464581</v>
       </c>
       <c r="R174" t="n">
-        <v>6784377</v>
+        <v>6784393</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19226,10 +19227,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127718375</v>
+        <v>127718015</v>
       </c>
       <c r="B175" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19237,21 +19238,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19261,10 +19262,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464664</v>
+        <v>464701</v>
       </c>
       <c r="R175" t="n">
-        <v>6784142</v>
+        <v>6784168</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19333,10 +19334,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127719813</v>
+        <v>127719816</v>
       </c>
       <c r="B176" t="n">
-        <v>79638</v>
+        <v>79609</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19344,37 +19345,40 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464647</v>
+        <v>464752</v>
       </c>
       <c r="R176" t="n">
-        <v>6784377</v>
+        <v>6784264</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19401,19 +19405,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19422,50 +19421,51 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127720766</v>
+        <v>127719841</v>
       </c>
       <c r="B177" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464581</v>
+        <v>464647</v>
       </c>
       <c r="R177" t="n">
-        <v>6784393</v>
+        <v>6784377</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19547,10 +19547,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127714169</v>
+        <v>127718840</v>
       </c>
       <c r="B178" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19558,37 +19558,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>464951</v>
+        <v>464588</v>
       </c>
       <c r="R178" t="n">
-        <v>6784236</v>
+        <v>6784281</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19617,7 +19622,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19627,7 +19632,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19654,10 +19659,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127718840</v>
+        <v>127714169</v>
       </c>
       <c r="B179" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19665,42 +19670,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>464588</v>
+        <v>464951</v>
       </c>
       <c r="R179" t="n">
-        <v>6784281</v>
+        <v>6784236</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20844,10 +20844,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127719877</v>
+        <v>127719836</v>
       </c>
       <c r="B190" t="n">
-        <v>91352</v>
+        <v>79609</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20855,21 +20855,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464667</v>
+        <v>464715</v>
       </c>
       <c r="R190" t="n">
-        <v>6784226</v>
+        <v>6784291</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -20918,6 +20918,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20945,10 +20950,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719836</v>
+        <v>127719877</v>
       </c>
       <c r="B191" t="n">
-        <v>79609</v>
+        <v>91358</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20956,21 +20961,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20983,10 +20988,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464715</v>
+        <v>464667</v>
       </c>
       <c r="R191" t="n">
-        <v>6784291</v>
+        <v>6784226</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21019,11 +21024,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21158,32 +21158,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127717898</v>
+        <v>127721018</v>
       </c>
       <c r="B193" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21193,10 +21193,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464701</v>
+        <v>464816</v>
       </c>
       <c r="R193" t="n">
-        <v>6784168</v>
+        <v>6784317</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21265,48 +21265,51 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127721018</v>
+        <v>127719210</v>
       </c>
       <c r="B194" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464816</v>
+        <v>464941</v>
       </c>
       <c r="R194" t="n">
-        <v>6784317</v>
+        <v>6784243</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21333,19 +21336,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21354,28 +21352,29 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127719210</v>
+        <v>127717898</v>
       </c>
       <c r="B195" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21383,40 +21382,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464941</v>
+        <v>464701</v>
       </c>
       <c r="R195" t="n">
-        <v>6784243</v>
+        <v>6784168</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21443,14 +21439,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21459,29 +21460,28 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127717016</v>
+        <v>127717085</v>
       </c>
       <c r="B196" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21489,34 +21489,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464672</v>
+        <v>464671</v>
       </c>
       <c r="R196" t="n">
-        <v>6784257</v>
+        <v>6784233</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21585,10 +21590,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127717085</v>
+        <v>127717016</v>
       </c>
       <c r="B197" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21596,39 +21601,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>464671</v>
+        <v>464672</v>
       </c>
       <c r="R197" t="n">
-        <v>6784233</v>
+        <v>6784257</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21700,7 +21700,7 @@
         <v>127719863</v>
       </c>
       <c r="B198" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21915,48 +21915,53 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127707668</v>
+        <v>127706550</v>
       </c>
       <c r="B200" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464689</v>
+        <v>464683</v>
       </c>
       <c r="R200" t="n">
-        <v>6784378</v>
+        <v>6784461</v>
       </c>
       <c r="S200" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22000,7 +22005,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22009,6 +22014,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22027,7 +22033,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127708066</v>
+        <v>127707668</v>
       </c>
       <c r="B201" t="n">
         <v>79020</v>
@@ -22062,13 +22068,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464699</v>
+        <v>464689</v>
       </c>
       <c r="R201" t="n">
-        <v>6784396</v>
+        <v>6784378</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22112,7 +22118,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>2 bilder, rikligt på tall</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22139,7 +22145,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127718813</v>
+        <v>127708066</v>
       </c>
       <c r="B202" t="n">
         <v>79020</v>
@@ -22174,13 +22180,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464588</v>
+        <v>464699</v>
       </c>
       <c r="R202" t="n">
-        <v>6784281</v>
+        <v>6784396</v>
       </c>
       <c r="S202" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22204,27 +22210,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22251,53 +22257,48 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127706550</v>
+        <v>127718813</v>
       </c>
       <c r="B203" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464683</v>
+        <v>464588</v>
       </c>
       <c r="R203" t="n">
-        <v>6784461</v>
+        <v>6784281</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22321,27 +22322,27 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22350,7 +22351,6 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -22705,7 +22705,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127716564</v>
+        <v>127706968</v>
       </c>
       <c r="B207" t="n">
         <v>79020</v>
@@ -22734,19 +22734,22 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>464727</v>
+        <v>464673</v>
       </c>
       <c r="R207" t="n">
-        <v>6784316</v>
+        <v>6784503</v>
       </c>
       <c r="S207" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22770,27 +22773,27 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
+          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22799,6 +22802,7 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -22817,7 +22821,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127706968</v>
+        <v>127716564</v>
       </c>
       <c r="B208" t="n">
         <v>79020</v>
@@ -22846,22 +22850,19 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>464673</v>
+        <v>464727</v>
       </c>
       <c r="R208" t="n">
-        <v>6784503</v>
+        <v>6784316</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22885,27 +22886,27 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22914,7 +22915,6 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -23053,7 +23053,7 @@
         <v>127751842</v>
       </c>
       <c r="B210" t="n">
-        <v>91562</v>
+        <v>91568</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23156,32 +23156,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127707243</v>
+        <v>127720341</v>
       </c>
       <c r="B211" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23191,13 +23191,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>464652</v>
+        <v>464568</v>
       </c>
       <c r="R211" t="n">
-        <v>6784464</v>
+        <v>6784376</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23221,27 +23221,27 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>1 bild på låga med garnlav</t>
+          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23380,32 +23380,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127720341</v>
+        <v>127707243</v>
       </c>
       <c r="B213" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23415,13 +23415,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>464568</v>
+        <v>464652</v>
       </c>
       <c r="R213" t="n">
-        <v>6784376</v>
+        <v>6784464</v>
       </c>
       <c r="S213" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23445,27 +23445,27 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  3 bilder</t>
+          <t>1 bild på låga med garnlav</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23612,10 +23612,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127717659</v>
+        <v>127719315</v>
       </c>
       <c r="B215" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23623,21 +23623,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>464682</v>
+        <v>464650</v>
       </c>
       <c r="R215" t="n">
-        <v>6784195</v>
+        <v>6784317</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>2 bilder på 2 stubbar</t>
+          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23724,10 +23724,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127719315</v>
+        <v>127717659</v>
       </c>
       <c r="B216" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23735,21 +23735,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>464650</v>
+        <v>464682</v>
       </c>
       <c r="R216" t="n">
-        <v>6784317</v>
+        <v>6784195</v>
       </c>
       <c r="S216" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
+          <t>2 bilder på 2 stubbar</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23836,7 +23836,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127716791</v>
+        <v>127718616</v>
       </c>
       <c r="B217" t="n">
         <v>79020</v>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>464667</v>
+        <v>464618</v>
       </c>
       <c r="R217" t="n">
-        <v>6784294</v>
+        <v>6784236</v>
       </c>
       <c r="S217" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127718616</v>
+        <v>127716791</v>
       </c>
       <c r="B218" t="n">
         <v>79020</v>
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>464618</v>
+        <v>464667</v>
       </c>
       <c r="R218" t="n">
-        <v>6784236</v>
+        <v>6784294</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24172,10 +24172,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127707455</v>
+        <v>127716476</v>
       </c>
       <c r="B220" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24183,39 +24183,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>464669</v>
+        <v>464774</v>
       </c>
       <c r="R220" t="n">
-        <v>6784449</v>
+        <v>6784282</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24242,27 +24240,27 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24271,6 +24269,7 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24289,10 +24288,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127716476</v>
+        <v>127707455</v>
       </c>
       <c r="B221" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24300,37 +24299,39 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>464774</v>
+        <v>464669</v>
       </c>
       <c r="R221" t="n">
-        <v>6784282</v>
+        <v>6784449</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24357,27 +24358,27 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24386,7 +24387,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127716937</v>
+        <v>127705478</v>
       </c>
       <c r="B224" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,34 +24653,42 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464680</v>
+        <v>464863</v>
       </c>
       <c r="R224" t="n">
-        <v>6784254</v>
+        <v>6784423</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24707,27 +24715,27 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24866,10 +24874,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127705478</v>
+        <v>127716937</v>
       </c>
       <c r="B226" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24877,42 +24885,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464863</v>
+        <v>464680</v>
       </c>
       <c r="R226" t="n">
-        <v>6784423</v>
+        <v>6784254</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24939,27 +24939,27 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25098,10 +25098,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127707100</v>
+        <v>127717066</v>
       </c>
       <c r="B228" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25109,39 +25109,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>464660</v>
+        <v>464671</v>
       </c>
       <c r="R228" t="n">
-        <v>6784477</v>
+        <v>6784233</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25168,27 +25166,27 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>2 bilder, hål ca 3 meter upp</t>
+          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25197,6 +25195,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25215,10 +25214,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127717066</v>
+        <v>127707100</v>
       </c>
       <c r="B229" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25226,37 +25225,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>464671</v>
+        <v>464660</v>
       </c>
       <c r="R229" t="n">
-        <v>6784233</v>
+        <v>6784477</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25283,27 +25284,27 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
+          <t>2 bilder, hål ca 3 meter upp</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25312,7 +25313,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127511371</v>
       </c>
       <c r="B2" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R3" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127554096</v>
+        <v>127503574</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R4" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127566254</v>
+        <v>127601236</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464782</v>
+        <v>464862</v>
       </c>
       <c r="R5" t="n">
-        <v>6784529</v>
+        <v>6784534</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,19 +1067,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,28 +1083,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127505584</v>
+        <v>127602494</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1113,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464920</v>
+        <v>464821</v>
       </c>
       <c r="R6" t="n">
-        <v>6784591</v>
+        <v>6784490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1173,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,28 +1189,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127503663</v>
+        <v>127566254</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464847</v>
+        <v>464782</v>
       </c>
       <c r="R7" t="n">
-        <v>6784531</v>
+        <v>6784529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127536063</v>
+        <v>127505584</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464819</v>
+        <v>464920</v>
       </c>
       <c r="R8" t="n">
-        <v>6784639</v>
+        <v>6784591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,40 +1433,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R9" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,14 +1490,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,29 +1511,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,40 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R10" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,14 +1597,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,19 +1618,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127518186</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127503996</v>
+        <v>127601675</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,37 +1754,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464844</v>
+        <v>464886</v>
       </c>
       <c r="R12" t="n">
-        <v>6784533</v>
+        <v>6784594</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,19 +1814,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,28 +1830,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127601675</v>
+        <v>127503996</v>
       </c>
       <c r="B13" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,40 +1860,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464886</v>
+        <v>464844</v>
       </c>
       <c r="R13" t="n">
-        <v>6784594</v>
+        <v>6784533</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1921,14 +1917,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,19 +1938,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
         <v>127581092</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>127585141</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>127504284</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>127580771</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,48 +2501,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127524724</v>
+        <v>127602573</v>
       </c>
       <c r="B19" t="n">
-        <v>75144</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464825</v>
+        <v>464867</v>
       </c>
       <c r="R19" t="n">
-        <v>6784652</v>
+        <v>6784461</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,19 +2578,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,28 +2594,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127503116</v>
+        <v>127602544</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79612</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,37 +2624,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464870</v>
+        <v>464858</v>
       </c>
       <c r="R20" t="n">
-        <v>6784516</v>
+        <v>6784447</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2676,19 +2684,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,75 +2700,67 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127602573</v>
+        <v>127524724</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>75147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464867</v>
+        <v>464825</v>
       </c>
       <c r="R21" t="n">
-        <v>6784461</v>
+        <v>6784652</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,14 +2787,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,29 +2808,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127602544</v>
+        <v>127503116</v>
       </c>
       <c r="B22" t="n">
-        <v>79609</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,40 +2837,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464858</v>
+        <v>464870</v>
       </c>
       <c r="R22" t="n">
-        <v>6784447</v>
+        <v>6784516</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2898,14 +2894,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2914,51 +2915,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127502954</v>
+        <v>127537979</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464884</v>
+        <v>464830</v>
       </c>
       <c r="R23" t="n">
-        <v>6784499</v>
+        <v>6784627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,32 +3040,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127547132</v>
+        <v>127502954</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464846</v>
+        <v>464884</v>
       </c>
       <c r="R24" t="n">
-        <v>6784631</v>
+        <v>6784499</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127537979</v>
+        <v>127547132</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464830</v>
+        <v>464846</v>
       </c>
       <c r="R25" t="n">
-        <v>6784627</v>
+        <v>6784631</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
         <v>127584626</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>127505499</v>
       </c>
       <c r="B28" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>127580438</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127503065</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>127503208</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>127601782</v>
       </c>
       <c r="B32" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>127567350</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B34" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R34" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B35" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R35" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127585927</v>
+        <v>127601649</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,37 +4337,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464839</v>
+        <v>464890</v>
       </c>
       <c r="R36" t="n">
-        <v>6784435</v>
+        <v>6784589</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4394,19 +4397,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,28 +4413,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4468,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R37" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127601649</v>
+        <v>127559415</v>
       </c>
       <c r="B38" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4551,40 +4550,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464890</v>
+        <v>464894</v>
       </c>
       <c r="R38" t="n">
-        <v>6784589</v>
+        <v>6784597</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4611,14 +4607,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,19 +4628,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4649,7 +4649,7 @@
         <v>127602118</v>
       </c>
       <c r="B39" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>127601608</v>
       </c>
       <c r="B40" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>127582358</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127580584</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127601312</v>
       </c>
       <c r="B44" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127602418</v>
+        <v>127507819</v>
       </c>
       <c r="B45" t="n">
-        <v>79052</v>
+        <v>75147</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,40 +5301,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464873</v>
+        <v>464858</v>
       </c>
       <c r="R45" t="n">
-        <v>6784704</v>
+        <v>6784650</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5361,14 +5358,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5377,29 +5379,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127507819</v>
+        <v>127539258</v>
       </c>
       <c r="B46" t="n">
-        <v>75144</v>
+        <v>79023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5407,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5431,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464858</v>
+        <v>464840</v>
       </c>
       <c r="R46" t="n">
-        <v>6784650</v>
+        <v>6784645</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,10 +5504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127539258</v>
+        <v>127602418</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5514,37 +5515,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464840</v>
+        <v>464873</v>
       </c>
       <c r="R47" t="n">
-        <v>6784645</v>
+        <v>6784704</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5571,19 +5575,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,18 +5591,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
         <v>127538460</v>
       </c>
       <c r="B48" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127503078</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>127528615</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127627233</v>
+        <v>127627267</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464804</v>
+        <v>464839</v>
       </c>
       <c r="R51" t="n">
-        <v>6784620</v>
+        <v>6784616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,11 +6005,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127627267</v>
+        <v>127627233</v>
       </c>
       <c r="B52" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6048,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464839</v>
+        <v>464804</v>
       </c>
       <c r="R52" t="n">
-        <v>6784616</v>
+        <v>6784620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,6 +6106,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6141,7 +6141,7 @@
         <v>127627395</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127627464</v>
+        <v>127627347</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464880</v>
+        <v>464841</v>
       </c>
       <c r="R54" t="n">
-        <v>6784448</v>
+        <v>6784551</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6345,10 +6345,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127627347</v>
+        <v>127626980</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464841</v>
+        <v>464883</v>
       </c>
       <c r="R55" t="n">
-        <v>6784551</v>
+        <v>6784583</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6419,11 +6419,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6451,10 +6446,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626980</v>
+        <v>127627464</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6489,10 +6484,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464883</v>
+        <v>464880</v>
       </c>
       <c r="R56" t="n">
-        <v>6784583</v>
+        <v>6784448</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6525,6 +6520,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,7 +6555,7 @@
         <v>127627419</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>127627476</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>127627244</v>
       </c>
       <c r="B59" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>127627165</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>127626973</v>
       </c>
       <c r="B61" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>127626997</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>127627349</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>127627375</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127627343</v>
+        <v>127627017</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464836</v>
+        <v>464871</v>
       </c>
       <c r="R65" t="n">
-        <v>6784540</v>
+        <v>6784599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7459,11 +7459,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7494,7 +7489,7 @@
         <v>127627035</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7592,10 +7587,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627017</v>
+        <v>127627343</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7630,10 +7625,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464871</v>
+        <v>464836</v>
       </c>
       <c r="R67" t="n">
-        <v>6784599</v>
+        <v>6784540</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7666,6 +7661,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7696,7 +7696,7 @@
         <v>127626939</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>127626956</v>
       </c>
       <c r="B69" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127626911</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>127627429</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>127627174</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>127627007</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>127627101</v>
       </c>
       <c r="B75" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8739,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627329</v>
+        <v>127627129</v>
       </c>
       <c r="B78" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464867</v>
+        <v>464866</v>
       </c>
       <c r="R78" t="n">
-        <v>6784590</v>
+        <v>6784700</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8840,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627129</v>
+        <v>127627329</v>
       </c>
       <c r="B79" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464866</v>
+        <v>464867</v>
       </c>
       <c r="R79" t="n">
-        <v>6784700</v>
+        <v>6784590</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
         <v>127627358</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>127626927</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>127627351</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127627454</v>
+        <v>127626967</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464860</v>
+        <v>464854</v>
       </c>
       <c r="R83" t="n">
-        <v>6784458</v>
+        <v>6784570</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9333,11 +9333,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9365,10 +9360,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127626967</v>
+        <v>127627454</v>
       </c>
       <c r="B84" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9376,21 +9371,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9403,10 +9398,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464854</v>
+        <v>464860</v>
       </c>
       <c r="R84" t="n">
-        <v>6784570</v>
+        <v>6784458</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9439,6 +9434,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9581,7 +9581,7 @@
         <v>127505687</v>
       </c>
       <c r="B86" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B88" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R88" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>79024</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R89" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10129,7 +10129,7 @@
         <v>127504671</v>
       </c>
       <c r="B91" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>127506640</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>127505537</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B95" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R95" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R96" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10805,7 +10805,7 @@
         <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>127504835</v>
       </c>
       <c r="B98" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>127565174</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>127504014</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>127706126</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11369,32 +11369,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127705341</v>
+        <v>127706377</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464871</v>
+        <v>464687</v>
       </c>
       <c r="R102" t="n">
-        <v>6784452</v>
+        <v>6784448</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127706377</v>
+        <v>127705454</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464687</v>
+        <v>464863</v>
       </c>
       <c r="R103" t="n">
-        <v>6784448</v>
+        <v>6784423</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127705454</v>
+        <v>127707616</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464863</v>
+        <v>464701</v>
       </c>
       <c r="R104" t="n">
-        <v>6784423</v>
+        <v>6784412</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11690,32 +11690,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127707616</v>
+        <v>127705341</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464701</v>
+        <v>464871</v>
       </c>
       <c r="R105" t="n">
-        <v>6784412</v>
+        <v>6784452</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11800,7 +11800,7 @@
         <v>127707829</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>127706778</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>127705423</v>
       </c>
       <c r="B110" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>127705998</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12439,10 +12439,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127706997</v>
+        <v>127704413</v>
       </c>
       <c r="B112" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464666</v>
+        <v>464906</v>
       </c>
       <c r="R112" t="n">
-        <v>6784496</v>
+        <v>6784432</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12546,10 +12546,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127704413</v>
+        <v>127704473</v>
       </c>
       <c r="B113" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464906</v>
+        <v>464897</v>
       </c>
       <c r="R113" t="n">
-        <v>6784432</v>
+        <v>6784413</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12653,10 +12653,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127704473</v>
+        <v>127706997</v>
       </c>
       <c r="B114" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12664,21 +12664,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464897</v>
+        <v>464666</v>
       </c>
       <c r="R114" t="n">
-        <v>6784413</v>
+        <v>6784496</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12763,7 +12763,7 @@
         <v>127706073</v>
       </c>
       <c r="B115" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>127707041</v>
       </c>
       <c r="B116" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>127706768</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>127705869</v>
       </c>
       <c r="B118" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>127705109</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>127705654</v>
       </c>
       <c r="B120" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>127704405</v>
       </c>
       <c r="B121" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>127704457</v>
       </c>
       <c r="B122" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>127707956</v>
       </c>
       <c r="B123" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13743,32 +13743,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127707246</v>
+        <v>127707282</v>
       </c>
       <c r="B124" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13778,10 +13778,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464652</v>
+        <v>464658</v>
       </c>
       <c r="R124" t="n">
-        <v>6784464</v>
+        <v>6784455</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13850,32 +13850,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127707282</v>
+        <v>127707246</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464658</v>
+        <v>464652</v>
       </c>
       <c r="R125" t="n">
-        <v>6784455</v>
+        <v>6784464</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13960,7 +13960,7 @@
         <v>127707368</v>
       </c>
       <c r="B126" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>127705832</v>
       </c>
       <c r="B127" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>127707123</v>
       </c>
       <c r="B128" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>127705062</v>
       </c>
       <c r="B129" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>127705893</v>
       </c>
       <c r="B130" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>127706848</v>
       </c>
       <c r="B131" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>127707939</v>
       </c>
       <c r="B133" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14813,10 +14813,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127721029</v>
+        <v>127719564</v>
       </c>
       <c r="B134" t="n">
-        <v>79020</v>
+        <v>79612</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14824,37 +14824,40 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464816</v>
+        <v>464859</v>
       </c>
       <c r="R134" t="n">
-        <v>6784317</v>
+        <v>6784218</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14881,19 +14884,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14902,28 +14900,29 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127715439</v>
+        <v>127721029</v>
       </c>
       <c r="B135" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14955,10 +14954,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464832</v>
+        <v>464816</v>
       </c>
       <c r="R135" t="n">
-        <v>6784214</v>
+        <v>6784317</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15030,7 +15029,7 @@
         <v>127714234</v>
       </c>
       <c r="B136" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15137,7 +15136,7 @@
         <v>127720285</v>
       </c>
       <c r="B137" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15249,7 +15248,7 @@
         <v>127715198</v>
       </c>
       <c r="B138" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15353,32 +15352,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127718498</v>
+        <v>127715439</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15388,13 +15387,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464686</v>
+        <v>464832</v>
       </c>
       <c r="R139" t="n">
-        <v>6784147</v>
+        <v>6784214</v>
       </c>
       <c r="S139" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15460,51 +15459,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127719564</v>
+        <v>127718498</v>
       </c>
       <c r="B140" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464859</v>
+        <v>464686</v>
       </c>
       <c r="R140" t="n">
-        <v>6784218</v>
+        <v>6784147</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15531,14 +15527,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15547,19 +15548,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
         <v>127715717</v>
       </c>
       <c r="B141" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>127718502</v>
       </c>
       <c r="B142" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>127718980</v>
       </c>
       <c r="B143" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15887,10 +15887,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127719996</v>
+        <v>127719621</v>
       </c>
       <c r="B144" t="n">
-        <v>57823</v>
+        <v>78782</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15898,46 +15898,40 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464615</v>
+        <v>464775</v>
       </c>
       <c r="R144" t="n">
-        <v>6784345</v>
+        <v>6784302</v>
       </c>
       <c r="S144" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15964,19 +15958,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15985,28 +15974,29 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127719621</v>
+        <v>127719996</v>
       </c>
       <c r="B145" t="n">
-        <v>78779</v>
+        <v>57826</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16014,40 +16004,46 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464775</v>
+        <v>464615</v>
       </c>
       <c r="R145" t="n">
-        <v>6784302</v>
+        <v>6784345</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16074,14 +16070,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16090,19 +16091,18 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
         <v>127715912</v>
       </c>
       <c r="B146" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>127714269</v>
       </c>
       <c r="B147" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>127718380</v>
       </c>
       <c r="B148" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>127719855</v>
       </c>
       <c r="B149" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>127715006</v>
       </c>
       <c r="B150" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>127715519</v>
       </c>
       <c r="B151" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>127718190</v>
       </c>
       <c r="B152" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16863,48 +16863,57 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127718021</v>
+        <v>127719421</v>
       </c>
       <c r="B153" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464701</v>
+        <v>464871</v>
       </c>
       <c r="R153" t="n">
-        <v>6784168</v>
+        <v>6784277</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16931,19 +16940,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På 2 torrtallar, en tallåga</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16952,28 +16956,29 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127719463</v>
+        <v>127718021</v>
       </c>
       <c r="B154" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16999,22 +17004,19 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464867</v>
+        <v>464701</v>
       </c>
       <c r="R154" t="n">
-        <v>6784270</v>
+        <v>6784168</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17041,14 +17043,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17057,62 +17064,55 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127719421</v>
+        <v>127719463</v>
       </c>
       <c r="B155" t="n">
-        <v>8450</v>
+        <v>78782</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464871</v>
+        <v>464867</v>
       </c>
       <c r="R155" t="n">
-        <v>6784277</v>
+        <v>6784270</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På 2 torrtallar, en tallåga</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17188,10 +17188,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719674</v>
+        <v>127719947</v>
       </c>
       <c r="B156" t="n">
-        <v>79052</v>
+        <v>79641</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,40 +17199,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464745</v>
+        <v>464623</v>
       </c>
       <c r="R156" t="n">
-        <v>6784305</v>
+        <v>6784354</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17259,14 +17256,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17275,29 +17277,28 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127719947</v>
+        <v>127717666</v>
       </c>
       <c r="B157" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17329,10 +17330,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464623</v>
+        <v>464682</v>
       </c>
       <c r="R157" t="n">
-        <v>6784354</v>
+        <v>6784195</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17401,10 +17402,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127717666</v>
+        <v>127719674</v>
       </c>
       <c r="B158" t="n">
-        <v>79638</v>
+        <v>79055</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17412,37 +17413,40 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464682</v>
+        <v>464745</v>
       </c>
       <c r="R158" t="n">
-        <v>6784195</v>
+        <v>6784305</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17469,19 +17473,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17490,18 +17489,19 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
         <v>127719762</v>
       </c>
       <c r="B159" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17614,10 +17614,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127719525</v>
+        <v>127714369</v>
       </c>
       <c r="B160" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17625,40 +17625,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464859</v>
+        <v>464931</v>
       </c>
       <c r="R160" t="n">
-        <v>6784218</v>
+        <v>6784233</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17685,14 +17682,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17701,29 +17703,28 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127714657</v>
+        <v>127719525</v>
       </c>
       <c r="B161" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17731,37 +17732,40 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464858</v>
+        <v>464859</v>
       </c>
       <c r="R161" t="n">
-        <v>6784259</v>
+        <v>6784218</v>
       </c>
       <c r="S161" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17788,19 +17792,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17809,28 +17808,29 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127714369</v>
+        <v>127714657</v>
       </c>
       <c r="B162" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17862,13 +17862,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>464931</v>
+        <v>464858</v>
       </c>
       <c r="R162" t="n">
-        <v>6784233</v>
+        <v>6784259</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17934,48 +17934,51 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127716709</v>
+        <v>127719588</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>78782</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R163" t="n">
-        <v>6784275</v>
+        <v>6784242</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18002,19 +18005,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18023,28 +18021,29 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127719588</v>
+        <v>127718357</v>
       </c>
       <c r="B164" t="n">
-        <v>78779</v>
+        <v>79612</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18052,40 +18051,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>464844</v>
+        <v>464664</v>
       </c>
       <c r="R164" t="n">
-        <v>6784242</v>
+        <v>6784142</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18112,14 +18108,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18128,51 +18129,50 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127718357</v>
+        <v>127716709</v>
       </c>
       <c r="B165" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18182,10 +18182,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464664</v>
+        <v>464710</v>
       </c>
       <c r="R165" t="n">
-        <v>6784142</v>
+        <v>6784275</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18257,7 +18257,7 @@
         <v>127714909</v>
       </c>
       <c r="B166" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>127718026</v>
       </c>
       <c r="B167" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>127720039</v>
       </c>
       <c r="B168" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127714955</v>
+        <v>127716661</v>
       </c>
       <c r="B169" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18591,34 +18591,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R169" t="n">
-        <v>6784281</v>
+        <v>6784275</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18687,10 +18692,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127715185</v>
+        <v>127714955</v>
       </c>
       <c r="B170" t="n">
-        <v>79609</v>
+        <v>78782</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18698,21 +18703,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18722,10 +18727,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464836</v>
+        <v>464844</v>
       </c>
       <c r="R170" t="n">
-        <v>6784199</v>
+        <v>6784281</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18794,10 +18799,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127716661</v>
+        <v>127715185</v>
       </c>
       <c r="B171" t="n">
-        <v>57660</v>
+        <v>79612</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18805,39 +18810,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464710</v>
+        <v>464836</v>
       </c>
       <c r="R171" t="n">
-        <v>6784275</v>
+        <v>6784199</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,10 +18906,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127718375</v>
+        <v>127718015</v>
       </c>
       <c r="B172" t="n">
-        <v>79638</v>
+        <v>79612</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18917,21 +18917,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18941,10 +18941,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464664</v>
+        <v>464701</v>
       </c>
       <c r="R172" t="n">
-        <v>6784142</v>
+        <v>6784168</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19013,10 +19013,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127719813</v>
+        <v>127719816</v>
       </c>
       <c r="B173" t="n">
-        <v>79638</v>
+        <v>79612</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,37 +19024,40 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464647</v>
+        <v>464752</v>
       </c>
       <c r="R173" t="n">
-        <v>6784377</v>
+        <v>6784264</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19081,19 +19084,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19102,50 +19100,51 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127720766</v>
+        <v>127719841</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79612</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19155,10 +19154,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>464581</v>
+        <v>464647</v>
       </c>
       <c r="R174" t="n">
-        <v>6784393</v>
+        <v>6784377</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19227,10 +19226,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127718015</v>
+        <v>127718375</v>
       </c>
       <c r="B175" t="n">
-        <v>79609</v>
+        <v>79641</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19238,21 +19237,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19262,10 +19261,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464701</v>
+        <v>464664</v>
       </c>
       <c r="R175" t="n">
-        <v>6784168</v>
+        <v>6784142</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19334,10 +19333,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127719816</v>
+        <v>127719813</v>
       </c>
       <c r="B176" t="n">
-        <v>79609</v>
+        <v>79641</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19345,40 +19344,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464752</v>
+        <v>464647</v>
       </c>
       <c r="R176" t="n">
-        <v>6784264</v>
+        <v>6784377</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19405,14 +19401,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19421,51 +19422,50 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127719841</v>
+        <v>127720766</v>
       </c>
       <c r="B177" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464647</v>
+        <v>464581</v>
       </c>
       <c r="R177" t="n">
-        <v>6784377</v>
+        <v>6784393</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19547,10 +19547,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127718840</v>
+        <v>127714169</v>
       </c>
       <c r="B178" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19558,42 +19558,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>464588</v>
+        <v>464951</v>
       </c>
       <c r="R178" t="n">
-        <v>6784281</v>
+        <v>6784236</v>
       </c>
       <c r="S178" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19622,7 +19617,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19632,7 +19627,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19659,10 +19654,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127714169</v>
+        <v>127718840</v>
       </c>
       <c r="B179" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19670,37 +19665,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>464951</v>
+        <v>464588</v>
       </c>
       <c r="R179" t="n">
-        <v>6784236</v>
+        <v>6784281</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19766,10 +19766,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127719298</v>
+        <v>127719838</v>
       </c>
       <c r="B180" t="n">
-        <v>57660</v>
+        <v>78782</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19777,45 +19777,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>464943</v>
+        <v>464647</v>
       </c>
       <c r="R180" t="n">
-        <v>6784241</v>
+        <v>6784377</v>
       </c>
       <c r="S180" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19842,9 +19834,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19859,22 +19861,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127718884</v>
+        <v>127719298</v>
       </c>
       <c r="B181" t="n">
-        <v>57790</v>
+        <v>57663</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19882,42 +19884,45 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>103035</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>464607</v>
+        <v>464943</v>
       </c>
       <c r="R181" t="n">
-        <v>6784297</v>
+        <v>6784241</v>
       </c>
       <c r="S181" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19944,19 +19949,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19971,69 +19966,65 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127719338</v>
+        <v>127718884</v>
       </c>
       <c r="B182" t="n">
-        <v>8450</v>
+        <v>57793</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>103035</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464893</v>
+        <v>464607</v>
       </c>
       <c r="R182" t="n">
-        <v>6784258</v>
+        <v>6784297</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20060,78 +20051,96 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127719838</v>
+        <v>127719338</v>
       </c>
       <c r="B183" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>464647</v>
+        <v>464893</v>
       </c>
       <c r="R183" t="n">
-        <v>6784377</v>
+        <v>6784258</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20158,39 +20167,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20200,7 +20200,7 @@
         <v>127715270</v>
       </c>
       <c r="B184" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>127719747</v>
       </c>
       <c r="B186" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>127716097</v>
       </c>
       <c r="B187" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20630,10 +20630,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127715332</v>
+        <v>127718968</v>
       </c>
       <c r="B188" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20641,21 +20641,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20665,10 +20665,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464836</v>
+        <v>464628</v>
       </c>
       <c r="R188" t="n">
-        <v>6784193</v>
+        <v>6784279</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20737,10 +20737,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127718968</v>
+        <v>127715332</v>
       </c>
       <c r="B189" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20748,21 +20748,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20772,10 +20772,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>464628</v>
+        <v>464836</v>
       </c>
       <c r="R189" t="n">
-        <v>6784279</v>
+        <v>6784193</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20847,7 +20847,7 @@
         <v>127719836</v>
       </c>
       <c r="B190" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>127719877</v>
       </c>
       <c r="B191" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21051,10 +21051,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127714444</v>
+        <v>127717898</v>
       </c>
       <c r="B192" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21062,21 +21062,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464913</v>
+        <v>464701</v>
       </c>
       <c r="R192" t="n">
-        <v>6784254</v>
+        <v>6784168</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21268,7 +21268,7 @@
         <v>127719210</v>
       </c>
       <c r="B194" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21371,10 +21371,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127717898</v>
+        <v>127714444</v>
       </c>
       <c r="B195" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21382,21 +21382,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464701</v>
+        <v>464913</v>
       </c>
       <c r="R195" t="n">
-        <v>6784168</v>
+        <v>6784254</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21481,7 +21481,7 @@
         <v>127717085</v>
       </c>
       <c r="B196" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>127717016</v>
       </c>
       <c r="B197" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>127719863</v>
       </c>
       <c r="B198" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>127718180</v>
       </c>
       <c r="B199" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21915,53 +21915,48 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127706550</v>
+        <v>127707668</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464683</v>
+        <v>464689</v>
       </c>
       <c r="R200" t="n">
-        <v>6784461</v>
+        <v>6784378</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22005,7 +22000,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22014,7 +22009,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22033,10 +22027,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127707668</v>
+        <v>127708066</v>
       </c>
       <c r="B201" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22068,13 +22062,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464689</v>
+        <v>464699</v>
       </c>
       <c r="R201" t="n">
-        <v>6784378</v>
+        <v>6784396</v>
       </c>
       <c r="S201" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22118,7 +22112,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22145,10 +22139,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127708066</v>
+        <v>127718813</v>
       </c>
       <c r="B202" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22180,13 +22174,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464699</v>
+        <v>464588</v>
       </c>
       <c r="R202" t="n">
-        <v>6784396</v>
+        <v>6784281</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22210,27 +22204,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>2 bilder, rikligt på tall</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22257,48 +22251,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127718813</v>
+        <v>127706550</v>
       </c>
       <c r="B203" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464588</v>
+        <v>464683</v>
       </c>
       <c r="R203" t="n">
-        <v>6784281</v>
+        <v>6784461</v>
       </c>
       <c r="S203" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22322,27 +22321,27 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22351,6 +22350,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -22372,7 +22372,7 @@
         <v>127717251</v>
       </c>
       <c r="B204" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>127718352</v>
       </c>
       <c r="B205" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>127707057</v>
       </c>
       <c r="B206" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>127706968</v>
       </c>
       <c r="B207" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>127716564</v>
       </c>
       <c r="B208" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>127718964</v>
       </c>
       <c r="B209" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>127751842</v>
       </c>
       <c r="B210" t="n">
-        <v>91568</v>
+        <v>91571</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>127720341</v>
       </c>
       <c r="B211" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>127719613</v>
       </c>
       <c r="B212" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>127719544</v>
       </c>
       <c r="B214" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23612,10 +23612,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127719315</v>
+        <v>127717659</v>
       </c>
       <c r="B215" t="n">
-        <v>79020</v>
+        <v>79612</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23623,21 +23623,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>464650</v>
+        <v>464682</v>
       </c>
       <c r="R215" t="n">
-        <v>6784317</v>
+        <v>6784195</v>
       </c>
       <c r="S215" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
+          <t>2 bilder på 2 stubbar</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23724,10 +23724,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127717659</v>
+        <v>127719315</v>
       </c>
       <c r="B216" t="n">
-        <v>79609</v>
+        <v>79023</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23735,21 +23735,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>464682</v>
+        <v>464650</v>
       </c>
       <c r="R216" t="n">
-        <v>6784195</v>
+        <v>6784317</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>2 bilder på 2 stubbar</t>
+          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23839,7 +23839,7 @@
         <v>127718616</v>
       </c>
       <c r="B217" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>127716791</v>
       </c>
       <c r="B218" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>127717010</v>
       </c>
       <c r="B219" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>127716476</v>
       </c>
       <c r="B220" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24288,50 +24288,53 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127707455</v>
+        <v>127707530</v>
       </c>
       <c r="B221" t="n">
-        <v>57663</v>
+        <v>56858</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>464669</v>
+        <v>464686</v>
       </c>
       <c r="R221" t="n">
-        <v>6784449</v>
+        <v>6784430</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24378,7 +24381,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Spillning under tall med en vit påläggning på stammen</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24405,53 +24408,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127707530</v>
+        <v>127707455</v>
       </c>
       <c r="B222" t="n">
-        <v>56855</v>
+        <v>57666</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464686</v>
+        <v>464669</v>
       </c>
       <c r="R222" t="n">
-        <v>6784430</v>
+        <v>6784449</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Spillning under tall med en vit påläggning på stammen</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24528,7 +24528,7 @@
         <v>127705327</v>
       </c>
       <c r="B223" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>127705478</v>
       </c>
       <c r="B224" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24762,10 +24762,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127714858</v>
+        <v>127719810</v>
       </c>
       <c r="B225" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24773,21 +24773,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24797,10 +24797,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464856</v>
+        <v>464647</v>
       </c>
       <c r="R225" t="n">
-        <v>6784268</v>
+        <v>6784377</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24847,7 +24847,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild band i bakgrund</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24874,10 +24874,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127716937</v>
+        <v>127714858</v>
       </c>
       <c r="B226" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24909,10 +24909,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464680</v>
+        <v>464856</v>
       </c>
       <c r="R226" t="n">
-        <v>6784254</v>
+        <v>6784268</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24959,7 +24959,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24986,10 +24986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127719810</v>
+        <v>127716937</v>
       </c>
       <c r="B227" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24997,21 +24997,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25021,10 +25021,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464647</v>
+        <v>464680</v>
       </c>
       <c r="R227" t="n">
-        <v>6784377</v>
+        <v>6784254</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25071,7 +25071,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25101,7 +25101,7 @@
         <v>127717066</v>
       </c>
       <c r="B228" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>127707100</v>
       </c>
       <c r="B229" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>127719942</v>
       </c>
       <c r="B230" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>127714717</v>
       </c>
       <c r="B231" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>127793591</v>
       </c>
       <c r="B232" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127511371</v>
+        <v>127554096</v>
       </c>
       <c r="B2" t="n">
-        <v>75147</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R2" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127554096</v>
+        <v>127511371</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>75153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R3" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127503574</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,40 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R5" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,14 +1064,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,29 +1085,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B6" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R6" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,14 +1171,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,19 +1192,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1211,7 +1213,7 @@
         <v>127566254</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1320,7 @@
         <v>127505584</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127503663</v>
+        <v>127601236</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,37 +1435,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464847</v>
+        <v>464862</v>
       </c>
       <c r="R9" t="n">
-        <v>6784531</v>
+        <v>6784534</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,19 +1495,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,28 +1511,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127536063</v>
+        <v>127602494</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,37 +1541,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464819</v>
+        <v>464821</v>
       </c>
       <c r="R10" t="n">
-        <v>6784639</v>
+        <v>6784490</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,19 +1601,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,18 +1617,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127518186</v>
       </c>
       <c r="B11" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127601675</v>
+        <v>127503996</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,40 +1754,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464886</v>
+        <v>464844</v>
       </c>
       <c r="R12" t="n">
-        <v>6784594</v>
+        <v>6784533</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,14 +1811,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,29 +1832,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127503996</v>
+        <v>127601675</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,37 +1861,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464844</v>
+        <v>464886</v>
       </c>
       <c r="R13" t="n">
-        <v>6784533</v>
+        <v>6784594</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,19 +1921,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,18 +1937,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
         <v>127581092</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>127585141</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>127504284</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,48 +2394,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127580771</v>
+        <v>127602573</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464785</v>
+        <v>464867</v>
       </c>
       <c r="R18" t="n">
-        <v>6784477</v>
+        <v>6784461</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2462,19 +2471,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,75 +2487,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127602573</v>
+        <v>127580771</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464867</v>
+        <v>464785</v>
       </c>
       <c r="R19" t="n">
-        <v>6784461</v>
+        <v>6784477</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2578,14 +2574,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,29 +2595,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127602544</v>
+        <v>127524724</v>
       </c>
       <c r="B20" t="n">
-        <v>79612</v>
+        <v>75153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,40 +2624,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464858</v>
+        <v>464825</v>
       </c>
       <c r="R20" t="n">
-        <v>6784447</v>
+        <v>6784652</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2684,14 +2681,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,29 +2702,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B21" t="n">
-        <v>75147</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2731,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R21" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127503116</v>
+        <v>127602544</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,37 +2838,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464870</v>
+        <v>464858</v>
       </c>
       <c r="R22" t="n">
-        <v>6784516</v>
+        <v>6784447</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2894,19 +2898,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,50 +2914,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127537979</v>
+        <v>127502954</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464830</v>
+        <v>464884</v>
       </c>
       <c r="R23" t="n">
-        <v>6784627</v>
+        <v>6784499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,32 +3040,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127502954</v>
+        <v>127547132</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464884</v>
+        <v>464846</v>
       </c>
       <c r="R24" t="n">
-        <v>6784499</v>
+        <v>6784631</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127547132</v>
+        <v>127537979</v>
       </c>
       <c r="B25" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464846</v>
+        <v>464830</v>
       </c>
       <c r="R25" t="n">
-        <v>6784631</v>
+        <v>6784627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R27" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B28" t="n">
-        <v>79612</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
         <v>127580438</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>127503065</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>127503208</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>127601782</v>
       </c>
       <c r="B32" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127567350</v>
+        <v>127602770</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,37 +4018,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464790</v>
+        <v>464833</v>
       </c>
       <c r="R33" t="n">
-        <v>6784508</v>
+        <v>6784487</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4075,19 +4078,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4096,28 +4094,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B34" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4152,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R34" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,10 +4219,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602073</v>
+        <v>127567350</v>
       </c>
       <c r="B35" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,40 +4230,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464813</v>
+        <v>464790</v>
       </c>
       <c r="R35" t="n">
-        <v>6784586</v>
+        <v>6784508</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4291,14 +4287,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,19 +4308,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4329,7 +4329,7 @@
         <v>127601649</v>
       </c>
       <c r="B36" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>127585927</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>127559415</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>127602118</v>
       </c>
       <c r="B39" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>127601608</v>
       </c>
       <c r="B40" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>127582358</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127580584</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127601312</v>
       </c>
       <c r="B44" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127507819</v>
+        <v>127602418</v>
       </c>
       <c r="B45" t="n">
-        <v>75147</v>
+        <v>79061</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,37 +5301,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464858</v>
+        <v>464873</v>
       </c>
       <c r="R45" t="n">
-        <v>6784650</v>
+        <v>6784704</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5358,19 +5361,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5379,28 +5377,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127539258</v>
+        <v>127507819</v>
       </c>
       <c r="B46" t="n">
-        <v>79023</v>
+        <v>75153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5407,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464840</v>
+        <v>464858</v>
       </c>
       <c r="R46" t="n">
-        <v>6784645</v>
+        <v>6784650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5504,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127602418</v>
+        <v>127539258</v>
       </c>
       <c r="B47" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,40 +5514,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464873</v>
+        <v>464840</v>
       </c>
       <c r="R47" t="n">
-        <v>6784704</v>
+        <v>6784645</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5575,14 +5571,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5591,19 +5592,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
         <v>127538460</v>
       </c>
       <c r="B48" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127503078</v>
       </c>
       <c r="B49" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>127528615</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127627267</v>
+        <v>127627233</v>
       </c>
       <c r="B51" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464839</v>
+        <v>464804</v>
       </c>
       <c r="R51" t="n">
-        <v>6784616</v>
+        <v>6784620</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,6 +6005,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6037,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127627233</v>
+        <v>127627267</v>
       </c>
       <c r="B52" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464804</v>
+        <v>464839</v>
       </c>
       <c r="R52" t="n">
-        <v>6784620</v>
+        <v>6784616</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,11 +6111,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6141,7 +6141,7 @@
         <v>127627395</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>127627347</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>127626980</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>127627464</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127627419</v>
+        <v>127627244</v>
       </c>
       <c r="B57" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464828</v>
+        <v>464822</v>
       </c>
       <c r="R57" t="n">
-        <v>6784480</v>
+        <v>6784620</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,11 +6626,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6658,10 +6653,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127627476</v>
+        <v>127627419</v>
       </c>
       <c r="B58" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464889</v>
+        <v>464828</v>
       </c>
       <c r="R58" t="n">
-        <v>6784444</v>
+        <v>6784480</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6736,7 +6731,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6764,10 +6759,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127627244</v>
+        <v>127627476</v>
       </c>
       <c r="B59" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,21 +6770,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6802,10 +6797,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464822</v>
+        <v>464889</v>
       </c>
       <c r="R59" t="n">
-        <v>6784620</v>
+        <v>6784444</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6838,6 +6833,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R60" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B61" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R61" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,7 +7070,7 @@
         <v>127626997</v>
       </c>
       <c r="B62" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>127627349</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>127627375</v>
       </c>
       <c r="B64" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127627017</v>
+        <v>127627035</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464871</v>
+        <v>464881</v>
       </c>
       <c r="R65" t="n">
-        <v>6784599</v>
+        <v>6784597</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627035</v>
+        <v>127627343</v>
       </c>
       <c r="B66" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464881</v>
+        <v>464836</v>
       </c>
       <c r="R66" t="n">
-        <v>6784597</v>
+        <v>6784540</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7560,6 +7560,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7587,10 +7592,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127627343</v>
+        <v>127627017</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7625,10 +7630,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464836</v>
+        <v>464871</v>
       </c>
       <c r="R67" t="n">
-        <v>6784540</v>
+        <v>6784599</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,11 +7666,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7693,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,21 +7704,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,11 +7769,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7799,10 +7794,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B69" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,21 +7805,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7875,6 +7870,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>127626911</v>
       </c>
       <c r="B70" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>127627429</v>
       </c>
       <c r="B71" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627174</v>
+        <v>127627007</v>
       </c>
       <c r="B72" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464796</v>
+        <v>464841</v>
       </c>
       <c r="R72" t="n">
-        <v>6784631</v>
+        <v>6784612</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,6 +8186,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,10 +8218,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8251,10 +8256,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R73" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,11 +8292,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,7 +8434,7 @@
         <v>127627101</v>
       </c>
       <c r="B75" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627383</v>
+        <v>127627129</v>
       </c>
       <c r="B76" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464805</v>
+        <v>464866</v>
       </c>
       <c r="R76" t="n">
-        <v>6784486</v>
+        <v>6784700</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627242</v>
+        <v>127627329</v>
       </c>
       <c r="B77" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464822</v>
+        <v>464867</v>
       </c>
       <c r="R77" t="n">
-        <v>6784620</v>
+        <v>6784590</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,11 +8707,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8739,10 +8734,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627129</v>
+        <v>127627383</v>
       </c>
       <c r="B78" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8750,21 +8745,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8777,10 +8772,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464866</v>
+        <v>464805</v>
       </c>
       <c r="R78" t="n">
-        <v>6784700</v>
+        <v>6784486</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8840,10 +8835,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627329</v>
+        <v>127627242</v>
       </c>
       <c r="B79" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8851,21 +8846,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8878,10 +8873,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464867</v>
+        <v>464822</v>
       </c>
       <c r="R79" t="n">
-        <v>6784590</v>
+        <v>6784620</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8914,6 +8909,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8941,10 +8941,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127627358</v>
+        <v>127626927</v>
       </c>
       <c r="B80" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464792</v>
+        <v>464868</v>
       </c>
       <c r="R80" t="n">
-        <v>6784524</v>
+        <v>6784557</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9047,10 +9047,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127626927</v>
+        <v>127627358</v>
       </c>
       <c r="B81" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464868</v>
+        <v>464792</v>
       </c>
       <c r="R81" t="n">
-        <v>6784557</v>
+        <v>6784524</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9153,10 +9153,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127627351</v>
+        <v>127626967</v>
       </c>
       <c r="B82" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9191,10 +9191,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464813</v>
+        <v>464854</v>
       </c>
       <c r="R82" t="n">
-        <v>6784554</v>
+        <v>6784570</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9227,11 +9227,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9259,10 +9254,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127626967</v>
+        <v>127627351</v>
       </c>
       <c r="B83" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9270,21 +9265,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9297,10 +9292,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464854</v>
+        <v>464813</v>
       </c>
       <c r="R83" t="n">
-        <v>6784570</v>
+        <v>6784554</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9333,6 +9328,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9363,7 +9363,7 @@
         <v>127627454</v>
       </c>
       <c r="B84" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>127505687</v>
       </c>
       <c r="B86" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B88" t="n">
-        <v>79023</v>
+        <v>79030</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R88" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B89" t="n">
-        <v>79024</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R89" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10129,7 +10129,7 @@
         <v>127504671</v>
       </c>
       <c r="B91" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>127506640</v>
       </c>
       <c r="B92" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>127505537</v>
       </c>
       <c r="B93" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B95" t="n">
-        <v>79023</v>
+        <v>91369</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R95" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B96" t="n">
-        <v>91361</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R96" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10805,7 +10805,7 @@
         <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>127504835</v>
       </c>
       <c r="B98" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>127565174</v>
       </c>
       <c r="B99" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>127504014</v>
       </c>
       <c r="B100" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>127706126</v>
       </c>
       <c r="B101" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>127706377</v>
       </c>
       <c r="B102" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>127705454</v>
       </c>
       <c r="B103" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>127707616</v>
       </c>
       <c r="B104" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11797,10 +11797,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127707829</v>
+        <v>127707823</v>
       </c>
       <c r="B106" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>127706778</v>
       </c>
       <c r="B107" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>127705423</v>
       </c>
       <c r="B110" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>127705998</v>
       </c>
       <c r="B111" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>127704413</v>
       </c>
       <c r="B112" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>127704473</v>
       </c>
       <c r="B113" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>127706997</v>
       </c>
       <c r="B114" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>127706073</v>
       </c>
       <c r="B115" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>127707041</v>
       </c>
       <c r="B116" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>127706768</v>
       </c>
       <c r="B117" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>127705869</v>
       </c>
       <c r="B118" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>127705109</v>
       </c>
       <c r="B119" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>127705654</v>
       </c>
       <c r="B120" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>127704405</v>
       </c>
       <c r="B121" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>127704457</v>
       </c>
       <c r="B122" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>127707956</v>
       </c>
       <c r="B123" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13743,32 +13743,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127707282</v>
+        <v>127707246</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13778,10 +13778,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464658</v>
+        <v>464652</v>
       </c>
       <c r="R124" t="n">
-        <v>6784455</v>
+        <v>6784464</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13850,32 +13850,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127707246</v>
+        <v>127707282</v>
       </c>
       <c r="B125" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464652</v>
+        <v>464658</v>
       </c>
       <c r="R125" t="n">
-        <v>6784464</v>
+        <v>6784455</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13957,10 +13957,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127707368</v>
+        <v>127707123</v>
       </c>
       <c r="B126" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464658</v>
+        <v>464660</v>
       </c>
       <c r="R126" t="n">
-        <v>6784455</v>
+        <v>6784477</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14064,10 +14064,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127705832</v>
+        <v>127707368</v>
       </c>
       <c r="B127" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464736</v>
+        <v>464658</v>
       </c>
       <c r="R127" t="n">
-        <v>6784473</v>
+        <v>6784455</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14171,10 +14171,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127707123</v>
+        <v>127705832</v>
       </c>
       <c r="B128" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14206,10 +14206,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464660</v>
+        <v>464736</v>
       </c>
       <c r="R128" t="n">
-        <v>6784477</v>
+        <v>6784473</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14281,7 +14281,7 @@
         <v>127705062</v>
       </c>
       <c r="B129" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>127705893</v>
       </c>
       <c r="B130" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>127706848</v>
       </c>
       <c r="B131" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14599,32 +14599,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127706356</v>
+        <v>127707939</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14634,10 +14634,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464687</v>
+        <v>464707</v>
       </c>
       <c r="R132" t="n">
-        <v>6784448</v>
+        <v>6784355</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14706,32 +14706,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127707939</v>
+        <v>127706356</v>
       </c>
       <c r="B133" t="n">
-        <v>79612</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14741,10 +14741,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464707</v>
+        <v>464687</v>
       </c>
       <c r="R133" t="n">
-        <v>6784355</v>
+        <v>6784448</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14813,10 +14813,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127719564</v>
+        <v>127715439</v>
       </c>
       <c r="B134" t="n">
-        <v>79612</v>
+        <v>79029</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14824,40 +14824,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464859</v>
+        <v>464832</v>
       </c>
       <c r="R134" t="n">
-        <v>6784218</v>
+        <v>6784214</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14884,14 +14881,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14900,19 +14902,18 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14922,7 +14923,7 @@
         <v>127721029</v>
       </c>
       <c r="B135" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15029,7 +15030,7 @@
         <v>127714234</v>
       </c>
       <c r="B136" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15136,7 +15137,7 @@
         <v>127720285</v>
       </c>
       <c r="B137" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15248,7 +15249,7 @@
         <v>127715198</v>
       </c>
       <c r="B138" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15352,32 +15353,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127715439</v>
+        <v>127718498</v>
       </c>
       <c r="B139" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15387,13 +15388,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464832</v>
+        <v>464686</v>
       </c>
       <c r="R139" t="n">
-        <v>6784214</v>
+        <v>6784147</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15459,48 +15460,51 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127718498</v>
+        <v>127719564</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464686</v>
+        <v>464859</v>
       </c>
       <c r="R140" t="n">
-        <v>6784147</v>
+        <v>6784218</v>
       </c>
       <c r="S140" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15527,19 +15531,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15548,18 +15547,19 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
         <v>127715717</v>
       </c>
       <c r="B141" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15673,10 +15673,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127718502</v>
+        <v>127719996</v>
       </c>
       <c r="B142" t="n">
-        <v>79023</v>
+        <v>57832</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15684,34 +15684,43 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464686</v>
+        <v>464615</v>
       </c>
       <c r="R142" t="n">
-        <v>6784147</v>
+        <v>6784345</v>
       </c>
       <c r="S142" t="n">
         <v>50</v>
@@ -15780,10 +15789,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127718980</v>
+        <v>127718502</v>
       </c>
       <c r="B143" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15815,13 +15824,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464628</v>
+        <v>464686</v>
       </c>
       <c r="R143" t="n">
-        <v>6784279</v>
+        <v>6784147</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15887,10 +15896,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127719621</v>
+        <v>127718980</v>
       </c>
       <c r="B144" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15898,40 +15907,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464775</v>
+        <v>464628</v>
       </c>
       <c r="R144" t="n">
-        <v>6784302</v>
+        <v>6784279</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15958,14 +15964,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15974,29 +15985,28 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127719996</v>
+        <v>127719621</v>
       </c>
       <c r="B145" t="n">
-        <v>57826</v>
+        <v>78788</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16004,46 +16014,40 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464615</v>
+        <v>464775</v>
       </c>
       <c r="R145" t="n">
-        <v>6784345</v>
+        <v>6784302</v>
       </c>
       <c r="S145" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16070,19 +16074,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16091,28 +16090,29 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127715912</v>
+        <v>127714269</v>
       </c>
       <c r="B146" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16144,10 +16144,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>464770</v>
+        <v>464939</v>
       </c>
       <c r="R146" t="n">
-        <v>6784253</v>
+        <v>6784225</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16216,10 +16216,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127714269</v>
+        <v>127715912</v>
       </c>
       <c r="B147" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464939</v>
+        <v>464770</v>
       </c>
       <c r="R147" t="n">
-        <v>6784225</v>
+        <v>6784253</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16326,7 +16326,7 @@
         <v>127718380</v>
       </c>
       <c r="B148" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>127719855</v>
       </c>
       <c r="B149" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>127715006</v>
       </c>
       <c r="B150" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16649,10 +16649,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127715519</v>
+        <v>127718190</v>
       </c>
       <c r="B151" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16684,10 +16684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464800</v>
+        <v>464678</v>
       </c>
       <c r="R151" t="n">
-        <v>6784210</v>
+        <v>6784123</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16756,10 +16756,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127718190</v>
+        <v>127715684</v>
       </c>
       <c r="B152" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16791,10 +16791,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464678</v>
+        <v>464800</v>
       </c>
       <c r="R152" t="n">
-        <v>6784123</v>
+        <v>6784210</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16978,7 +16978,7 @@
         <v>127718021</v>
       </c>
       <c r="B154" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>127719463</v>
       </c>
       <c r="B155" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719947</v>
+        <v>127719674</v>
       </c>
       <c r="B156" t="n">
-        <v>79641</v>
+        <v>79061</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,37 +17199,40 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464623</v>
+        <v>464745</v>
       </c>
       <c r="R156" t="n">
-        <v>6784354</v>
+        <v>6784305</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17256,19 +17259,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17277,28 +17275,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127717666</v>
+        <v>127719947</v>
       </c>
       <c r="B157" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17330,10 +17329,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464682</v>
+        <v>464623</v>
       </c>
       <c r="R157" t="n">
-        <v>6784195</v>
+        <v>6784354</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17402,10 +17401,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127719674</v>
+        <v>127717666</v>
       </c>
       <c r="B158" t="n">
-        <v>79055</v>
+        <v>79647</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17413,40 +17412,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464745</v>
+        <v>464682</v>
       </c>
       <c r="R158" t="n">
-        <v>6784305</v>
+        <v>6784195</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17473,14 +17469,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17489,19 +17490,18 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
         <v>127719762</v>
       </c>
       <c r="B159" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>127714369</v>
       </c>
       <c r="B160" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17721,10 +17721,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127719525</v>
+        <v>127714657</v>
       </c>
       <c r="B161" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17732,40 +17732,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464859</v>
+        <v>464858</v>
       </c>
       <c r="R161" t="n">
-        <v>6784218</v>
+        <v>6784259</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17792,14 +17789,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17808,29 +17810,28 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127714657</v>
+        <v>127719525</v>
       </c>
       <c r="B162" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17838,37 +17839,40 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>464858</v>
+        <v>464859</v>
       </c>
       <c r="R162" t="n">
-        <v>6784259</v>
+        <v>6784218</v>
       </c>
       <c r="S162" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17895,19 +17899,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17916,18 +17915,19 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -17937,7 +17937,7 @@
         <v>127719588</v>
       </c>
       <c r="B163" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>127718357</v>
       </c>
       <c r="B164" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>127714909</v>
       </c>
       <c r="B166" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18361,48 +18361,53 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127718026</v>
+        <v>127720039</v>
       </c>
       <c r="B167" t="n">
-        <v>79023</v>
+        <v>58042</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464701</v>
+        <v>464615</v>
       </c>
       <c r="R167" t="n">
-        <v>6784168</v>
+        <v>6784345</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18468,53 +18473,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127720039</v>
+        <v>127718026</v>
       </c>
       <c r="B168" t="n">
-        <v>58036</v>
+        <v>79029</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>464615</v>
+        <v>464701</v>
       </c>
       <c r="R168" t="n">
-        <v>6784345</v>
+        <v>6784168</v>
       </c>
       <c r="S168" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127716661</v>
+        <v>127714955</v>
       </c>
       <c r="B169" t="n">
-        <v>57663</v>
+        <v>78788</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18591,39 +18591,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R169" t="n">
-        <v>6784275</v>
+        <v>6784281</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18692,10 +18687,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127714955</v>
+        <v>127715185</v>
       </c>
       <c r="B170" t="n">
-        <v>78782</v>
+        <v>79618</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18703,21 +18698,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18727,10 +18722,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464844</v>
+        <v>464836</v>
       </c>
       <c r="R170" t="n">
-        <v>6784281</v>
+        <v>6784199</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18799,10 +18794,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127715185</v>
+        <v>127716661</v>
       </c>
       <c r="B171" t="n">
-        <v>79612</v>
+        <v>57669</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18810,34 +18805,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464836</v>
+        <v>464710</v>
       </c>
       <c r="R171" t="n">
-        <v>6784199</v>
+        <v>6784275</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,10 +18906,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127718015</v>
+        <v>127719813</v>
       </c>
       <c r="B172" t="n">
-        <v>79612</v>
+        <v>79647</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18917,21 +18917,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18941,10 +18941,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464701</v>
+        <v>464647</v>
       </c>
       <c r="R172" t="n">
-        <v>6784168</v>
+        <v>6784377</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19013,10 +19013,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127719816</v>
+        <v>127718375</v>
       </c>
       <c r="B173" t="n">
-        <v>79612</v>
+        <v>79647</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,40 +19024,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464752</v>
+        <v>464664</v>
       </c>
       <c r="R173" t="n">
-        <v>6784264</v>
+        <v>6784142</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19084,14 +19081,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19100,51 +19102,50 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127719841</v>
+        <v>127720766</v>
       </c>
       <c r="B174" t="n">
-        <v>79612</v>
+        <v>8450</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19154,10 +19155,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>464647</v>
+        <v>464581</v>
       </c>
       <c r="R174" t="n">
-        <v>6784377</v>
+        <v>6784393</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19226,10 +19227,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127718375</v>
+        <v>127718015</v>
       </c>
       <c r="B175" t="n">
-        <v>79641</v>
+        <v>79618</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19237,21 +19238,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19261,10 +19262,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464664</v>
+        <v>464701</v>
       </c>
       <c r="R175" t="n">
-        <v>6784142</v>
+        <v>6784168</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19333,10 +19334,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127719813</v>
+        <v>127719816</v>
       </c>
       <c r="B176" t="n">
-        <v>79641</v>
+        <v>79618</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19344,37 +19345,40 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464647</v>
+        <v>464752</v>
       </c>
       <c r="R176" t="n">
-        <v>6784377</v>
+        <v>6784264</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19401,19 +19405,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19422,50 +19421,51 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127720766</v>
+        <v>127719841</v>
       </c>
       <c r="B177" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464581</v>
+        <v>464647</v>
       </c>
       <c r="R177" t="n">
-        <v>6784393</v>
+        <v>6784377</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19550,7 +19550,7 @@
         <v>127714169</v>
       </c>
       <c r="B178" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>127718840</v>
       </c>
       <c r="B179" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19766,10 +19766,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127719838</v>
+        <v>127719298</v>
       </c>
       <c r="B180" t="n">
-        <v>78782</v>
+        <v>57669</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19777,37 +19777,45 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>464647</v>
+        <v>464943</v>
       </c>
       <c r="R180" t="n">
-        <v>6784377</v>
+        <v>6784241</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19834,19 +19842,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>09:40</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19861,22 +19859,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127719298</v>
+        <v>127718884</v>
       </c>
       <c r="B181" t="n">
-        <v>57663</v>
+        <v>57799</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19884,45 +19882,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>103035</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>464943</v>
+        <v>464607</v>
       </c>
       <c r="R181" t="n">
-        <v>6784241</v>
+        <v>6784297</v>
       </c>
       <c r="S181" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19949,9 +19944,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19966,65 +19971,69 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127718884</v>
+        <v>127719338</v>
       </c>
       <c r="B182" t="n">
-        <v>57793</v>
+        <v>8450</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>103035</v>
+        <v>106545</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464607</v>
+        <v>464893</v>
       </c>
       <c r="R182" t="n">
-        <v>6784297</v>
+        <v>6784258</v>
       </c>
       <c r="S182" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20051,96 +20060,78 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127719338</v>
+        <v>127719838</v>
       </c>
       <c r="B183" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>464893</v>
+        <v>464647</v>
       </c>
       <c r="R183" t="n">
-        <v>6784258</v>
+        <v>6784377</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20167,30 +20158,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20200,7 +20200,7 @@
         <v>127715270</v>
       </c>
       <c r="B184" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127719747</v>
+        <v>127715332</v>
       </c>
       <c r="B186" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20428,40 +20428,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>464834</v>
+        <v>464836</v>
       </c>
       <c r="R186" t="n">
-        <v>6784187</v>
+        <v>6784193</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20488,14 +20485,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20504,29 +20506,28 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127716097</v>
+        <v>127719747</v>
       </c>
       <c r="B187" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20534,37 +20535,40 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>464774</v>
+        <v>464834</v>
       </c>
       <c r="R187" t="n">
-        <v>6784280</v>
+        <v>6784187</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20591,19 +20595,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20612,18 +20611,19 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -20633,7 +20633,7 @@
         <v>127718968</v>
       </c>
       <c r="B188" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20737,10 +20737,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127715332</v>
+        <v>127716097</v>
       </c>
       <c r="B189" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20772,10 +20772,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>464836</v>
+        <v>464774</v>
       </c>
       <c r="R189" t="n">
-        <v>6784193</v>
+        <v>6784280</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20844,10 +20844,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127719836</v>
+        <v>127719877</v>
       </c>
       <c r="B190" t="n">
-        <v>79612</v>
+        <v>91369</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20855,21 +20855,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464715</v>
+        <v>464667</v>
       </c>
       <c r="R190" t="n">
-        <v>6784291</v>
+        <v>6784226</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -20918,11 +20918,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20950,10 +20945,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719877</v>
+        <v>127719836</v>
       </c>
       <c r="B191" t="n">
-        <v>91361</v>
+        <v>79618</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20961,21 +20956,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20988,10 +20983,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464667</v>
+        <v>464715</v>
       </c>
       <c r="R191" t="n">
-        <v>6784226</v>
+        <v>6784291</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21024,6 +21019,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21051,10 +21051,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127717898</v>
+        <v>127714444</v>
       </c>
       <c r="B192" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21062,21 +21062,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464701</v>
+        <v>464913</v>
       </c>
       <c r="R192" t="n">
-        <v>6784168</v>
+        <v>6784254</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21158,32 +21158,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127721018</v>
+        <v>127717898</v>
       </c>
       <c r="B193" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21193,10 +21193,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464816</v>
+        <v>464701</v>
       </c>
       <c r="R193" t="n">
-        <v>6784317</v>
+        <v>6784168</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21265,51 +21265,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127719210</v>
+        <v>127721018</v>
       </c>
       <c r="B194" t="n">
-        <v>79612</v>
+        <v>8450</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464941</v>
+        <v>464816</v>
       </c>
       <c r="R194" t="n">
-        <v>6784243</v>
+        <v>6784317</v>
       </c>
       <c r="S194" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21336,14 +21333,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21352,29 +21354,28 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127714444</v>
+        <v>127719210</v>
       </c>
       <c r="B195" t="n">
-        <v>79023</v>
+        <v>79618</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21382,37 +21383,40 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464913</v>
+        <v>464941</v>
       </c>
       <c r="R195" t="n">
-        <v>6784254</v>
+        <v>6784243</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21439,19 +21443,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21460,28 +21459,29 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127717085</v>
+        <v>127719863</v>
       </c>
       <c r="B196" t="n">
-        <v>57826</v>
+        <v>91369</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21489,42 +21489,40 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464671</v>
+        <v>464688</v>
       </c>
       <c r="R196" t="n">
-        <v>6784233</v>
+        <v>6784295</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21551,39 +21549,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -21593,7 +21582,7 @@
         <v>127717016</v>
       </c>
       <c r="B197" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21697,10 +21686,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127719863</v>
+        <v>127717085</v>
       </c>
       <c r="B198" t="n">
-        <v>91361</v>
+        <v>57832</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21708,40 +21697,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>464688</v>
+        <v>464671</v>
       </c>
       <c r="R198" t="n">
-        <v>6784295</v>
+        <v>6784233</v>
       </c>
       <c r="S198" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21768,30 +21759,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
@@ -21801,7 +21801,7 @@
         <v>127718180</v>
       </c>
       <c r="B199" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21915,10 +21915,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127707668</v>
+        <v>127718813</v>
       </c>
       <c r="B200" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21950,10 +21950,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464689</v>
+        <v>464588</v>
       </c>
       <c r="R200" t="n">
-        <v>6784378</v>
+        <v>6784281</v>
       </c>
       <c r="S200" t="n">
         <v>50</v>
@@ -21980,27 +21980,27 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22030,7 +22030,7 @@
         <v>127708066</v>
       </c>
       <c r="B201" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22139,48 +22139,53 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127718813</v>
+        <v>127706550</v>
       </c>
       <c r="B202" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464588</v>
+        <v>464683</v>
       </c>
       <c r="R202" t="n">
-        <v>6784281</v>
+        <v>6784461</v>
       </c>
       <c r="S202" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22204,27 +22209,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22233,6 +22238,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22251,53 +22257,48 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127706550</v>
+        <v>127707668</v>
       </c>
       <c r="B203" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464683</v>
+        <v>464689</v>
       </c>
       <c r="R203" t="n">
-        <v>6784461</v>
+        <v>6784378</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22341,7 +22342,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22350,7 +22351,6 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -22372,7 +22372,7 @@
         <v>127717251</v>
       </c>
       <c r="B204" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>127718352</v>
       </c>
       <c r="B205" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>127707057</v>
       </c>
       <c r="B206" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>127706968</v>
       </c>
       <c r="B207" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>127716564</v>
       </c>
       <c r="B208" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>127718964</v>
       </c>
       <c r="B209" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>127751842</v>
       </c>
       <c r="B210" t="n">
-        <v>91571</v>
+        <v>91579</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>127720341</v>
       </c>
       <c r="B211" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>127719613</v>
       </c>
       <c r="B212" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>127719544</v>
       </c>
       <c r="B214" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23612,10 +23612,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127717659</v>
+        <v>127719315</v>
       </c>
       <c r="B215" t="n">
-        <v>79612</v>
+        <v>79029</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23623,21 +23623,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>464682</v>
+        <v>464650</v>
       </c>
       <c r="R215" t="n">
-        <v>6784195</v>
+        <v>6784317</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>2 bilder på 2 stubbar</t>
+          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23724,10 +23724,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127719315</v>
+        <v>127717659</v>
       </c>
       <c r="B216" t="n">
-        <v>79023</v>
+        <v>79618</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23735,21 +23735,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>464650</v>
+        <v>464682</v>
       </c>
       <c r="R216" t="n">
-        <v>6784317</v>
+        <v>6784195</v>
       </c>
       <c r="S216" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  7 bilder där två visar en cirkel</t>
+          <t>2 bilder på 2 stubbar</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23836,10 +23836,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127718616</v>
+        <v>127716791</v>
       </c>
       <c r="B217" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>464618</v>
+        <v>464667</v>
       </c>
       <c r="R217" t="n">
-        <v>6784236</v>
+        <v>6784294</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23948,10 +23948,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127716791</v>
+        <v>127718616</v>
       </c>
       <c r="B218" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>464667</v>
+        <v>464618</v>
       </c>
       <c r="R218" t="n">
-        <v>6784294</v>
+        <v>6784236</v>
       </c>
       <c r="S218" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>127717010</v>
       </c>
       <c r="B219" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24172,10 +24172,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127716476</v>
+        <v>127707455</v>
       </c>
       <c r="B220" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24183,37 +24183,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>464774</v>
+        <v>464669</v>
       </c>
       <c r="R220" t="n">
-        <v>6784282</v>
+        <v>6784449</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24240,27 +24242,27 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24269,7 +24271,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24291,7 +24292,7 @@
         <v>127707530</v>
       </c>
       <c r="B221" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24408,10 +24409,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127707455</v>
+        <v>127716476</v>
       </c>
       <c r="B222" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24419,39 +24420,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464669</v>
+        <v>464774</v>
       </c>
       <c r="R222" t="n">
-        <v>6784449</v>
+        <v>6784282</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24478,27 +24477,27 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24507,6 +24506,7 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -24528,7 +24528,7 @@
         <v>127705327</v>
       </c>
       <c r="B223" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127705478</v>
+        <v>127719810</v>
       </c>
       <c r="B224" t="n">
-        <v>57663</v>
+        <v>78787</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,42 +24653,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464863</v>
+        <v>464647</v>
       </c>
       <c r="R224" t="n">
-        <v>6784423</v>
+        <v>6784377</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24715,27 +24707,27 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24762,10 +24754,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127719810</v>
+        <v>127716937</v>
       </c>
       <c r="B225" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24773,21 +24765,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24797,10 +24789,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464647</v>
+        <v>464680</v>
       </c>
       <c r="R225" t="n">
-        <v>6784377</v>
+        <v>6784254</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24847,7 +24839,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24877,7 +24869,7 @@
         <v>127714858</v>
       </c>
       <c r="B226" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24986,10 +24978,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127716937</v>
+        <v>127705478</v>
       </c>
       <c r="B227" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24997,34 +24989,42 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464680</v>
+        <v>464863</v>
       </c>
       <c r="R227" t="n">
-        <v>6784254</v>
+        <v>6784423</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25051,27 +25051,27 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25101,7 +25101,7 @@
         <v>127717066</v>
       </c>
       <c r="B228" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>127707100</v>
       </c>
       <c r="B229" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>127719942</v>
       </c>
       <c r="B230" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>127714717</v>
       </c>
       <c r="B231" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>127793591</v>
       </c>
       <c r="B232" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127554096</v>
+        <v>127511371</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R2" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127511371</v>
+        <v>127503574</v>
       </c>
       <c r="B3" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R4" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127503663</v>
+        <v>127566254</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464847</v>
+        <v>464782</v>
       </c>
       <c r="R5" t="n">
-        <v>6784531</v>
+        <v>6784529</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127536063</v>
+        <v>127505584</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464819</v>
+        <v>464920</v>
       </c>
       <c r="R6" t="n">
-        <v>6784639</v>
+        <v>6784591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127566254</v>
+        <v>127503663</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464782</v>
+        <v>464847</v>
       </c>
       <c r="R7" t="n">
-        <v>6784529</v>
+        <v>6784531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127505584</v>
+        <v>127536063</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464920</v>
+        <v>464819</v>
       </c>
       <c r="R8" t="n">
-        <v>6784591</v>
+        <v>6784639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127518186</v>
+        <v>127601675</v>
       </c>
       <c r="B11" t="n">
-        <v>75153</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,37 +1647,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464838</v>
+        <v>464886</v>
       </c>
       <c r="R11" t="n">
-        <v>6784648</v>
+        <v>6784594</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,19 +1707,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,28 +1723,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127503996</v>
+        <v>127518186</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464844</v>
+        <v>464838</v>
       </c>
       <c r="R12" t="n">
-        <v>6784533</v>
+        <v>6784648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127601675</v>
+        <v>127503996</v>
       </c>
       <c r="B13" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,40 +1860,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464886</v>
+        <v>464844</v>
       </c>
       <c r="R13" t="n">
-        <v>6784594</v>
+        <v>6784533</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1921,14 +1917,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,19 +1938,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2394,57 +2394,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127602573</v>
+        <v>127580771</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464867</v>
+        <v>464785</v>
       </c>
       <c r="R18" t="n">
-        <v>6784461</v>
+        <v>6784477</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2471,14 +2462,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en torrtall</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,29 +2483,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127580771</v>
+        <v>127524724</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464785</v>
+        <v>464825</v>
       </c>
       <c r="R19" t="n">
-        <v>6784477</v>
+        <v>6784652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B20" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R20" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,48 +2715,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127503116</v>
+        <v>127602573</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464870</v>
+        <v>464867</v>
       </c>
       <c r="R21" t="n">
-        <v>6784516</v>
+        <v>6784461</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,19 +2792,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en torrtall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,18 +2808,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127502954</v>
+        <v>127547132</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464884</v>
+        <v>464846</v>
       </c>
       <c r="R23" t="n">
-        <v>6784499</v>
+        <v>6784631</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127547132</v>
+        <v>127537979</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464846</v>
+        <v>464830</v>
       </c>
       <c r="R24" t="n">
-        <v>6784631</v>
+        <v>6784627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127537979</v>
+        <v>127502954</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464830</v>
+        <v>464884</v>
       </c>
       <c r="R25" t="n">
-        <v>6784627</v>
+        <v>6784499</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B27" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R28" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127602770</v>
+        <v>127567350</v>
       </c>
       <c r="B33" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,40 +4018,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464833</v>
+        <v>464790</v>
       </c>
       <c r="R33" t="n">
-        <v>6784487</v>
+        <v>6784508</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4078,14 +4075,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,26 +4096,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602073</v>
+        <v>127602770</v>
       </c>
       <c r="B34" t="n">
         <v>79061</v>
@@ -4151,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464813</v>
+        <v>464833</v>
       </c>
       <c r="R34" t="n">
-        <v>6784586</v>
+        <v>6784487</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4219,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127567350</v>
+        <v>127602073</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4230,37 +4231,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464790</v>
+        <v>464813</v>
       </c>
       <c r="R35" t="n">
-        <v>6784508</v>
+        <v>6784586</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4287,19 +4291,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4308,28 +4307,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127601649</v>
+        <v>127585927</v>
       </c>
       <c r="B36" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,40 +4337,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464890</v>
+        <v>464839</v>
       </c>
       <c r="R36" t="n">
-        <v>6784589</v>
+        <v>6784435</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,14 +4394,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4413,26 +4415,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4467,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R37" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,10 +4540,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127559415</v>
+        <v>127601649</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,37 +4551,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464894</v>
+        <v>464890</v>
       </c>
       <c r="R38" t="n">
-        <v>6784597</v>
+        <v>6784589</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4607,19 +4611,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,18 +4627,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127582358</v>
+        <v>127601312</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,37 +4981,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464803</v>
+        <v>464864</v>
       </c>
       <c r="R42" t="n">
-        <v>6784481</v>
+        <v>6784567</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5038,19 +5041,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,25 +5057,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127580584</v>
+        <v>127582358</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5112,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464783</v>
+        <v>464803</v>
       </c>
       <c r="R43" t="n">
-        <v>6784477</v>
+        <v>6784481</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5184,10 +5183,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127601312</v>
+        <v>127580584</v>
       </c>
       <c r="B44" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5195,40 +5194,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464864</v>
+        <v>464783</v>
       </c>
       <c r="R44" t="n">
-        <v>6784567</v>
+        <v>6784477</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5255,14 +5251,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,29 +5272,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127602418</v>
+        <v>127507819</v>
       </c>
       <c r="B45" t="n">
-        <v>79061</v>
+        <v>75153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,40 +5301,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464873</v>
+        <v>464858</v>
       </c>
       <c r="R45" t="n">
-        <v>6784704</v>
+        <v>6784650</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5361,14 +5358,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5377,29 +5379,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127507819</v>
+        <v>127539258</v>
       </c>
       <c r="B46" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5407,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5431,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464858</v>
+        <v>464840</v>
       </c>
       <c r="R46" t="n">
-        <v>6784650</v>
+        <v>6784645</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,10 +5504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127539258</v>
+        <v>127602418</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5514,37 +5515,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464840</v>
+        <v>464873</v>
       </c>
       <c r="R47" t="n">
-        <v>6784645</v>
+        <v>6784704</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5571,19 +5575,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,18 +5591,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B60" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R60" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R61" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127627035</v>
+        <v>127627343</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464881</v>
+        <v>464836</v>
       </c>
       <c r="R65" t="n">
-        <v>6784597</v>
+        <v>6784540</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7459,6 +7459,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7486,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127627343</v>
+        <v>127627035</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -7524,10 +7529,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464836</v>
+        <v>464881</v>
       </c>
       <c r="R66" t="n">
-        <v>6784540</v>
+        <v>6784597</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7560,11 +7565,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På 5 tallstammar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8112,7 +8112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R72" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,11 +8186,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8218,7 +8213,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627174</v>
+        <v>127627007</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464796</v>
+        <v>464841</v>
       </c>
       <c r="R73" t="n">
-        <v>6784631</v>
+        <v>6784612</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8292,6 +8287,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8532,7 +8532,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627129</v>
+        <v>127627329</v>
       </c>
       <c r="B76" t="n">
         <v>79061</v>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464866</v>
+        <v>464867</v>
       </c>
       <c r="R76" t="n">
-        <v>6784700</v>
+        <v>6784590</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,7 +8633,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627329</v>
+        <v>127627129</v>
       </c>
       <c r="B77" t="n">
         <v>79061</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464867</v>
+        <v>464866</v>
       </c>
       <c r="R77" t="n">
-        <v>6784590</v>
+        <v>6784700</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9696,7 +9696,7 @@
         <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>127562945</v>
       </c>
       <c r="B95" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127707823</v>
+        <v>127707829</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -13310,50 +13310,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127705654</v>
+        <v>127704405</v>
       </c>
       <c r="B120" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464863</v>
+        <v>464901</v>
       </c>
       <c r="R120" t="n">
-        <v>6784423</v>
+        <v>6784434</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13422,45 +13417,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127704405</v>
+        <v>127705654</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464901</v>
+        <v>464863</v>
       </c>
       <c r="R121" t="n">
-        <v>6784434</v>
+        <v>6784423</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13957,7 +13957,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127707123</v>
+        <v>127707368</v>
       </c>
       <c r="B126" t="n">
         <v>79029</v>
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464660</v>
+        <v>464658</v>
       </c>
       <c r="R126" t="n">
-        <v>6784477</v>
+        <v>6784455</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127707368</v>
+        <v>127705062</v>
       </c>
       <c r="B127" t="n">
         <v>79029</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464658</v>
+        <v>464888</v>
       </c>
       <c r="R127" t="n">
-        <v>6784455</v>
+        <v>6784446</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14278,7 +14278,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127705062</v>
+        <v>127707123</v>
       </c>
       <c r="B129" t="n">
         <v>79029</v>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464888</v>
+        <v>464660</v>
       </c>
       <c r="R129" t="n">
-        <v>6784446</v>
+        <v>6784477</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14813,7 +14813,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127715439</v>
+        <v>127714234</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -14848,13 +14848,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464832</v>
+        <v>464936</v>
       </c>
       <c r="R134" t="n">
-        <v>6784214</v>
+        <v>6784248</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14920,10 +14920,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127721029</v>
+        <v>127719564</v>
       </c>
       <c r="B135" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14931,37 +14931,40 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464816</v>
+        <v>464859</v>
       </c>
       <c r="R135" t="n">
-        <v>6784317</v>
+        <v>6784218</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14988,19 +14991,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15009,25 +15007,26 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127714234</v>
+        <v>127721029</v>
       </c>
       <c r="B136" t="n">
         <v>79029</v>
@@ -15062,13 +15061,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464936</v>
+        <v>464816</v>
       </c>
       <c r="R136" t="n">
-        <v>6784248</v>
+        <v>6784317</v>
       </c>
       <c r="S136" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15097,7 +15096,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15107,7 +15106,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15134,7 +15133,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127720285</v>
+        <v>127715439</v>
       </c>
       <c r="B137" t="n">
         <v>79029</v>
@@ -15169,13 +15168,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464564</v>
+        <v>464832</v>
       </c>
       <c r="R137" t="n">
-        <v>6784324</v>
+        <v>6784214</v>
       </c>
       <c r="S137" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15215,11 +15214,6 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15246,7 +15240,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127715198</v>
+        <v>127720285</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -15281,13 +15275,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464836</v>
+        <v>464564</v>
       </c>
       <c r="R138" t="n">
-        <v>6784199</v>
+        <v>6784324</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15327,6 +15321,11 @@
       <c r="AB138" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15353,32 +15352,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127718498</v>
+        <v>127715198</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15388,13 +15387,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464686</v>
+        <v>464836</v>
       </c>
       <c r="R139" t="n">
-        <v>6784147</v>
+        <v>6784199</v>
       </c>
       <c r="S139" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15460,51 +15459,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127719564</v>
+        <v>127718498</v>
       </c>
       <c r="B140" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464859</v>
+        <v>464686</v>
       </c>
       <c r="R140" t="n">
-        <v>6784218</v>
+        <v>6784147</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15531,14 +15527,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15547,19 +15548,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15673,10 +15673,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127719996</v>
+        <v>127718502</v>
       </c>
       <c r="B142" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15684,43 +15684,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464615</v>
+        <v>464686</v>
       </c>
       <c r="R142" t="n">
-        <v>6784345</v>
+        <v>6784147</v>
       </c>
       <c r="S142" t="n">
         <v>50</v>
@@ -15789,7 +15780,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127718502</v>
+        <v>127718980</v>
       </c>
       <c r="B143" t="n">
         <v>79029</v>
@@ -15824,13 +15815,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464686</v>
+        <v>464628</v>
       </c>
       <c r="R143" t="n">
-        <v>6784147</v>
+        <v>6784279</v>
       </c>
       <c r="S143" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15896,10 +15887,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127718980</v>
+        <v>127719996</v>
       </c>
       <c r="B144" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15907,37 +15898,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464628</v>
+        <v>464615</v>
       </c>
       <c r="R144" t="n">
-        <v>6784279</v>
+        <v>6784345</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127715912</v>
+        <v>127718380</v>
       </c>
       <c r="B147" t="n">
         <v>79029</v>
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464770</v>
+        <v>464664</v>
       </c>
       <c r="R147" t="n">
-        <v>6784253</v>
+        <v>6784142</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16323,7 +16323,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127718380</v>
+        <v>127715912</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -16358,10 +16358,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464664</v>
+        <v>464770</v>
       </c>
       <c r="R148" t="n">
-        <v>6784142</v>
+        <v>6784253</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16430,10 +16430,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127719855</v>
+        <v>127715006</v>
       </c>
       <c r="B149" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16441,34 +16441,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464647</v>
+        <v>464844</v>
       </c>
       <c r="R149" t="n">
-        <v>6784377</v>
+        <v>6784281</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16537,10 +16542,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127715006</v>
+        <v>127719855</v>
       </c>
       <c r="B150" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16548,39 +16553,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464844</v>
+        <v>464647</v>
       </c>
       <c r="R150" t="n">
-        <v>6784281</v>
+        <v>6784377</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16649,48 +16649,57 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127718190</v>
+        <v>127719421</v>
       </c>
       <c r="B151" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464678</v>
+        <v>464871</v>
       </c>
       <c r="R151" t="n">
-        <v>6784123</v>
+        <v>6784277</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16717,19 +16726,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På 2 torrtallar, en tallåga</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16738,28 +16742,29 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127715684</v>
+        <v>127718021</v>
       </c>
       <c r="B152" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16767,21 +16772,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16791,10 +16796,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464800</v>
+        <v>464701</v>
       </c>
       <c r="R152" t="n">
-        <v>6784210</v>
+        <v>6784168</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16863,43 +16868,37 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127719421</v>
+        <v>127719463</v>
       </c>
       <c r="B153" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16907,10 +16906,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464871</v>
+        <v>464867</v>
       </c>
       <c r="R153" t="n">
-        <v>6784277</v>
+        <v>6784270</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16947,7 +16946,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På 2 torrtallar, en tallåga</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16975,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127718021</v>
+        <v>127715519</v>
       </c>
       <c r="B154" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16986,21 +16985,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17010,10 +17009,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464701</v>
+        <v>464800</v>
       </c>
       <c r="R154" t="n">
-        <v>6784168</v>
+        <v>6784210</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17082,10 +17081,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127719463</v>
+        <v>127718190</v>
       </c>
       <c r="B155" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17093,40 +17092,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464867</v>
+        <v>464678</v>
       </c>
       <c r="R155" t="n">
-        <v>6784270</v>
+        <v>6784123</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17153,14 +17149,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17169,29 +17170,28 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719674</v>
+        <v>127719947</v>
       </c>
       <c r="B156" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,40 +17199,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464745</v>
+        <v>464623</v>
       </c>
       <c r="R156" t="n">
-        <v>6784305</v>
+        <v>6784354</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17259,14 +17256,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17275,26 +17277,25 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127719947</v>
+        <v>127717666</v>
       </c>
       <c r="B157" t="n">
         <v>79647</v>
@@ -17329,10 +17330,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464623</v>
+        <v>464682</v>
       </c>
       <c r="R157" t="n">
-        <v>6784354</v>
+        <v>6784195</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17401,10 +17402,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127717666</v>
+        <v>127719674</v>
       </c>
       <c r="B158" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17412,37 +17413,40 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464682</v>
+        <v>464745</v>
       </c>
       <c r="R158" t="n">
-        <v>6784195</v>
+        <v>6784305</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17469,19 +17473,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17490,18 +17489,19 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17614,7 +17614,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127714369</v>
+        <v>127714657</v>
       </c>
       <c r="B160" t="n">
         <v>79029</v>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464931</v>
+        <v>464858</v>
       </c>
       <c r="R160" t="n">
-        <v>6784233</v>
+        <v>6784259</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127714657</v>
+        <v>127714369</v>
       </c>
       <c r="B161" t="n">
         <v>79029</v>
@@ -17756,13 +17756,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464858</v>
+        <v>464931</v>
       </c>
       <c r="R161" t="n">
-        <v>6784259</v>
+        <v>6784233</v>
       </c>
       <c r="S161" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17934,51 +17934,48 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127719588</v>
+        <v>127716709</v>
       </c>
       <c r="B163" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R163" t="n">
-        <v>6784242</v>
+        <v>6784275</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18005,14 +18002,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18021,19 +18023,18 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -18147,48 +18148,51 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127716709</v>
+        <v>127719588</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R165" t="n">
-        <v>6784275</v>
+        <v>6784242</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18215,19 +18219,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18236,66 +18235,72 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127714909</v>
+        <v>127720039</v>
       </c>
       <c r="B166" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464844</v>
+        <v>464615</v>
       </c>
       <c r="R166" t="n">
-        <v>6784281</v>
+        <v>6784345</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18361,53 +18366,48 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127720039</v>
+        <v>127714909</v>
       </c>
       <c r="B167" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464615</v>
+        <v>464844</v>
       </c>
       <c r="R167" t="n">
-        <v>6784345</v>
+        <v>6784281</v>
       </c>
       <c r="S167" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18687,10 +18687,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127715185</v>
+        <v>127716661</v>
       </c>
       <c r="B170" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18698,34 +18698,39 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464836</v>
+        <v>464710</v>
       </c>
       <c r="R170" t="n">
-        <v>6784199</v>
+        <v>6784275</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18794,10 +18799,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127716661</v>
+        <v>127715185</v>
       </c>
       <c r="B171" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18805,39 +18810,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464710</v>
+        <v>464836</v>
       </c>
       <c r="R171" t="n">
-        <v>6784275</v>
+        <v>6784199</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,7 +18906,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127719813</v>
+        <v>127718375</v>
       </c>
       <c r="B172" t="n">
         <v>79647</v>
@@ -18941,10 +18941,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464647</v>
+        <v>464664</v>
       </c>
       <c r="R172" t="n">
-        <v>6784377</v>
+        <v>6784142</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19013,7 +19013,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127718375</v>
+        <v>127719813</v>
       </c>
       <c r="B173" t="n">
         <v>79647</v>
@@ -19048,10 +19048,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464664</v>
+        <v>464647</v>
       </c>
       <c r="R173" t="n">
-        <v>6784142</v>
+        <v>6784377</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20197,53 +20197,53 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127715270</v>
+        <v>127719259</v>
       </c>
       <c r="B184" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>464836</v>
+        <v>464943</v>
       </c>
       <c r="R184" t="n">
-        <v>6784199</v>
+        <v>6784241</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20270,19 +20270,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår i talllåga</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20291,71 +20286,72 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127719259</v>
+        <v>127715270</v>
       </c>
       <c r="B185" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>464943</v>
+        <v>464836</v>
       </c>
       <c r="R185" t="n">
-        <v>6784241</v>
+        <v>6784199</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20382,14 +20378,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår i talllåga</t>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20398,26 +20399,25 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127715332</v>
+        <v>127716097</v>
       </c>
       <c r="B186" t="n">
         <v>79029</v>
@@ -20452,10 +20452,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>464836</v>
+        <v>464774</v>
       </c>
       <c r="R186" t="n">
-        <v>6784193</v>
+        <v>6784280</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20524,10 +20524,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127719747</v>
+        <v>127715332</v>
       </c>
       <c r="B187" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20535,40 +20535,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>464834</v>
+        <v>464836</v>
       </c>
       <c r="R187" t="n">
-        <v>6784187</v>
+        <v>6784193</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20595,14 +20592,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20611,19 +20613,18 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -20737,10 +20738,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127716097</v>
+        <v>127719747</v>
       </c>
       <c r="B189" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20748,37 +20749,40 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>464774</v>
+        <v>464834</v>
       </c>
       <c r="R189" t="n">
-        <v>6784280</v>
+        <v>6784187</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20805,19 +20809,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20826,18 +20825,19 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
         <v>127719877</v>
       </c>
       <c r="B190" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21051,32 +21051,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127714444</v>
+        <v>127721018</v>
       </c>
       <c r="B192" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464913</v>
+        <v>464816</v>
       </c>
       <c r="R192" t="n">
-        <v>6784254</v>
+        <v>6784317</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21158,10 +21158,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127717898</v>
+        <v>127719210</v>
       </c>
       <c r="B193" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21169,37 +21169,40 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464701</v>
+        <v>464941</v>
       </c>
       <c r="R193" t="n">
-        <v>6784168</v>
+        <v>6784243</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21226,19 +21229,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21247,50 +21245,51 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127721018</v>
+        <v>127714444</v>
       </c>
       <c r="B194" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21300,10 +21299,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>464816</v>
+        <v>464913</v>
       </c>
       <c r="R194" t="n">
-        <v>6784317</v>
+        <v>6784254</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21335,7 +21334,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21345,7 +21344,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21372,10 +21371,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127719210</v>
+        <v>127717898</v>
       </c>
       <c r="B195" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21383,40 +21382,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464941</v>
+        <v>464701</v>
       </c>
       <c r="R195" t="n">
-        <v>6784243</v>
+        <v>6784168</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21443,14 +21439,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21459,19 +21460,18 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
         <v>127719863</v>
       </c>
       <c r="B196" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127708066</v>
+        <v>127707668</v>
       </c>
       <c r="B201" t="n">
         <v>79029</v>
@@ -22062,13 +22062,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464699</v>
+        <v>464689</v>
       </c>
       <c r="R201" t="n">
-        <v>6784396</v>
+        <v>6784378</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>2 bilder, rikligt på tall</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22139,50 +22139,45 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127706550</v>
+        <v>127708066</v>
       </c>
       <c r="B202" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464683</v>
+        <v>464699</v>
       </c>
       <c r="R202" t="n">
-        <v>6784461</v>
+        <v>6784396</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22229,7 +22224,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22238,7 +22233,6 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22257,48 +22251,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127707668</v>
+        <v>127706550</v>
       </c>
       <c r="B203" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>464689</v>
+        <v>464683</v>
       </c>
       <c r="R203" t="n">
-        <v>6784378</v>
+        <v>6784461</v>
       </c>
       <c r="S203" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22342,7 +22341,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>3 bilder på vedsvamp, tallåga.  Citronticka/Filtskinn, osäker artbestämning</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22351,6 +22350,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -23053,7 +23053,7 @@
         <v>127751842</v>
       </c>
       <c r="B210" t="n">
-        <v>91579</v>
+        <v>91580</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127716791</v>
+        <v>127718616</v>
       </c>
       <c r="B217" t="n">
         <v>79029</v>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>464667</v>
+        <v>464618</v>
       </c>
       <c r="R217" t="n">
-        <v>6784294</v>
+        <v>6784236</v>
       </c>
       <c r="S217" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127718616</v>
+        <v>127716791</v>
       </c>
       <c r="B218" t="n">
         <v>79029</v>
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>464618</v>
+        <v>464667</v>
       </c>
       <c r="R218" t="n">
-        <v>6784236</v>
+        <v>6784294</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24172,10 +24172,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127707455</v>
+        <v>127716476</v>
       </c>
       <c r="B220" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24183,39 +24183,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>464669</v>
+        <v>464774</v>
       </c>
       <c r="R220" t="n">
-        <v>6784449</v>
+        <v>6784282</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24242,27 +24240,27 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24271,6 +24269,7 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -24409,10 +24408,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127716476</v>
+        <v>127707455</v>
       </c>
       <c r="B222" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24420,37 +24419,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464774</v>
+        <v>464669</v>
       </c>
       <c r="R222" t="n">
-        <v>6784282</v>
+        <v>6784449</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24477,27 +24478,27 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24506,7 +24507,6 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127719810</v>
+        <v>127714858</v>
       </c>
       <c r="B224" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,21 +24653,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24677,10 +24677,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464647</v>
+        <v>464856</v>
       </c>
       <c r="R224" t="n">
-        <v>6784377</v>
+        <v>6784268</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24754,10 +24754,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127716937</v>
+        <v>127719810</v>
       </c>
       <c r="B225" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24765,21 +24765,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24789,10 +24789,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464680</v>
+        <v>464647</v>
       </c>
       <c r="R225" t="n">
-        <v>6784254</v>
+        <v>6784377</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24866,7 +24866,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127714858</v>
+        <v>127716937</v>
       </c>
       <c r="B226" t="n">
         <v>79029</v>
@@ -24901,10 +24901,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464856</v>
+        <v>464680</v>
       </c>
       <c r="R226" t="n">
-        <v>6784268</v>
+        <v>6784254</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild band i bakgrund</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD226" t="b">

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127511371</v>
+        <v>127554096</v>
       </c>
       <c r="B2" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R2" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127503574</v>
+        <v>127511371</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127554096</v>
+        <v>127503574</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R4" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127566254</v>
+        <v>127505584</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464782</v>
+        <v>464920</v>
       </c>
       <c r="R5" t="n">
-        <v>6784529</v>
+        <v>6784591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127505584</v>
+        <v>127503663</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464920</v>
+        <v>464847</v>
       </c>
       <c r="R6" t="n">
-        <v>6784591</v>
+        <v>6784531</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127503663</v>
+        <v>127536063</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464847</v>
+        <v>464819</v>
       </c>
       <c r="R7" t="n">
-        <v>6784531</v>
+        <v>6784639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127536063</v>
+        <v>127566254</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464819</v>
+        <v>464782</v>
       </c>
       <c r="R8" t="n">
-        <v>6784639</v>
+        <v>6784529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127581092</v>
+        <v>127504284</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464794</v>
+        <v>464840</v>
       </c>
       <c r="R14" t="n">
-        <v>6784479</v>
+        <v>6784571</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,6 +2037,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,48 +2068,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127585141</v>
+        <v>127503447</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464827</v>
+        <v>464865</v>
       </c>
       <c r="R15" t="n">
-        <v>6784453</v>
+        <v>6784539</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2180,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127504284</v>
+        <v>127581092</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2205,13 +2215,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464840</v>
+        <v>464794</v>
       </c>
       <c r="R16" t="n">
-        <v>6784571</v>
+        <v>6784479</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,11 +2261,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,53 +2287,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127503447</v>
+        <v>127585141</v>
       </c>
       <c r="B17" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464865</v>
+        <v>464827</v>
       </c>
       <c r="R17" t="n">
-        <v>6784539</v>
+        <v>6784453</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127580771</v>
+        <v>127524724</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464785</v>
+        <v>464825</v>
       </c>
       <c r="R18" t="n">
-        <v>6784477</v>
+        <v>6784652</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B19" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R19" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127503116</v>
+        <v>127580771</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464870</v>
+        <v>464785</v>
       </c>
       <c r="R20" t="n">
-        <v>6784516</v>
+        <v>6784477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127547132</v>
+        <v>127502954</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464846</v>
+        <v>464884</v>
       </c>
       <c r="R23" t="n">
-        <v>6784631</v>
+        <v>6784499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127537979</v>
+        <v>127547132</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464830</v>
+        <v>464846</v>
       </c>
       <c r="R24" t="n">
-        <v>6784627</v>
+        <v>6784631</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127502954</v>
+        <v>127537979</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464884</v>
+        <v>464830</v>
       </c>
       <c r="R25" t="n">
-        <v>6784499</v>
+        <v>6784627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R27" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B28" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R28" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127580438</v>
+        <v>127503065</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464780</v>
+        <v>464885</v>
       </c>
       <c r="R29" t="n">
-        <v>6784485</v>
+        <v>6784500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,6 +3656,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,7 +3687,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127503065</v>
+        <v>127503208</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464885</v>
+        <v>464880</v>
       </c>
       <c r="R30" t="n">
-        <v>6784500</v>
+        <v>6784522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,7 +3794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127503208</v>
+        <v>127580438</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464880</v>
+        <v>464780</v>
       </c>
       <c r="R31" t="n">
-        <v>6784522</v>
+        <v>6784485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127601312</v>
+        <v>127582358</v>
       </c>
       <c r="B42" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,40 +4981,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464864</v>
+        <v>464803</v>
       </c>
       <c r="R42" t="n">
-        <v>6784567</v>
+        <v>6784481</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5041,14 +5038,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5057,26 +5059,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127582358</v>
+        <v>127580584</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5111,10 +5112,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464803</v>
+        <v>464783</v>
       </c>
       <c r="R43" t="n">
-        <v>6784481</v>
+        <v>6784477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5183,10 +5184,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127580584</v>
+        <v>127601312</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5194,37 +5195,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464783</v>
+        <v>464864</v>
       </c>
       <c r="R44" t="n">
-        <v>6784477</v>
+        <v>6784567</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5251,19 +5255,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5272,18 +5271,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127627233</v>
+        <v>127627267</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464804</v>
+        <v>464839</v>
       </c>
       <c r="R51" t="n">
-        <v>6784620</v>
+        <v>6784616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,11 +6005,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127627267</v>
+        <v>127627233</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6048,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464839</v>
+        <v>464804</v>
       </c>
       <c r="R52" t="n">
-        <v>6784616</v>
+        <v>6784620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,6 +6106,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6345,7 +6345,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626980</v>
+        <v>127627464</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464883</v>
+        <v>464880</v>
       </c>
       <c r="R55" t="n">
-        <v>6784583</v>
+        <v>6784448</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6419,6 +6419,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,7 +6451,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127627464</v>
+        <v>127626980</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6484,10 +6489,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464880</v>
+        <v>464883</v>
       </c>
       <c r="R56" t="n">
-        <v>6784448</v>
+        <v>6784583</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6520,11 +6525,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6552,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127627244</v>
+        <v>127627419</v>
       </c>
       <c r="B57" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464822</v>
+        <v>464828</v>
       </c>
       <c r="R57" t="n">
-        <v>6784620</v>
+        <v>6784480</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,6 +6626,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6653,10 +6658,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127627419</v>
+        <v>127627244</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6664,21 +6669,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464828</v>
+        <v>464822</v>
       </c>
       <c r="R58" t="n">
-        <v>6784480</v>
+        <v>6784620</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6727,11 +6732,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R60" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B61" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R61" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8213,37 +8213,43 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627007</v>
+        <v>127627287</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8251,10 +8257,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464841</v>
+        <v>464842</v>
       </c>
       <c r="R73" t="n">
-        <v>6784612</v>
+        <v>6784599</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8291,7 +8297,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På 10 tallstammar</t>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,43 +8325,37 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627287</v>
+        <v>127627007</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464842</v>
+        <v>464841</v>
       </c>
       <c r="R74" t="n">
-        <v>6784599</v>
+        <v>6784612</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627329</v>
+        <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464867</v>
+        <v>464805</v>
       </c>
       <c r="R76" t="n">
-        <v>6784590</v>
+        <v>6784486</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627129</v>
+        <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464866</v>
+        <v>464822</v>
       </c>
       <c r="R77" t="n">
-        <v>6784700</v>
+        <v>6784620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,6 +8707,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8734,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627383</v>
+        <v>127627129</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8745,21 +8750,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8772,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464805</v>
+        <v>464866</v>
       </c>
       <c r="R78" t="n">
-        <v>6784486</v>
+        <v>6784700</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8835,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627242</v>
+        <v>127627329</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8846,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464822</v>
+        <v>464867</v>
       </c>
       <c r="R79" t="n">
-        <v>6784620</v>
+        <v>6784590</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8909,11 +8914,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8941,7 +8941,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127626927</v>
+        <v>127627358</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464868</v>
+        <v>464792</v>
       </c>
       <c r="R80" t="n">
-        <v>6784557</v>
+        <v>6784524</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9047,7 +9047,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127627358</v>
+        <v>127626927</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464792</v>
+        <v>464868</v>
       </c>
       <c r="R81" t="n">
-        <v>6784524</v>
+        <v>6784557</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På 3 tallstammar</t>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9153,10 +9153,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127626967</v>
+        <v>127627351</v>
       </c>
       <c r="B82" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9191,10 +9191,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464854</v>
+        <v>464813</v>
       </c>
       <c r="R82" t="n">
-        <v>6784570</v>
+        <v>6784554</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9227,6 +9227,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9254,7 +9259,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127627351</v>
+        <v>127627454</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -9292,10 +9297,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464813</v>
+        <v>464860</v>
       </c>
       <c r="R83" t="n">
-        <v>6784554</v>
+        <v>6784458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9332,7 +9337,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9360,10 +9365,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127627454</v>
+        <v>127626967</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9371,21 +9376,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9398,10 +9403,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464860</v>
+        <v>464854</v>
       </c>
       <c r="R84" t="n">
-        <v>6784458</v>
+        <v>6784570</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9434,11 +9439,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På 3 granar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127562945</v>
+        <v>127544415</v>
       </c>
       <c r="B95" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464814</v>
+        <v>464836</v>
       </c>
       <c r="R95" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Bilder, 2 exemplar</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10690,10 +10690,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127544415</v>
+        <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10701,21 +10701,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464836</v>
+        <v>464814</v>
       </c>
       <c r="R96" t="n">
-        <v>6784606</v>
+        <v>6784582</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder</t>
+          <t>Bilder, 2 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10802,10 +10802,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127554764</v>
+        <v>127504835</v>
       </c>
       <c r="B97" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10813,27 +10813,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10841,13 +10840,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464854</v>
+        <v>464893</v>
       </c>
       <c r="R97" t="n">
-        <v>6784587</v>
+        <v>6784570</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10891,7 +10890,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Bild på hackspår samt Mindre m...</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10900,6 +10899,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10918,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127504835</v>
+        <v>127554764</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10929,26 +10929,27 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10956,13 +10957,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464893</v>
+        <v>464854</v>
       </c>
       <c r="R98" t="n">
-        <v>6784570</v>
+        <v>6784587</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11006,7 +11007,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11015,7 +11016,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -11063,19 +11063,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R99" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11122,7 +11119,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Miljöbilder för området, rikligt med garnlav</t>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11131,7 +11128,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11150,7 +11146,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -11179,16 +11175,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R100" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11235,7 +11234,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11244,6 +11243,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127705423</v>
+        <v>127705998</v>
       </c>
       <c r="B110" t="n">
         <v>79029</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464849</v>
+        <v>464708</v>
       </c>
       <c r="R110" t="n">
-        <v>6784443</v>
+        <v>6784437</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127705998</v>
+        <v>127705423</v>
       </c>
       <c r="B111" t="n">
         <v>79029</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464708</v>
+        <v>464849</v>
       </c>
       <c r="R111" t="n">
-        <v>6784437</v>
+        <v>6784443</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12439,10 +12439,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127704413</v>
+        <v>127706997</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464906</v>
+        <v>464666</v>
       </c>
       <c r="R112" t="n">
-        <v>6784432</v>
+        <v>6784496</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127704473</v>
+        <v>127704413</v>
       </c>
       <c r="B113" t="n">
         <v>79029</v>
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464897</v>
+        <v>464906</v>
       </c>
       <c r="R113" t="n">
-        <v>6784413</v>
+        <v>6784432</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12653,10 +12653,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127706997</v>
+        <v>127704473</v>
       </c>
       <c r="B114" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12664,21 +12664,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12688,10 +12688,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464666</v>
+        <v>464897</v>
       </c>
       <c r="R114" t="n">
-        <v>6784496</v>
+        <v>6784413</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12984,10 +12984,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127706768</v>
+        <v>127705869</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12995,34 +12995,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464683</v>
+        <v>464736</v>
       </c>
       <c r="R117" t="n">
-        <v>6784461</v>
+        <v>6784473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13091,10 +13096,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127705869</v>
+        <v>127706768</v>
       </c>
       <c r="B118" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13102,39 +13107,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464736</v>
+        <v>464683</v>
       </c>
       <c r="R118" t="n">
-        <v>6784473</v>
+        <v>6784461</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127705062</v>
+        <v>127705832</v>
       </c>
       <c r="B127" t="n">
         <v>79029</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464888</v>
+        <v>464736</v>
       </c>
       <c r="R127" t="n">
-        <v>6784446</v>
+        <v>6784473</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14171,7 +14171,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127705832</v>
+        <v>127707123</v>
       </c>
       <c r="B128" t="n">
         <v>79029</v>
@@ -14206,10 +14206,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464736</v>
+        <v>464660</v>
       </c>
       <c r="R128" t="n">
-        <v>6784473</v>
+        <v>6784477</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14278,7 +14278,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127707123</v>
+        <v>127705062</v>
       </c>
       <c r="B129" t="n">
         <v>79029</v>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464660</v>
+        <v>464888</v>
       </c>
       <c r="R129" t="n">
-        <v>6784477</v>
+        <v>6784446</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14599,32 +14599,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127707939</v>
+        <v>127706356</v>
       </c>
       <c r="B132" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14634,10 +14634,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464707</v>
+        <v>464687</v>
       </c>
       <c r="R132" t="n">
-        <v>6784355</v>
+        <v>6784448</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14706,32 +14706,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127706356</v>
+        <v>127707939</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14741,10 +14741,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464687</v>
+        <v>464707</v>
       </c>
       <c r="R133" t="n">
-        <v>6784448</v>
+        <v>6784355</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14813,7 +14813,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127714234</v>
+        <v>127721029</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -14848,13 +14848,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464936</v>
+        <v>464816</v>
       </c>
       <c r="R134" t="n">
-        <v>6784248</v>
+        <v>6784317</v>
       </c>
       <c r="S134" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14920,10 +14920,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127719564</v>
+        <v>127715439</v>
       </c>
       <c r="B135" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14931,40 +14931,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464859</v>
+        <v>464832</v>
       </c>
       <c r="R135" t="n">
-        <v>6784218</v>
+        <v>6784214</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14991,14 +14988,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15007,26 +15009,25 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127721029</v>
+        <v>127714234</v>
       </c>
       <c r="B136" t="n">
         <v>79029</v>
@@ -15061,13 +15062,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464816</v>
+        <v>464936</v>
       </c>
       <c r="R136" t="n">
-        <v>6784317</v>
+        <v>6784248</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15096,7 +15097,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15106,7 +15107,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15133,7 +15134,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127715439</v>
+        <v>127720285</v>
       </c>
       <c r="B137" t="n">
         <v>79029</v>
@@ -15168,13 +15169,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464832</v>
+        <v>464564</v>
       </c>
       <c r="R137" t="n">
-        <v>6784214</v>
+        <v>6784324</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15214,6 +15215,11 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15240,7 +15246,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127720285</v>
+        <v>127715198</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -15275,13 +15281,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464564</v>
+        <v>464836</v>
       </c>
       <c r="R138" t="n">
-        <v>6784324</v>
+        <v>6784199</v>
       </c>
       <c r="S138" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15321,11 +15327,6 @@
       <c r="AB138" t="inlineStr">
         <is>
           <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 30 meter  Inga bilder</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15352,32 +15353,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127715198</v>
+        <v>127718498</v>
       </c>
       <c r="B139" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15387,13 +15388,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464836</v>
+        <v>464686</v>
       </c>
       <c r="R139" t="n">
-        <v>6784199</v>
+        <v>6784147</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15459,48 +15460,51 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127718498</v>
+        <v>127719564</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464686</v>
+        <v>464859</v>
       </c>
       <c r="R140" t="n">
-        <v>6784147</v>
+        <v>6784218</v>
       </c>
       <c r="S140" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15527,19 +15531,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15548,25 +15547,26 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127715717</v>
+        <v>127718502</v>
       </c>
       <c r="B141" t="n">
         <v>79029</v>
@@ -15601,13 +15601,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464788</v>
+        <v>464686</v>
       </c>
       <c r="R141" t="n">
-        <v>6784220</v>
+        <v>6784147</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15673,10 +15673,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127718502</v>
+        <v>127719996</v>
       </c>
       <c r="B142" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15684,34 +15684,43 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464686</v>
+        <v>464615</v>
       </c>
       <c r="R142" t="n">
-        <v>6784147</v>
+        <v>6784345</v>
       </c>
       <c r="S142" t="n">
         <v>50</v>
@@ -15780,10 +15789,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127718980</v>
+        <v>127719621</v>
       </c>
       <c r="B143" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15791,37 +15800,40 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464628</v>
+        <v>464775</v>
       </c>
       <c r="R143" t="n">
-        <v>6784279</v>
+        <v>6784302</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15848,19 +15860,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15869,28 +15876,29 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127719996</v>
+        <v>127715717</v>
       </c>
       <c r="B144" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15898,46 +15906,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464615</v>
+        <v>464788</v>
       </c>
       <c r="R144" t="n">
-        <v>6784345</v>
+        <v>6784220</v>
       </c>
       <c r="S144" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16003,10 +16002,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127719621</v>
+        <v>127718980</v>
       </c>
       <c r="B145" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16014,40 +16013,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464775</v>
+        <v>464628</v>
       </c>
       <c r="R145" t="n">
-        <v>6784302</v>
+        <v>6784279</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16074,14 +16070,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16090,26 +16091,25 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127714269</v>
+        <v>127715912</v>
       </c>
       <c r="B146" t="n">
         <v>79029</v>
@@ -16144,10 +16144,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>464939</v>
+        <v>464770</v>
       </c>
       <c r="R146" t="n">
-        <v>6784225</v>
+        <v>6784253</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16323,7 +16323,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127715912</v>
+        <v>127714269</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -16358,10 +16358,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464770</v>
+        <v>464939</v>
       </c>
       <c r="R148" t="n">
-        <v>6784253</v>
+        <v>6784225</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16761,10 +16761,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127718021</v>
+        <v>127715519</v>
       </c>
       <c r="B152" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16772,21 +16772,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16796,10 +16796,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464701</v>
+        <v>464800</v>
       </c>
       <c r="R152" t="n">
-        <v>6784168</v>
+        <v>6784210</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16868,10 +16868,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127719463</v>
+        <v>127718190</v>
       </c>
       <c r="B153" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16879,40 +16879,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464867</v>
+        <v>464678</v>
       </c>
       <c r="R153" t="n">
-        <v>6784270</v>
+        <v>6784123</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16939,14 +16936,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16955,29 +16957,28 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127715519</v>
+        <v>127719463</v>
       </c>
       <c r="B154" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16985,37 +16986,40 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R154" t="n">
-        <v>6784210</v>
+        <v>6784270</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17042,19 +17046,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17063,28 +17062,29 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127718190</v>
+        <v>127718021</v>
       </c>
       <c r="B155" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17092,21 +17092,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17116,10 +17116,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464678</v>
+        <v>464701</v>
       </c>
       <c r="R155" t="n">
-        <v>6784123</v>
+        <v>6784168</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17295,10 +17295,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127717666</v>
+        <v>127719674</v>
       </c>
       <c r="B157" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17306,37 +17306,40 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464682</v>
+        <v>464745</v>
       </c>
       <c r="R157" t="n">
-        <v>6784195</v>
+        <v>6784305</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17363,19 +17366,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17384,28 +17382,29 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127719674</v>
+        <v>127717666</v>
       </c>
       <c r="B158" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17413,40 +17412,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464745</v>
+        <v>464682</v>
       </c>
       <c r="R158" t="n">
-        <v>6784305</v>
+        <v>6784195</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17473,14 +17469,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17489,19 +17490,18 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17934,48 +17934,51 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127716709</v>
+        <v>127719588</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464710</v>
+        <v>464844</v>
       </c>
       <c r="R163" t="n">
-        <v>6784275</v>
+        <v>6784242</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18002,19 +18005,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18023,18 +18021,19 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -18148,51 +18147,48 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127719588</v>
+        <v>127716709</v>
       </c>
       <c r="B165" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R165" t="n">
-        <v>6784242</v>
+        <v>6784275</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18219,14 +18215,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18235,72 +18236,66 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127720039</v>
+        <v>127714909</v>
       </c>
       <c r="B166" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464615</v>
+        <v>464844</v>
       </c>
       <c r="R166" t="n">
-        <v>6784345</v>
+        <v>6784281</v>
       </c>
       <c r="S166" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18366,7 +18361,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127714909</v>
+        <v>127718026</v>
       </c>
       <c r="B167" t="n">
         <v>79029</v>
@@ -18401,10 +18396,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464844</v>
+        <v>464701</v>
       </c>
       <c r="R167" t="n">
-        <v>6784281</v>
+        <v>6784168</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18473,48 +18468,53 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127718026</v>
+        <v>127720039</v>
       </c>
       <c r="B168" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>464701</v>
+        <v>464615</v>
       </c>
       <c r="R168" t="n">
-        <v>6784168</v>
+        <v>6784345</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127714955</v>
+        <v>127716661</v>
       </c>
       <c r="B169" t="n">
-        <v>78788</v>
+        <v>57669</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18591,34 +18591,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R169" t="n">
-        <v>6784281</v>
+        <v>6784275</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18687,10 +18692,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127716661</v>
+        <v>127715185</v>
       </c>
       <c r="B170" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18698,39 +18703,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464710</v>
+        <v>464836</v>
       </c>
       <c r="R170" t="n">
-        <v>6784275</v>
+        <v>6784199</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18799,10 +18799,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127715185</v>
+        <v>127714955</v>
       </c>
       <c r="B171" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18810,21 +18810,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18834,10 +18834,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464836</v>
+        <v>464844</v>
       </c>
       <c r="R171" t="n">
-        <v>6784199</v>
+        <v>6784281</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19227,7 +19227,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127718015</v>
+        <v>127719816</v>
       </c>
       <c r="B175" t="n">
         <v>79618</v>
@@ -19256,19 +19256,22 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464701</v>
+        <v>464752</v>
       </c>
       <c r="R175" t="n">
-        <v>6784168</v>
+        <v>6784264</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19295,19 +19298,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19316,25 +19314,26 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127719816</v>
+        <v>127718015</v>
       </c>
       <c r="B176" t="n">
         <v>79618</v>
@@ -19363,22 +19362,19 @@
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464752</v>
+        <v>464701</v>
       </c>
       <c r="R176" t="n">
-        <v>6784264</v>
+        <v>6784168</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19405,14 +19401,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19421,19 +19422,18 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -20197,53 +20197,53 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127719259</v>
+        <v>127715270</v>
       </c>
       <c r="B184" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>464943</v>
+        <v>464836</v>
       </c>
       <c r="R184" t="n">
-        <v>6784241</v>
+        <v>6784199</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20270,14 +20270,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår i talllåga</t>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20286,72 +20291,71 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127715270</v>
+        <v>127719259</v>
       </c>
       <c r="B185" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>464836</v>
+        <v>464943</v>
       </c>
       <c r="R185" t="n">
-        <v>6784199</v>
+        <v>6784241</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20378,19 +20382,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår i talllåga</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20399,28 +20398,29 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127716097</v>
+        <v>127719747</v>
       </c>
       <c r="B186" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20428,37 +20428,40 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>464774</v>
+        <v>464834</v>
       </c>
       <c r="R186" t="n">
-        <v>6784280</v>
+        <v>6784187</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20485,19 +20488,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20506,25 +20504,26 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127715332</v>
+        <v>127716097</v>
       </c>
       <c r="B187" t="n">
         <v>79029</v>
@@ -20559,10 +20558,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>464836</v>
+        <v>464774</v>
       </c>
       <c r="R187" t="n">
-        <v>6784193</v>
+        <v>6784280</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20631,10 +20630,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127718968</v>
+        <v>127715332</v>
       </c>
       <c r="B188" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20642,21 +20641,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20666,10 +20665,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464628</v>
+        <v>464836</v>
       </c>
       <c r="R188" t="n">
-        <v>6784279</v>
+        <v>6784193</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20738,10 +20737,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127719747</v>
+        <v>127718968</v>
       </c>
       <c r="B189" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20749,40 +20748,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>464834</v>
+        <v>464628</v>
       </c>
       <c r="R189" t="n">
-        <v>6784187</v>
+        <v>6784279</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20809,14 +20805,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20825,19 +20826,18 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -21158,10 +21158,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127719210</v>
+        <v>127717898</v>
       </c>
       <c r="B193" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21169,40 +21169,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464941</v>
+        <v>464701</v>
       </c>
       <c r="R193" t="n">
-        <v>6784243</v>
+        <v>6784168</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21229,14 +21226,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21245,19 +21247,18 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -21371,10 +21372,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127717898</v>
+        <v>127719210</v>
       </c>
       <c r="B195" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21382,37 +21383,40 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464701</v>
+        <v>464941</v>
       </c>
       <c r="R195" t="n">
-        <v>6784168</v>
+        <v>6784243</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21439,19 +21443,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21460,28 +21459,29 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127719863</v>
+        <v>127717016</v>
       </c>
       <c r="B196" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21489,40 +21489,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464688</v>
+        <v>464672</v>
       </c>
       <c r="R196" t="n">
-        <v>6784295</v>
+        <v>6784257</v>
       </c>
       <c r="S196" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21549,40 +21546,49 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127717016</v>
+        <v>127719863</v>
       </c>
       <c r="B197" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21590,37 +21596,40 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>464672</v>
+        <v>464688</v>
       </c>
       <c r="R197" t="n">
-        <v>6784257</v>
+        <v>6784295</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21647,39 +21656,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
@@ -21915,7 +21915,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127718813</v>
+        <v>127707668</v>
       </c>
       <c r="B200" t="n">
         <v>79029</v>
@@ -21950,10 +21950,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>464588</v>
+        <v>464689</v>
       </c>
       <c r="R200" t="n">
-        <v>6784281</v>
+        <v>6784378</v>
       </c>
       <c r="S200" t="n">
         <v>50</v>
@@ -21980,27 +21980,27 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22027,7 +22027,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127707668</v>
+        <v>127708066</v>
       </c>
       <c r="B201" t="n">
         <v>79029</v>
@@ -22062,13 +22062,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>464689</v>
+        <v>464699</v>
       </c>
       <c r="R201" t="n">
-        <v>6784378</v>
+        <v>6784396</v>
       </c>
       <c r="S201" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder</t>
+          <t>2 bilder, rikligt på tall</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22139,7 +22139,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127708066</v>
+        <v>127718813</v>
       </c>
       <c r="B202" t="n">
         <v>79029</v>
@@ -22174,13 +22174,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>464699</v>
+        <v>464588</v>
       </c>
       <c r="R202" t="n">
-        <v>6784396</v>
+        <v>6784281</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22204,27 +22204,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>2 bilder, rikligt på tall</t>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22705,7 +22705,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127706968</v>
+        <v>127716564</v>
       </c>
       <c r="B207" t="n">
         <v>79029</v>
@@ -22734,22 +22734,19 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>464673</v>
+        <v>464727</v>
       </c>
       <c r="R207" t="n">
-        <v>6784503</v>
+        <v>6784316</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22773,27 +22770,27 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
+          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22802,7 +22799,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -22821,7 +22817,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127716564</v>
+        <v>127706968</v>
       </c>
       <c r="B208" t="n">
         <v>79029</v>
@@ -22850,19 +22846,22 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>464727</v>
+        <v>464673</v>
       </c>
       <c r="R208" t="n">
-        <v>6784316</v>
+        <v>6784503</v>
       </c>
       <c r="S208" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22886,27 +22885,27 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter  5 bilder varav en med garn 6 meter</t>
+          <t>Nära garnlav 5 bilder på vedsvampar på tallåga.  Timmergröppa/Gullgröppa, osäker artbestämning.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22915,6 +22914,7 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127714858</v>
+        <v>127719810</v>
       </c>
       <c r="B224" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,21 +24653,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24677,10 +24677,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464856</v>
+        <v>464647</v>
       </c>
       <c r="R224" t="n">
-        <v>6784268</v>
+        <v>6784377</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild band i bakgrund</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24754,10 +24754,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127719810</v>
+        <v>127705478</v>
       </c>
       <c r="B225" t="n">
-        <v>78787</v>
+        <v>57669</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24765,34 +24765,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464647</v>
+        <v>464863</v>
       </c>
       <c r="R225" t="n">
-        <v>6784377</v>
+        <v>6784423</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24819,27 +24827,27 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24866,7 +24874,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127716937</v>
+        <v>127714858</v>
       </c>
       <c r="B226" t="n">
         <v>79029</v>
@@ -24901,10 +24909,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464680</v>
+        <v>464856</v>
       </c>
       <c r="R226" t="n">
-        <v>6784254</v>
+        <v>6784268</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24951,7 +24959,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24978,10 +24986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127705478</v>
+        <v>127716937</v>
       </c>
       <c r="B227" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24989,42 +24997,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464863</v>
+        <v>464680</v>
       </c>
       <c r="R227" t="n">
-        <v>6784423</v>
+        <v>6784254</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25051,27 +25051,27 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25098,10 +25098,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127717066</v>
+        <v>127707100</v>
       </c>
       <c r="B228" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25109,37 +25109,39 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>464671</v>
+        <v>464660</v>
       </c>
       <c r="R228" t="n">
-        <v>6784233</v>
+        <v>6784477</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25166,27 +25168,27 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
+          <t>2 bilder, hål ca 3 meter upp</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25195,7 +25197,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25214,10 +25215,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127707100</v>
+        <v>127717066</v>
       </c>
       <c r="B229" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25225,39 +25226,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>464660</v>
+        <v>464671</v>
       </c>
       <c r="R229" t="n">
-        <v>6784477</v>
+        <v>6784233</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25284,27 +25283,27 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>2 bilder, hål ca 3 meter upp</t>
+          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25313,6 +25312,7 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127505584</v>
+        <v>127566254</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464920</v>
+        <v>464782</v>
       </c>
       <c r="R5" t="n">
-        <v>6784591</v>
+        <v>6784529</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127503663</v>
+        <v>127601236</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1114,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464847</v>
+        <v>464862</v>
       </c>
       <c r="R6" t="n">
-        <v>6784531</v>
+        <v>6784534</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,19 +1174,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,28 +1190,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127536063</v>
+        <v>127602494</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1220,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464819</v>
+        <v>464821</v>
       </c>
       <c r="R7" t="n">
-        <v>6784639</v>
+        <v>6784490</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,19 +1280,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,25 +1296,26 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127566254</v>
+        <v>127505584</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1352,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464782</v>
+        <v>464920</v>
       </c>
       <c r="R8" t="n">
-        <v>6784529</v>
+        <v>6784591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B9" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,40 +1433,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R9" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,14 +1490,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,29 +1511,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B10" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,40 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R10" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,14 +1597,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,29 +1618,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127601675</v>
+        <v>127518186</v>
       </c>
       <c r="B11" t="n">
-        <v>78787</v>
+        <v>75153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,40 +1647,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464886</v>
+        <v>464838</v>
       </c>
       <c r="R11" t="n">
-        <v>6784594</v>
+        <v>6784648</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,14 +1704,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,29 +1725,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127518186</v>
+        <v>127503996</v>
       </c>
       <c r="B12" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464838</v>
+        <v>464844</v>
       </c>
       <c r="R12" t="n">
-        <v>6784648</v>
+        <v>6784533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127503996</v>
+        <v>127601675</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,37 +1861,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464844</v>
+        <v>464886</v>
       </c>
       <c r="R13" t="n">
-        <v>6784533</v>
+        <v>6784594</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,19 +1921,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,25 +1937,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127504284</v>
+        <v>127581092</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464840</v>
+        <v>464794</v>
       </c>
       <c r="R14" t="n">
-        <v>6784571</v>
+        <v>6784479</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,11 +2037,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,53 +2063,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127503447</v>
+        <v>127585141</v>
       </c>
       <c r="B15" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464865</v>
+        <v>464827</v>
       </c>
       <c r="R15" t="n">
-        <v>6784539</v>
+        <v>6784453</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,48 +2170,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127581092</v>
+        <v>127503447</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464794</v>
+        <v>464865</v>
       </c>
       <c r="R16" t="n">
-        <v>6784479</v>
+        <v>6784539</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2287,7 +2282,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127585141</v>
+        <v>127504284</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2322,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464827</v>
+        <v>464840</v>
       </c>
       <c r="R17" t="n">
-        <v>6784453</v>
+        <v>6784571</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2368,6 +2363,11 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127524724</v>
+        <v>127580771</v>
       </c>
       <c r="B18" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464825</v>
+        <v>464785</v>
       </c>
       <c r="R18" t="n">
-        <v>6784652</v>
+        <v>6784477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127503116</v>
+        <v>127524724</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464870</v>
+        <v>464825</v>
       </c>
       <c r="R19" t="n">
-        <v>6784516</v>
+        <v>6784652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127580771</v>
+        <v>127503116</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464785</v>
+        <v>464870</v>
       </c>
       <c r="R20" t="n">
-        <v>6784477</v>
+        <v>6784516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127502954</v>
+        <v>127547132</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464884</v>
+        <v>464846</v>
       </c>
       <c r="R23" t="n">
-        <v>6784499</v>
+        <v>6784631</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127547132</v>
+        <v>127537979</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464846</v>
+        <v>464830</v>
       </c>
       <c r="R24" t="n">
-        <v>6784631</v>
+        <v>6784627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127537979</v>
+        <v>127502954</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464830</v>
+        <v>464884</v>
       </c>
       <c r="R25" t="n">
-        <v>6784627</v>
+        <v>6784499</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127503065</v>
+        <v>127580438</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464885</v>
+        <v>464780</v>
       </c>
       <c r="R29" t="n">
-        <v>6784500</v>
+        <v>6784485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,11 +3656,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3687,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127503208</v>
+        <v>127503065</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464880</v>
+        <v>464885</v>
       </c>
       <c r="R30" t="n">
-        <v>6784522</v>
+        <v>6784500</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,6 +3763,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,7 +3794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127580438</v>
+        <v>127503208</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464780</v>
+        <v>464880</v>
       </c>
       <c r="R31" t="n">
-        <v>6784485</v>
+        <v>6784522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127585927</v>
+        <v>127601649</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,37 +4337,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464839</v>
+        <v>464890</v>
       </c>
       <c r="R36" t="n">
-        <v>6784435</v>
+        <v>6784589</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4394,19 +4397,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,25 +4413,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127559415</v>
+        <v>127585927</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4468,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464894</v>
+        <v>464839</v>
       </c>
       <c r="R37" t="n">
-        <v>6784597</v>
+        <v>6784435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127601649</v>
+        <v>127559415</v>
       </c>
       <c r="B38" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4551,40 +4550,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464890</v>
+        <v>464894</v>
       </c>
       <c r="R38" t="n">
-        <v>6784589</v>
+        <v>6784597</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4611,14 +4607,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,19 +4628,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127627267</v>
+        <v>127627233</v>
       </c>
       <c r="B51" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464839</v>
+        <v>464804</v>
       </c>
       <c r="R51" t="n">
-        <v>6784616</v>
+        <v>6784620</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,6 +6005,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6037,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127627233</v>
+        <v>127627267</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6043,21 +6048,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464804</v>
+        <v>464839</v>
       </c>
       <c r="R52" t="n">
-        <v>6784620</v>
+        <v>6784616</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6106,11 +6111,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127627347</v>
+        <v>127626980</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464841</v>
+        <v>464883</v>
       </c>
       <c r="R54" t="n">
-        <v>6784551</v>
+        <v>6784583</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,11 +6313,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6451,7 +6446,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626980</v>
+        <v>127627347</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6489,10 +6484,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464883</v>
+        <v>464841</v>
       </c>
       <c r="R56" t="n">
-        <v>6784583</v>
+        <v>6784551</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6525,6 +6520,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6552,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127627419</v>
+        <v>127627244</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,21 +6563,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464828</v>
+        <v>464822</v>
       </c>
       <c r="R57" t="n">
-        <v>6784480</v>
+        <v>6784620</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,11 +6626,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6658,10 +6653,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127627244</v>
+        <v>127627419</v>
       </c>
       <c r="B58" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6669,21 +6664,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464822</v>
+        <v>464828</v>
       </c>
       <c r="R58" t="n">
-        <v>6784620</v>
+        <v>6784480</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6732,6 +6727,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7693,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B68" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,21 +7704,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,6 +7769,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7794,10 +7799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7805,21 +7810,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7870,11 +7875,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8112,37 +8112,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627174</v>
+        <v>127627287</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8150,10 +8156,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464796</v>
+        <v>464842</v>
       </c>
       <c r="R72" t="n">
-        <v>6784631</v>
+        <v>6784599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,6 +8192,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,43 +8224,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127627287</v>
+        <v>127627007</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8257,10 +8262,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464842</v>
+        <v>464841</v>
       </c>
       <c r="R73" t="n">
-        <v>6784599</v>
+        <v>6784612</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8297,7 +8302,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På raka</t>
+          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8325,7 +8330,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627007</v>
+        <v>127627174</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -8363,10 +8368,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464841</v>
+        <v>464796</v>
       </c>
       <c r="R74" t="n">
-        <v>6784612</v>
+        <v>6784631</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8399,11 +8404,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På 10 tallstammar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627383</v>
+        <v>127627129</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464805</v>
+        <v>464866</v>
       </c>
       <c r="R76" t="n">
-        <v>6784486</v>
+        <v>6784700</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627242</v>
+        <v>127627329</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464822</v>
+        <v>464867</v>
       </c>
       <c r="R77" t="n">
-        <v>6784620</v>
+        <v>6784590</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,11 +8707,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8739,10 +8734,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627129</v>
+        <v>127627242</v>
       </c>
       <c r="B78" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8750,21 +8745,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8777,10 +8772,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464866</v>
+        <v>464822</v>
       </c>
       <c r="R78" t="n">
-        <v>6784700</v>
+        <v>6784620</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8813,6 +8808,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627329</v>
+        <v>127627383</v>
       </c>
       <c r="B79" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464867</v>
+        <v>464805</v>
       </c>
       <c r="R79" t="n">
-        <v>6784590</v>
+        <v>6784486</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9578,42 +9578,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127505687</v>
+        <v>127681891</v>
       </c>
       <c r="B86" t="n">
-        <v>57669</v>
+        <v>97346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9621,13 +9617,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464919</v>
+        <v>464897</v>
       </c>
       <c r="R86" t="n">
-        <v>6784599</v>
+        <v>6784620</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9654,27 +9650,18 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9693,38 +9680,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127681891</v>
+        <v>127505687</v>
       </c>
       <c r="B87" t="n">
-        <v>97345</v>
+        <v>57669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9732,13 +9723,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464897</v>
+        <v>464919</v>
       </c>
       <c r="R87" t="n">
-        <v>6784620</v>
+        <v>6784599</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9765,18 +9756,27 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10802,10 +10802,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127504835</v>
+        <v>127554764</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10813,26 +10813,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10840,13 +10841,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464893</v>
+        <v>464854</v>
       </c>
       <c r="R97" t="n">
-        <v>6784570</v>
+        <v>6784587</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10890,7 +10891,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10899,7 +10900,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10918,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127554764</v>
+        <v>127504835</v>
       </c>
       <c r="B98" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10929,27 +10929,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10957,13 +10956,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464854</v>
+        <v>464893</v>
       </c>
       <c r="R98" t="n">
-        <v>6784587</v>
+        <v>6784570</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11007,7 +11006,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Bild på hackspår samt Mindre m...</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11016,6 +11015,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -11063,16 +11063,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R99" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11119,7 +11122,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11128,6 +11131,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11146,7 +11150,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -11175,19 +11179,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R100" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11234,7 +11235,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Miljöbilder för området, rikligt med garnlav</t>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11243,7 +11244,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127705998</v>
+        <v>127705423</v>
       </c>
       <c r="B110" t="n">
         <v>79029</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464708</v>
+        <v>464849</v>
       </c>
       <c r="R110" t="n">
-        <v>6784437</v>
+        <v>6784443</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127705423</v>
+        <v>127705998</v>
       </c>
       <c r="B111" t="n">
         <v>79029</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464849</v>
+        <v>464708</v>
       </c>
       <c r="R111" t="n">
-        <v>6784443</v>
+        <v>6784437</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127706073</v>
+        <v>127707041</v>
       </c>
       <c r="B115" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12771,39 +12771,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464701</v>
+        <v>464666</v>
       </c>
       <c r="R115" t="n">
-        <v>6784425</v>
+        <v>6784496</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12846,11 +12841,6 @@
       <c r="AB115" t="inlineStr">
         <is>
           <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12877,10 +12867,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127707041</v>
+        <v>127706073</v>
       </c>
       <c r="B116" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12888,34 +12878,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464666</v>
+        <v>464701</v>
       </c>
       <c r="R116" t="n">
-        <v>6784496</v>
+        <v>6784425</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12958,6 +12953,11 @@
       <c r="AB116" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15566,7 +15566,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127718502</v>
+        <v>127715717</v>
       </c>
       <c r="B141" t="n">
         <v>79029</v>
@@ -15601,13 +15601,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464686</v>
+        <v>464788</v>
       </c>
       <c r="R141" t="n">
-        <v>6784147</v>
+        <v>6784220</v>
       </c>
       <c r="S141" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127715717</v>
+        <v>127718502</v>
       </c>
       <c r="B144" t="n">
         <v>79029</v>
@@ -15930,13 +15930,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464788</v>
+        <v>464686</v>
       </c>
       <c r="R144" t="n">
-        <v>6784220</v>
+        <v>6784147</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127718380</v>
+        <v>127714269</v>
       </c>
       <c r="B147" t="n">
         <v>79029</v>
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464664</v>
+        <v>464939</v>
       </c>
       <c r="R147" t="n">
-        <v>6784142</v>
+        <v>6784225</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16323,7 +16323,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127714269</v>
+        <v>127718380</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -16358,10 +16358,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464939</v>
+        <v>464664</v>
       </c>
       <c r="R148" t="n">
-        <v>6784225</v>
+        <v>6784142</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17188,10 +17188,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127719947</v>
+        <v>127719674</v>
       </c>
       <c r="B156" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,37 +17199,40 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464623</v>
+        <v>464745</v>
       </c>
       <c r="R156" t="n">
-        <v>6784354</v>
+        <v>6784305</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17256,19 +17259,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17277,28 +17275,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127719674</v>
+        <v>127719947</v>
       </c>
       <c r="B157" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17306,40 +17305,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464745</v>
+        <v>464623</v>
       </c>
       <c r="R157" t="n">
-        <v>6784305</v>
+        <v>6784354</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17366,14 +17362,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17382,19 +17383,18 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -17508,10 +17508,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127719762</v>
+        <v>127719525</v>
       </c>
       <c r="B159" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17519,21 +17519,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>464798</v>
+        <v>464859</v>
       </c>
       <c r="R159" t="n">
-        <v>6784237</v>
+        <v>6784218</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17614,10 +17614,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127714657</v>
+        <v>127719762</v>
       </c>
       <c r="B160" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17625,37 +17625,40 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464858</v>
+        <v>464798</v>
       </c>
       <c r="R160" t="n">
-        <v>6784259</v>
+        <v>6784237</v>
       </c>
       <c r="S160" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17682,19 +17685,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>08:58</t>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17703,25 +17701,26 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127714369</v>
+        <v>127714657</v>
       </c>
       <c r="B161" t="n">
         <v>79029</v>
@@ -17756,13 +17755,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464931</v>
+        <v>464858</v>
       </c>
       <c r="R161" t="n">
-        <v>6784233</v>
+        <v>6784259</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17828,10 +17827,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127719525</v>
+        <v>127714369</v>
       </c>
       <c r="B162" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17839,40 +17838,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>464859</v>
+        <v>464931</v>
       </c>
       <c r="R162" t="n">
-        <v>6784218</v>
+        <v>6784233</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17899,14 +17895,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17915,19 +17916,18 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -18254,48 +18254,53 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127714909</v>
+        <v>127720039</v>
       </c>
       <c r="B166" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464844</v>
+        <v>464615</v>
       </c>
       <c r="R166" t="n">
-        <v>6784281</v>
+        <v>6784345</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18361,7 +18366,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127718026</v>
+        <v>127714909</v>
       </c>
       <c r="B167" t="n">
         <v>79029</v>
@@ -18396,10 +18401,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>464701</v>
+        <v>464844</v>
       </c>
       <c r="R167" t="n">
-        <v>6784168</v>
+        <v>6784281</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18468,53 +18473,48 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127720039</v>
+        <v>127718026</v>
       </c>
       <c r="B168" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>464615</v>
+        <v>464701</v>
       </c>
       <c r="R168" t="n">
-        <v>6784345</v>
+        <v>6784168</v>
       </c>
       <c r="S168" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18580,10 +18580,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127716661</v>
+        <v>127715185</v>
       </c>
       <c r="B169" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18591,39 +18591,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>464710</v>
+        <v>464836</v>
       </c>
       <c r="R169" t="n">
-        <v>6784275</v>
+        <v>6784199</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18692,10 +18687,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127715185</v>
+        <v>127714955</v>
       </c>
       <c r="B170" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18703,21 +18698,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18727,10 +18722,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>464836</v>
+        <v>464844</v>
       </c>
       <c r="R170" t="n">
-        <v>6784199</v>
+        <v>6784281</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18799,10 +18794,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127714955</v>
+        <v>127716661</v>
       </c>
       <c r="B171" t="n">
-        <v>78788</v>
+        <v>57669</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18810,34 +18805,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>464844</v>
+        <v>464710</v>
       </c>
       <c r="R171" t="n">
-        <v>6784281</v>
+        <v>6784275</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18906,10 +18906,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127718375</v>
+        <v>127719816</v>
       </c>
       <c r="B172" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18917,37 +18917,40 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>464664</v>
+        <v>464752</v>
       </c>
       <c r="R172" t="n">
-        <v>6784142</v>
+        <v>6784264</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18974,19 +18977,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18995,28 +18993,29 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127719813</v>
+        <v>127718015</v>
       </c>
       <c r="B173" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,21 +19023,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19048,10 +19047,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>464647</v>
+        <v>464701</v>
       </c>
       <c r="R173" t="n">
-        <v>6784377</v>
+        <v>6784168</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19120,32 +19119,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127720766</v>
+        <v>127719841</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19155,10 +19154,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>464581</v>
+        <v>464647</v>
       </c>
       <c r="R174" t="n">
-        <v>6784393</v>
+        <v>6784377</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19227,10 +19226,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127719816</v>
+        <v>127718375</v>
       </c>
       <c r="B175" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19238,40 +19237,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>464752</v>
+        <v>464664</v>
       </c>
       <c r="R175" t="n">
-        <v>6784264</v>
+        <v>6784142</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19298,14 +19294,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19314,29 +19315,28 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127718015</v>
+        <v>127719813</v>
       </c>
       <c r="B176" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19344,21 +19344,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19368,10 +19368,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464701</v>
+        <v>464647</v>
       </c>
       <c r="R176" t="n">
-        <v>6784168</v>
+        <v>6784377</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19440,32 +19440,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127719841</v>
+        <v>127720766</v>
       </c>
       <c r="B177" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>464647</v>
+        <v>464581</v>
       </c>
       <c r="R177" t="n">
-        <v>6784377</v>
+        <v>6784393</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19871,10 +19871,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127718884</v>
+        <v>127719838</v>
       </c>
       <c r="B181" t="n">
-        <v>57799</v>
+        <v>78788</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19882,42 +19882,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>103035</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>464607</v>
+        <v>464647</v>
       </c>
       <c r="R181" t="n">
-        <v>6784297</v>
+        <v>6784377</v>
       </c>
       <c r="S181" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19983,57 +19978,53 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127719338</v>
+        <v>127718884</v>
       </c>
       <c r="B182" t="n">
-        <v>8450</v>
+        <v>57799</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>103035</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>464893</v>
+        <v>464607</v>
       </c>
       <c r="R182" t="n">
-        <v>6784258</v>
+        <v>6784297</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20060,78 +20051,96 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127719838</v>
+        <v>127719338</v>
       </c>
       <c r="B183" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>464647</v>
+        <v>464893</v>
       </c>
       <c r="R183" t="n">
-        <v>6784377</v>
+        <v>6784258</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20158,39 +20167,30 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127719747</v>
+        <v>127715332</v>
       </c>
       <c r="B186" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20428,40 +20428,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>464834</v>
+        <v>464836</v>
       </c>
       <c r="R186" t="n">
-        <v>6784187</v>
+        <v>6784193</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20488,14 +20485,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20504,29 +20506,28 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127716097</v>
+        <v>127719747</v>
       </c>
       <c r="B187" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20534,37 +20535,40 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>464774</v>
+        <v>464834</v>
       </c>
       <c r="R187" t="n">
-        <v>6784280</v>
+        <v>6784187</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20591,19 +20595,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20612,25 +20611,26 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127715332</v>
+        <v>127716097</v>
       </c>
       <c r="B188" t="n">
         <v>79029</v>
@@ -20665,10 +20665,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464836</v>
+        <v>464774</v>
       </c>
       <c r="R188" t="n">
-        <v>6784193</v>
+        <v>6784280</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20844,10 +20844,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127719877</v>
+        <v>127719836</v>
       </c>
       <c r="B190" t="n">
-        <v>91370</v>
+        <v>79618</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20855,21 +20855,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20882,10 +20882,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>464667</v>
+        <v>464715</v>
       </c>
       <c r="R190" t="n">
-        <v>6784226</v>
+        <v>6784291</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -20918,6 +20918,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20945,10 +20950,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127719836</v>
+        <v>127719877</v>
       </c>
       <c r="B191" t="n">
-        <v>79618</v>
+        <v>91371</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20956,21 +20961,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20983,10 +20988,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464715</v>
+        <v>464667</v>
       </c>
       <c r="R191" t="n">
-        <v>6784291</v>
+        <v>6784226</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -21019,11 +21024,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21051,32 +21051,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127721018</v>
+        <v>127717898</v>
       </c>
       <c r="B192" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464816</v>
+        <v>464701</v>
       </c>
       <c r="R192" t="n">
-        <v>6784317</v>
+        <v>6784168</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21158,10 +21158,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127717898</v>
+        <v>127719210</v>
       </c>
       <c r="B193" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21169,37 +21169,40 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464701</v>
+        <v>464941</v>
       </c>
       <c r="R193" t="n">
-        <v>6784168</v>
+        <v>6784243</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21226,19 +21229,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>09:40</t>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>På en tallstubbe</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21247,18 +21245,19 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -21372,51 +21371,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127719210</v>
+        <v>127721018</v>
       </c>
       <c r="B195" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464941</v>
+        <v>464816</v>
       </c>
       <c r="R195" t="n">
-        <v>6784243</v>
+        <v>6784317</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21443,14 +21439,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>På en tallstubbe</t>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21459,29 +21460,28 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127717016</v>
+        <v>127719863</v>
       </c>
       <c r="B196" t="n">
-        <v>79029</v>
+        <v>91371</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21489,37 +21489,40 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464672</v>
+        <v>464688</v>
       </c>
       <c r="R196" t="n">
-        <v>6784257</v>
+        <v>6784295</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21546,49 +21549,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127719863</v>
+        <v>127717016</v>
       </c>
       <c r="B197" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21596,40 +21590,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>464688</v>
+        <v>464672</v>
       </c>
       <c r="R197" t="n">
-        <v>6784295</v>
+        <v>6784257</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21656,30 +21647,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
         <v>127751842</v>
       </c>
       <c r="B210" t="n">
-        <v>91580</v>
+        <v>91581</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24288,53 +24288,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127707530</v>
+        <v>127707455</v>
       </c>
       <c r="B221" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>464686</v>
+        <v>464669</v>
       </c>
       <c r="R221" t="n">
-        <v>6784430</v>
+        <v>6784449</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24381,7 +24378,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Spillning under tall med en vit påläggning på stammen</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24408,50 +24405,53 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127707455</v>
+        <v>127707530</v>
       </c>
       <c r="B222" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>464669</v>
+        <v>464686</v>
       </c>
       <c r="R222" t="n">
-        <v>6784449</v>
+        <v>6784430</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Spillning under tall med en vit påläggning på stammen</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24642,10 +24642,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127719810</v>
+        <v>127714858</v>
       </c>
       <c r="B224" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24653,21 +24653,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24677,10 +24677,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>464647</v>
+        <v>464856</v>
       </c>
       <c r="R224" t="n">
-        <v>6784377</v>
+        <v>6784268</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>1 bild på kolad högstubbe</t>
+          <t>1 bild band i bakgrund</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24754,10 +24754,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127705478</v>
+        <v>127716937</v>
       </c>
       <c r="B225" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24765,42 +24765,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>464863</v>
+        <v>464680</v>
       </c>
       <c r="R225" t="n">
-        <v>6784423</v>
+        <v>6784254</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24827,27 +24819,27 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, gran med garn</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24874,10 +24866,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127714858</v>
+        <v>127719810</v>
       </c>
       <c r="B226" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24885,21 +24877,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24909,10 +24901,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>464856</v>
+        <v>464647</v>
       </c>
       <c r="R226" t="n">
-        <v>6784268</v>
+        <v>6784377</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24959,7 +24951,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>1 bild band i bakgrund</t>
+          <t>1 bild på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24986,10 +24978,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127716937</v>
+        <v>127705478</v>
       </c>
       <c r="B227" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24997,34 +24989,42 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>464680</v>
+        <v>464863</v>
       </c>
       <c r="R227" t="n">
-        <v>6784254</v>
+        <v>6784423</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25051,27 +25051,27 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>1 bild, gran med garn</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25098,10 +25098,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127707100</v>
+        <v>127717066</v>
       </c>
       <c r="B228" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25109,39 +25109,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>464660</v>
+        <v>464671</v>
       </c>
       <c r="R228" t="n">
-        <v>6784477</v>
+        <v>6784233</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25168,27 +25166,27 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>2 bilder, hål ca 3 meter upp</t>
+          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25197,6 +25195,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25215,10 +25214,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127717066</v>
+        <v>127707100</v>
       </c>
       <c r="B229" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25226,37 +25225,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>464671</v>
+        <v>464660</v>
       </c>
       <c r="R229" t="n">
-        <v>6784233</v>
+        <v>6784477</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25283,27 +25284,27 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Garnlav samt 2 bilder på vedsvamp på tallåga.</t>
+          <t>2 bilder, hål ca 3 meter upp</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25312,7 +25313,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35200-2025 artfynd.xlsx
+++ b/artfynd/A 35200-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127554096</v>
+        <v>127503574</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464854</v>
+        <v>464865</v>
       </c>
       <c r="R2" t="n">
-        <v>6784587</v>
+        <v>6784539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127503574</v>
+        <v>127554096</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464865</v>
+        <v>464854</v>
       </c>
       <c r="R4" t="n">
-        <v>6784539</v>
+        <v>6784587</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127566254</v>
+        <v>127505584</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464782</v>
+        <v>464920</v>
       </c>
       <c r="R5" t="n">
-        <v>6784529</v>
+        <v>6784591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127601236</v>
+        <v>127503663</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464862</v>
+        <v>464847</v>
       </c>
       <c r="R6" t="n">
-        <v>6784534</v>
+        <v>6784531</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,14 +1171,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,29 +1192,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127602494</v>
+        <v>127536063</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,40 +1221,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464821</v>
+        <v>464819</v>
       </c>
       <c r="R7" t="n">
-        <v>6784490</v>
+        <v>6784639</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,14 +1278,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,29 +1299,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127505584</v>
+        <v>127601236</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,37 +1328,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464920</v>
+        <v>464862</v>
       </c>
       <c r="R8" t="n">
-        <v>6784591</v>
+        <v>6784534</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,19 +1388,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,28 +1404,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127503663</v>
+        <v>127602494</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,37 +1434,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464847</v>
+        <v>464821</v>
       </c>
       <c r="R9" t="n">
-        <v>6784531</v>
+        <v>6784490</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,19 +1494,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,25 +1510,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127536063</v>
+        <v>127566254</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464819</v>
+        <v>464782</v>
       </c>
       <c r="R10" t="n">
-        <v>6784639</v>
+        <v>6784529</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127518186</v>
+        <v>127601675</v>
       </c>
       <c r="B11" t="n">
-        <v>75153</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,37 +1647,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464838</v>
+        <v>464886</v>
       </c>
       <c r="R11" t="n">
-        <v>6784648</v>
+        <v>6784594</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,19 +1707,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,28 +1723,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127503996</v>
+        <v>127518186</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464844</v>
+        <v>464838</v>
       </c>
       <c r="R12" t="n">
-        <v>6784533</v>
+        <v>6784648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127601675</v>
+        <v>127503996</v>
       </c>
       <c r="B13" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,40 +1860,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464886</v>
+        <v>464844</v>
       </c>
       <c r="R13" t="n">
-        <v>6784594</v>
+        <v>6784533</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1921,14 +1917,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,26 +1938,25 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127581092</v>
+        <v>127504284</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464794</v>
+        <v>464840</v>
       </c>
       <c r="R14" t="n">
-        <v>6784479</v>
+        <v>6784571</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,6 +2037,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127585141</v>
+        <v>127581092</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2098,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464827</v>
+        <v>464794</v>
       </c>
       <c r="R15" t="n">
-        <v>6784453</v>
+        <v>6784479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,53 +2175,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127503447</v>
+        <v>127585141</v>
       </c>
       <c r="B16" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464865</v>
+        <v>464827</v>
       </c>
       <c r="R16" t="n">
-        <v>6784539</v>
+        <v>6784453</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,45 +2282,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127504284</v>
+        <v>127503447</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464840</v>
+        <v>464865</v>
       </c>
       <c r="R17" t="n">
-        <v>6784571</v>
+        <v>6784539</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2363,11 +2368,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt på en radie av 50 meter.  5 bilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127580771</v>
+        <v>127524724</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464785</v>
+        <v>464825</v>
       </c>
       <c r="R18" t="n">
-        <v>6784477</v>
+        <v>6784652</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127524724</v>
+        <v>127503116</v>
       </c>
       <c r="B19" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464825</v>
+        <v>464870</v>
       </c>
       <c r="R19" t="n">
-        <v>6784652</v>
+        <v>6784516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127503116</v>
+        <v>127580771</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464870</v>
+        <v>464785</v>
       </c>
       <c r="R20" t="n">
-        <v>6784516</v>
+        <v>6784477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,32 +2933,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127547132</v>
+        <v>127502954</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464846</v>
+        <v>464884</v>
       </c>
       <c r="R23" t="n">
-        <v>6784631</v>
+        <v>6784499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127537979</v>
+        <v>127547132</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464830</v>
+        <v>464846</v>
       </c>
       <c r="R24" t="n">
-        <v>6784627</v>
+        <v>6784631</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,32 +3147,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127502954</v>
+        <v>127537979</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464884</v>
+        <v>464830</v>
       </c>
       <c r="R25" t="n">
-        <v>6784499</v>
+        <v>6784627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127505499</v>
+        <v>127584626</v>
       </c>
       <c r="B27" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464908</v>
+        <v>464815</v>
       </c>
       <c r="R27" t="n">
-        <v>6784550</v>
+        <v>6784461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127584626</v>
+        <v>127505499</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464815</v>
+        <v>464908</v>
       </c>
       <c r="R28" t="n">
-        <v>6784461</v>
+        <v>6784550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127580438</v>
+        <v>127503065</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464780</v>
+        <v>464885</v>
       </c>
       <c r="R29" t="n">
-        <v>6784485</v>
+        <v>6784500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,6 +3656,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,7 +3687,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127503065</v>
+        <v>127503208</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464885</v>
+        <v>464880</v>
       </c>
       <c r="R30" t="n">
-        <v>6784500</v>
+        <v>6784522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,7 +3794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127503208</v>
+        <v>127580438</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464880</v>
+        <v>464780</v>
       </c>
       <c r="R31" t="n">
-        <v>6784522</v>
+        <v>6784485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127567350</v>
+        <v>127602770</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,37 +4018,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464790</v>
+        <v>464833</v>
       </c>
       <c r="R33" t="n">
-        <v>6784508</v>
+        <v>6784487</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4075,19 +4078,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4096,25 +4094,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127602770</v>
+        <v>127602073</v>
       </c>
       <c r="B34" t="n">
         <v>79061</v>
@@ -4152,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464833</v>
+        <v>464813</v>
       </c>
       <c r="R34" t="n">
-        <v>6784487</v>
+        <v>6784586</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,10 +4219,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127602073</v>
+        <v>127567350</v>
       </c>
       <c r="B35" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,40 +4230,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464813</v>
+        <v>464790</v>
       </c>
       <c r="R35" t="n">
-        <v>6784586</v>
+        <v>6784508</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4291,14 +4287,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,29 +4308,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127601649</v>
+        <v>127585927</v>
       </c>
       <c r="B36" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,40 +4337,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464890</v>
+        <v>464839</v>
       </c>
       <c r="R36" t="n">
-        <v>6784589</v>
+        <v>6784435</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4397,14 +4394,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4413,26 +4415,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127585927</v>
+        <v>127559415</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4467,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464839</v>
+        <v>464894</v>
       </c>
       <c r="R37" t="n">
-        <v>6784435</v>
+        <v>6784597</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,10 +4540,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127559415</v>
+        <v>127601649</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,37 +4551,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464894</v>
+        <v>464890</v>
       </c>
       <c r="R38" t="n">
-        <v>6784597</v>
+        <v>6784589</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4607,19 +4611,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,18 +4627,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127582358</v>
+        <v>127601312</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,37 +4981,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464803</v>
+        <v>464864</v>
       </c>
       <c r="R42" t="n">
-        <v>6784481</v>
+        <v>6784567</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5038,19 +5041,14 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,25 +5057,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127580584</v>
+        <v>127582358</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -5112,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464783</v>
+        <v>464803</v>
       </c>
       <c r="R43" t="n">
-        <v>6784477</v>
+        <v>6784481</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5184,10 +5183,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127601312</v>
+        <v>127580584</v>
       </c>
       <c r="B44" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5195,40 +5194,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464864</v>
+        <v>464783</v>
       </c>
       <c r="R44" t="n">
-        <v>6784567</v>
+        <v>6784477</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5255,14 +5251,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,29 +5272,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127507819</v>
+        <v>127539258</v>
       </c>
       <c r="B45" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464858</v>
+        <v>464840</v>
       </c>
       <c r="R45" t="n">
-        <v>6784650</v>
+        <v>6784645</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127539258</v>
+        <v>127507819</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464840</v>
+        <v>464858</v>
       </c>
       <c r="R46" t="n">
-        <v>6784645</v>
+        <v>6784650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127503078</v>
+        <v>127528615</v>
       </c>
       <c r="B49" t="n">
         <v>79029</v>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464884</v>
+        <v>464875</v>
       </c>
       <c r="R49" t="n">
-        <v>6784499</v>
+        <v>6784695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,7 +5824,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127528615</v>
+        <v>127503078</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464875</v>
+        <v>464884</v>
       </c>
       <c r="R50" t="n">
-        <v>6784695</v>
+        <v>6784499</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127627233</v>
+        <v>127627267</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464804</v>
+        <v>464839</v>
       </c>
       <c r="R51" t="n">
-        <v>6784620</v>
+        <v>6784616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,11 +6005,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127627267</v>
+        <v>127627233</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6048,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464839</v>
+        <v>464804</v>
       </c>
       <c r="R52" t="n">
-        <v>6784616</v>
+        <v>6784620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,6 +6106,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626980</v>
+        <v>127627464</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464883</v>
+        <v>464880</v>
       </c>
       <c r="R54" t="n">
-        <v>6784583</v>
+        <v>6784448</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,6 +6313,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6340,7 +6345,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127627464</v>
+        <v>127627347</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464880</v>
+        <v>464841</v>
       </c>
       <c r="R55" t="n">
-        <v>6784448</v>
+        <v>6784551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6418,7 +6423,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På 2 tallstammar</t>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,7 +6451,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127627347</v>
+        <v>127626980</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6484,10 +6489,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464841</v>
+        <v>464883</v>
       </c>
       <c r="R56" t="n">
-        <v>6784551</v>
+        <v>6784583</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6520,11 +6525,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6865,10 +6865,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626973</v>
+        <v>127627165</v>
       </c>
       <c r="B60" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,21 +6876,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464856</v>
+        <v>464808</v>
       </c>
       <c r="R60" t="n">
-        <v>6784585</v>
+        <v>6784637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127627165</v>
+        <v>127626973</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,21 +6977,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464808</v>
+        <v>464856</v>
       </c>
       <c r="R61" t="n">
-        <v>6784637</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626939</v>
+        <v>127626956</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,21 +7704,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,11 +7769,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7799,10 +7794,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626956</v>
+        <v>127626939</v>
       </c>
       <c r="B69" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,21 +7805,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7875,6 +7870,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8112,43 +8112,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127627287</v>
+        <v>127627174</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8156,10 +8150,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464842</v>
+        <v>464796</v>
       </c>
       <c r="R72" t="n">
-        <v>6784599</v>
+        <v>6784631</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8192,11 +8186,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På raka</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8330,37 +8319,43 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127627174</v>
+        <v>127627287</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8368,10 +8363,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464796</v>
+        <v>464842</v>
       </c>
       <c r="R74" t="n">
-        <v>6784631</v>
+        <v>6784599</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8404,6 +8399,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På raka</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127627129</v>
+        <v>127627383</v>
       </c>
       <c r="B76" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464866</v>
+        <v>464805</v>
       </c>
       <c r="R76" t="n">
-        <v>6784700</v>
+        <v>6784486</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,10 +8633,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127627329</v>
+        <v>127627242</v>
       </c>
       <c r="B77" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8644,21 +8644,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464867</v>
+        <v>464822</v>
       </c>
       <c r="R77" t="n">
-        <v>6784590</v>
+        <v>6784620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8707,6 +8707,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8734,10 +8739,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627242</v>
+        <v>127627129</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8745,21 +8750,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8772,10 +8777,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464822</v>
+        <v>464866</v>
       </c>
       <c r="R78" t="n">
-        <v>6784620</v>
+        <v>6784700</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8808,11 +8813,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627383</v>
+        <v>127627329</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464805</v>
+        <v>464867</v>
       </c>
       <c r="R79" t="n">
-        <v>6784486</v>
+        <v>6784590</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9578,38 +9578,42 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127681891</v>
+        <v>127505687</v>
       </c>
       <c r="B86" t="n">
-        <v>97346</v>
+        <v>57669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9617,13 +9621,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464897</v>
+        <v>464919</v>
       </c>
       <c r="R86" t="n">
-        <v>6784620</v>
+        <v>6784599</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9650,18 +9654,27 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9680,42 +9693,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127505687</v>
+        <v>127681891</v>
       </c>
       <c r="B87" t="n">
-        <v>57669</v>
+        <v>97347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9723,13 +9732,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464919</v>
+        <v>464897</v>
       </c>
       <c r="R87" t="n">
-        <v>6784599</v>
+        <v>6784620</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9756,27 +9765,18 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127530350</v>
+        <v>127550588</v>
       </c>
       <c r="B88" t="n">
-        <v>79030</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464867</v>
+        <v>464800</v>
       </c>
       <c r="R88" t="n">
-        <v>6784698</v>
+        <v>6784606</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Bilder på gran med garn</t>
+          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127550588</v>
+        <v>127530350</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>79030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464800</v>
+        <v>464867</v>
       </c>
       <c r="R89" t="n">
-        <v>6784606</v>
+        <v>6784698</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 5 bilder nära väg</t>
+          <t>Bilder på gran med garn</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10238,7 +10238,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127506640</v>
+        <v>127505537</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -10273,10 +10273,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464876</v>
+        <v>464924</v>
       </c>
       <c r="R92" t="n">
-        <v>6784663</v>
+        <v>6784563</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Bild med tall i bakgrund</t>
+          <t>Bild på stam mot topp</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10350,7 +10350,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127505537</v>
+        <v>127506640</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464924</v>
+        <v>464876</v>
       </c>
       <c r="R93" t="n">
-        <v>6784563</v>
+        <v>6784663</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Bild på stam mot topp</t>
+          <t>Bild med tall i bakgrund</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10465,7 +10465,7 @@
         <v>127579179</v>
       </c>
       <c r="B94" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>127562945</v>
       </c>
       <c r="B96" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10802,10 +10802,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127554764</v>
+        <v>127504835</v>
       </c>
       <c r="B97" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10813,27 +10813,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10841,13 +10840,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464854</v>
+        <v>464893</v>
       </c>
       <c r="R97" t="n">
-        <v>6784587</v>
+        <v>6784570</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10891,7 +10890,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Bild på hackspår samt Mindre m...</t>
+          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10900,6 +10899,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10918,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127504835</v>
+        <v>127554764</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10929,26 +10929,27 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10956,13 +10957,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464893</v>
+        <v>464854</v>
       </c>
       <c r="R98" t="n">
-        <v>6784570</v>
+        <v>6784587</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11006,7 +11007,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Miljöbilder på rullstensås i området samt garnlav</t>
+          <t>Bild på hackspår samt Mindre m...</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11015,7 +11016,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127565174</v>
+        <v>127504014</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -11063,19 +11063,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464814</v>
+        <v>464846</v>
       </c>
       <c r="R99" t="n">
-        <v>6784582</v>
+        <v>6784532</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11122,7 +11119,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Miljöbilder för området, rikligt med garnlav</t>
+          <t>Bild 3 på tall rikligt</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11131,7 +11128,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11150,7 +11146,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127504014</v>
+        <v>127565174</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -11179,16 +11175,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464846</v>
+        <v>464814</v>
       </c>
       <c r="R100" t="n">
-        <v>6784532</v>
+        <v>6784582</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11235,7 +11234,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Bild 3 på tall rikligt</t>
+          <t>Miljöbilder för området, rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11244,6 +11243,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11797,32 +11797,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127707829</v>
+        <v>127706080</v>
       </c>
       <c r="B106" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464707</v>
+        <v>464701</v>
       </c>
       <c r="R106" t="n">
-        <v>6784355</v>
+        <v>6784425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11904,32 +11904,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127706778</v>
+        <v>127706856</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11939,10 +11939,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464678</v>
+        <v>464680</v>
       </c>
       <c r="R107" t="n">
-        <v>6784479</v>
+        <v>6784495</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12011,32 +12011,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127706080</v>
+        <v>127707829</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464701</v>
+        <v>464707</v>
       </c>
       <c r="R108" t="n">
-        <v>6784425</v>
+        <v>6784355</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12118,32 +12118,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127706856</v>
+        <v>127706778</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464680</v>
+        <v>464678</v>
       </c>
       <c r="R109" t="n">
-        <v>6784495</v>
+        <v>6784479</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12439,10 +12439,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127706997</v>
+        <v>127704413</v>
       </c>
       <c r="B112" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464666</v>
+        <v>464906</v>
       </c>
       <c r="R112" t="n">
-        <v>6784496</v>
+        <v>6784432</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12546,10 +12546,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127704413</v>
+        <v>127706997</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12557,21 +12557,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464906</v>
+        <v>464666</v>
       </c>
       <c r="R113" t="n">
-        <v>6784432</v>
+        <v>6784496</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127707041</v>
+        <v>127706073</v>
       </c>
       <c r="B115" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12771,34 +12771,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464666</v>
+        <v>464701</v>
       </c>
       <c r="R115" t="n">
-        <v>6784496</v>
+        <v>6784425</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,6 +12846,11 @@
       <c r="AB115" t="inlineStr">
         <is>
           <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12867,10 +12877,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127706073</v>
+        <v>127707041</v>
       </c>
       <c r="B116" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12878,39 +12888,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464701</v>
+        <v>464666</v>
       </c>
       <c r="R116" t="n">
-        <v>6784425</v>
+        <v>6784496</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12953,11 +1295